--- a/docs/Phieu-Trai-Nghiem-Tutor.xlsx
+++ b/docs/Phieu-Trai-Nghiem-Tutor.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>giáo viên Tiếng Anh 10A1</t>
+          <t>giáo viên bộ môn lớp 10A1</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Giáo viên của Người thử 2 dạy Toán 10A1 · Người thử 3 dạy Tiếng Anh 10A1.</t>
+          <t>Giáo viên của Người thử 2 và Người thử 3 là giáo viên bộ môn của lớp 10A1.</t>
         </is>
       </c>
       <c r="C29" s="18" t="n"/>
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="D4" s="21" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Đang thử môn nào?</t>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Toán 10 và Tiếng Anh 10 — bản chạy thử cho học sinh khối 10.</t>
+          <t>CHỈ TOÁN 10. Bản chạy thử lần này chỉ nạp Toán 10 (204 bài, 1.430 câu). Các môn khác chưa mở — thấy môn khác trống hoặc không vào được thì đó là đúng hiện trạng, không phải lỗi.</t>
         </is>
       </c>
       <c r="D5" s="21" t="n"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bài khoảng 8 câu, thứ tự cố định từ dễ tới khó. Có nhiều kiểu câu: chọn 1 trong 4 ô · chọn Đúng/Sai cho từng ý a,b,c,d · gõ đáp án · đề chia Bước 1-2-3 trả lời dần từng bước · (tiếng Anh) nối cột, sắp xếp câu.</t>
+          <t>Mỗi bài khoảng 8 câu, thứ tự cố định từ dễ tới khó. Có nhiều kiểu câu: chọn 1 trong 4 ô · chọn Đúng/Sai cho từng ý a,b,c,d · gõ đáp án · đề chia Bước 1-2-3 trả lời dần từng bước · câu tự luận dài thì nộp bài.</t>
         </is>
       </c>
       <c r="D15" s="21" t="n"/>
@@ -1303,98 +1303,98 @@
       </c>
       <c r="D17" s="21" t="n"/>
     </row>
-    <row r="18" ht="34" customHeight="1">
+    <row r="18" ht="62" customHeight="1">
       <c r="B18" s="13" t="inlineStr">
         <is>
+          <t>Học liệu đính kèm bài</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>App có sẵn chỗ gắn HỌC LIỆU vào đầu mỗi bài — slide, podcast, video, phiếu bài tập in ra, flashcard — để em xem/nghe trước khi làm câu hỏi. Học liệu là TỰ HỌC, xem xong không cộng điểm gì, chỉ để hiểu bài. HIỆN TẠI trường CHƯA nạp học liệu nào nên vào bài là thấy câu hỏi luôn, không có mục này — đó là đúng hiện trạng. Phiếu có một câu hỏi riêng để bạn nói muốn mỗi bài kèm sẵn thứ gì.</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="n"/>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="B19" s="13" t="inlineStr">
+        <is>
           <t>Ôn tập · Hạng · Mục tiêu · Tôi</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>Bốn mục dưới cùng. Ôn tập: câu từng làm sai quay lại đúng lúc sắp quên. Hạng: bảng xếp hạng theo nỗ lực. Mục tiêu: việc cần làm tuần này. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
-      <c r="D18" s="21" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+      <c r="D19" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>PHỤ HUYNH THẤY GÌ</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="B21" s="13" t="inlineStr">
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Báo cáo tuần</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>Tên con, số điểm kiến thức đã vững / đang luyện thêm, tiến độ mục tiêu. Đủ để biết con đang đi tới đâu mà không phải hỏi han.</t>
         </is>
       </c>
-      <c r="D21" s="21" t="n"/>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="B22" s="13" t="inlineStr">
+      <c r="D22" s="21" t="n"/>
+    </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>Cố ý KHÔNG có gì</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>Không có nội dung con trò chuyện với trợ lý, không có điểm số từng câu, không so con mình với con nhà người ta. Báo cáo nói về NỖ LỰC và TIẾN BỘ. Đây là ranh giới riêng tư của trẻ — thấy thiếu thông tin thì đó là chủ ý, không phải sót.</t>
         </is>
       </c>
-      <c r="D22" s="21" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="13" t="inlineStr">
+      <c r="D23" s="21" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>Chỉ thấy con mình</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>Một phụ huynh chỉ nhìn được đúng đứa con đã liên kết. Thấy tên em khác là lỗi nghiêm trọng, báo ngay.</t>
         </is>
       </c>
-      <c r="D23" s="21" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+      <c r="D24" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>GIÁO VIÊN THẤY GÌ</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>Tổng quan</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Đang có bao nhiêu em học lúc này, hoạt động 7 ngày, bao nhiêu lượt đến hạn ôn, bao nhiêu bài đang chờ chấm.</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Học sinh</t>
+          <t>Tổng quan</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Danh sách lớp kèm mức thành thạo, độ chính xác, mức nỗ lực — nhìn ra ngay em nào cần kèm.</t>
+          <t>Đang có bao nhiêu em học lúc này, hoạt động 7 ngày, bao nhiêu lượt đến hạn ôn, bao nhiêu bài đang chờ chấm.</t>
         </is>
       </c>
       <c r="D27" s="21" t="n"/>
@@ -1402,55 +1402,59 @@
     <row r="28" ht="20" customHeight="1">
       <c r="B28" s="13" t="inlineStr">
         <is>
+          <t>Học sinh</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Danh sách lớp kèm mức thành thạo, độ chính xác, mức nỗ lực — nhìn ra ngay em nào cần kèm.</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="13" t="inlineStr">
+        <is>
           <t>Chủ đề</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Ý kiến thức nào cả lớp đang yếu — dùng để quyết định tiết sau dạy lại phần nào.</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n"/>
-    </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="B29" s="13" t="inlineStr">
+      <c r="D29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Chấm bài</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>Hàng đợi bài tự luận học sinh nộp: bài em gõ, ảnh em chụp, đáp án mẫu để đối chiếu, và nhận xét sơ khảo của máy. Thầy cô bấm Đạt hoặc Chưa đạt kèm lời nhắn; chưa đạt thì bàn chân của em chuyển ĐỎ và em được mời làm lại.</t>
         </is>
       </c>
-      <c r="D29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="13" t="inlineStr">
+      <c r="D30" s="21" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>Duyệt &amp; nội dung</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Chỗ duyệt câu hỏi, học liệu trước khi tới tay học sinh. Nội dung nào cũng phải qua mắt người thật.</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="25" t="inlineStr">
+      <c r="D31" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>APP CỐ Ý KHÔNG LÀM (đừng báo là lỗi)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>· Không đưa đáp án khi em làm sai — kể cả sai nhiều lần.</t>
         </is>
       </c>
       <c r="C33" s="20" t="n"/>
@@ -1459,7 +1463,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>· Không chấm điểm số 8, 9, 10 kiểu bài kiểm tra. Chỉ có 'đã vững / chưa vững'.</t>
+          <t>· Không đưa đáp án khi em làm sai — kể cả sai nhiều lần.</t>
         </is>
       </c>
       <c r="C34" s="20" t="n"/>
@@ -1468,7 +1472,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="19" t="inlineStr">
         <is>
-          <t>· Không xếp hạng theo điểm giỏi-dốt; xếp theo nỗ lực.</t>
+          <t>· Không chấm điểm số 8, 9, 10 kiểu bài kiểm tra. Chỉ có 'đã vững / chưa vững'.</t>
         </is>
       </c>
       <c r="C35" s="20" t="n"/>
@@ -1477,7 +1481,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>· Không cho phụ huynh đọc nội dung con trò chuyện với trợ lý.</t>
+          <t>· Không xếp hạng theo điểm giỏi-dốt; xếp theo nỗ lực.</t>
         </is>
       </c>
       <c r="C36" s="20" t="n"/>
@@ -1486,55 +1490,65 @@
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>· Không tự động cho qua bài chỉ vì em làm hết số câu.</t>
+          <t>· Không cho phụ huynh đọc nội dung con trò chuyện với trợ lý.</t>
         </is>
       </c>
       <c r="C37" s="20" t="n"/>
       <c r="D37" s="20" t="n"/>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="26" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>· Không tự động cho qua bài chỉ vì em làm hết số câu.</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>Bạn đang thử một bản CHẠY THỬ. Nó chưa hoàn thiện — đó là lý do có phiếu này. Thấy gì lạ cứ ghi, kể cả khi bạn không chắc đó là lỗi hay do mình chưa quen.</t>
         </is>
       </c>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="33">
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B38:D38"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B40:D40"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="C31:D31"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="C21:D21"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B25:D25"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1546,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1832,7 +1846,7 @@
       <c r="N8" s="46" t="n"/>
       <c r="O8" s="40" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>4</v>
       </c>
@@ -1843,12 +1857,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
+          <t>Hiện tại trường CHƯA nạp học liệu nào nên chỗ này KHÔNG hiện gì, vào thẳng câu hỏi luôn — đúng hiện trạng, không phải lỗi. Nếu bạn LẠI thấy một mục 'Bài học' kèm danh sách tài liệu thì mở thử một mục và ghi lại cảm nhận.</t>
         </is>
       </c>
       <c r="E9" s="42" t="n"/>
@@ -1874,12 +1888,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
+          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
         </is>
       </c>
       <c r="E10" s="42" t="n"/>
@@ -1894,7 +1908,7 @@
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="40" t="n"/>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="41" t="n">
         <v>6</v>
       </c>
@@ -1905,12 +1919,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
+          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
         </is>
       </c>
       <c r="E11" s="42" t="n"/>
@@ -1925,7 +1939,7 @@
       <c r="N11" s="46" t="n"/>
       <c r="O11" s="40" t="n"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="41" t="n">
         <v>7</v>
       </c>
@@ -1936,12 +1950,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
+          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
         </is>
       </c>
       <c r="E12" s="42" t="n"/>
@@ -1956,7 +1970,7 @@
       <c r="N12" s="46" t="n"/>
       <c r="O12" s="40" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="41" t="n">
         <v>8</v>
       </c>
@@ -1967,12 +1981,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
+          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
         </is>
       </c>
       <c r="E13" s="42" t="n"/>
@@ -1998,12 +2012,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
+          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
         </is>
       </c>
       <c r="E14" s="42" t="n"/>
@@ -2029,12 +2043,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
         </is>
       </c>
       <c r="E15" s="42" t="n"/>
@@ -2060,12 +2074,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
+          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
         </is>
       </c>
       <c r="E16" s="42" t="n"/>
@@ -2091,12 +2105,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Quay ra chọn môn, thử TIẾNG ANH 10 vài câu.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Cũng có lộ trình riêng. Câu tiếng Anh có dạng nối cột / sắp xếp / điền — thao tác bằng chạm hoặc kéo thả.</t>
+          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
       <c r="E17" s="42" t="n"/>
@@ -2111,7 +2125,7 @@
       <c r="N17" s="46" t="n"/>
       <c r="O17" s="40" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="41" t="n">
         <v>13</v>
       </c>
@@ -2122,12 +2136,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
         </is>
       </c>
       <c r="E18" s="42" t="n"/>
@@ -2142,59 +2156,59 @@
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="40" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Học Sinh</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="43" t="n"/>
+      <c r="I19" s="44" t="n"/>
+      <c r="J19" s="44" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="40" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>VAI PHỤ HUYNH</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Phụ Huynh</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
-        </is>
-      </c>
-      <c r="E20" s="42" t="n"/>
-      <c r="F20" s="42" t="n"/>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="44" t="n"/>
-      <c r="J20" s="44" t="n"/>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="n"/>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="46" t="n"/>
-      <c r="O20" s="40" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="41" t="n">
         <v>15</v>
       </c>
@@ -2205,12 +2219,12 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
+          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
         </is>
       </c>
       <c r="E21" s="42" t="n"/>
@@ -2225,7 +2239,7 @@
       <c r="N21" s="46" t="n"/>
       <c r="O21" s="40" t="n"/>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="41" t="n">
         <v>16</v>
       </c>
@@ -2236,12 +2250,12 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
         </is>
       </c>
       <c r="E22" s="42" t="n"/>
@@ -2256,57 +2270,57 @@
       <c r="N22" s="46" t="n"/>
       <c r="O22" s="40" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="48" t="inlineStr">
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Phụ Huynh</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="43" t="n"/>
+      <c r="H23" s="43" t="n"/>
+      <c r="I23" s="44" t="n"/>
+      <c r="J23" s="44" t="n"/>
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="45" t="n"/>
+      <c r="M23" s="46" t="n"/>
+      <c r="N23" s="46" t="n"/>
+      <c r="O23" s="40" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>VAI GIÁO VIÊN</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="41" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Giáo Viên</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
-        </is>
-      </c>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
-      <c r="G24" s="43" t="n"/>
-      <c r="H24" s="43" t="n"/>
-      <c r="I24" s="44" t="n"/>
-      <c r="J24" s="44" t="n"/>
-      <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="n"/>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="46" t="n"/>
-      <c r="O24" s="40" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="41" t="n">
@@ -2319,12 +2333,12 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
+          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
         </is>
       </c>
       <c r="E25" s="42" t="n"/>
@@ -2339,7 +2353,7 @@
       <c r="N25" s="46" t="n"/>
       <c r="O25" s="40" t="n"/>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="41" t="n">
         <v>19</v>
       </c>
@@ -2350,12 +2364,12 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
         </is>
       </c>
       <c r="E26" s="42" t="n"/>
@@ -2370,7 +2384,7 @@
       <c r="N26" s="46" t="n"/>
       <c r="O26" s="40" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="41" t="n">
         <v>20</v>
       </c>
@@ -2381,12 +2395,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+          <t>Vào tab CHẤM BÀI.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
+          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
         </is>
       </c>
       <c r="E27" s="42" t="n"/>
@@ -2412,12 +2426,12 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
         </is>
       </c>
       <c r="E28" s="42" t="n"/>
@@ -2443,12 +2457,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
         </is>
       </c>
       <c r="E29" s="42" t="n"/>
@@ -2463,90 +2477,102 @@
       <c r="N29" s="46" t="n"/>
       <c r="O29" s="40" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+        </is>
+      </c>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="43" t="n"/>
+      <c r="I30" s="44" t="n"/>
+      <c r="J30" s="44" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="46" t="n"/>
+      <c r="N30" s="46" t="n"/>
+      <c r="O30" s="40" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>NHẬT KÝ TỰ DO — bất cứ điều gì bạn gặp, kể cả ngoài các chặng trên</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr"/>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr"/>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Đợt</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Vai lúc đó</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Ở màn hình nào / đang làm gì</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Chuyện gì xảy ra</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>Nặng hay nhẹ?</t>
         </is>
       </c>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>Bạn mong nó phải thế nào</t>
         </is>
       </c>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="49" t="n"/>
-      <c r="G33" s="49" t="n"/>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="49" t="n"/>
-      <c r="J33" s="49" t="n"/>
-      <c r="K33" s="49" t="n"/>
-      <c r="L33" s="49" t="n"/>
-      <c r="M33" s="49" t="n"/>
-      <c r="N33" s="49" t="n"/>
-      <c r="O33" s="49" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="49" t="n"/>
       <c r="C34" s="49" t="n"/>
@@ -2565,7 +2591,7 @@
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" s="49" t="n"/>
       <c r="C35" s="49" t="n"/>
@@ -2584,7 +2610,7 @@
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="49" t="n"/>
       <c r="C36" s="49" t="n"/>
@@ -2603,7 +2629,7 @@
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="49" t="n"/>
       <c r="C37" s="49" t="n"/>
@@ -2622,7 +2648,7 @@
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="49" t="n"/>
       <c r="C38" s="49" t="n"/>
@@ -2641,7 +2667,7 @@
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="49" t="n"/>
       <c r="C39" s="49" t="n"/>
@@ -2660,7 +2686,7 @@
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" s="49" t="n"/>
       <c r="C40" s="49" t="n"/>
@@ -2679,7 +2705,7 @@
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" s="49" t="n"/>
       <c r="C41" s="49" t="n"/>
@@ -2698,7 +2724,7 @@
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B42" s="49" t="n"/>
       <c r="C42" s="49" t="n"/>
@@ -2717,7 +2743,7 @@
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="49" t="n"/>
@@ -2736,7 +2762,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="49" t="n"/>
       <c r="C44" s="49" t="n"/>
@@ -2753,52 +2779,50 @@
       <c r="N44" s="49" t="n"/>
       <c r="O44" s="49" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+      <c r="M45" s="49" t="n"/>
+      <c r="N45" s="49" t="n"/>
+      <c r="O45" s="49" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>NÓI THẬT GIÙM CHÚNG TÔI (trả lời sau ĐỢT 1; đợt sau có gì đổi ý thì ghi thêm)</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="50" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Điều bạn THÍCH nhất khi dùng app:</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="50" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48" ht="50" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
+          <t>Điều bạn THÍCH nhất khi dùng app:</t>
         </is>
       </c>
       <c r="B48" s="21" t="n"/>
@@ -2819,7 +2843,7 @@
     <row r="49" ht="50" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
+          <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
         </is>
       </c>
       <c r="B49" s="21" t="n"/>
@@ -2840,7 +2864,7 @@
     <row r="50" ht="50" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
+          <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
         </is>
       </c>
       <c r="B50" s="21" t="n"/>
@@ -2861,7 +2885,7 @@
     <row r="51" ht="50" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
+          <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
         </is>
       </c>
       <c r="B51" s="21" t="n"/>
@@ -2882,7 +2906,7 @@
     <row r="52" ht="50" customHeight="1">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
+          <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
         </is>
       </c>
       <c r="B52" s="21" t="n"/>
@@ -2903,7 +2927,7 @@
     <row r="53" ht="50" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
+          <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
         </is>
       </c>
       <c r="B53" s="21" t="n"/>
@@ -2924,7 +2948,7 @@
     <row r="54" ht="50" customHeight="1">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
+          <t>HỌC LIỆU: bạn muốn mỗi bài kèm sẵn thứ gì trước khi em làm câu hỏi — video ngắn, slide, phiếu in ra làm, đề cương, hay không cần gì? Nguồn lấy từ đâu: cô tự soạn, kho của trường, hay link ngoài (YouTube/Drive)?</t>
         </is>
       </c>
       <c r="B54" s="21" t="n"/>
@@ -2942,34 +2966,77 @@
       <c r="N54" s="21" t="n"/>
       <c r="O54" s="21" t="n"/>
     </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="50" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="21" t="n"/>
+      <c r="L55" s="21" t="n"/>
+      <c r="M55" s="21" t="n"/>
+      <c r="N55" s="21" t="n"/>
+      <c r="O55" s="21" t="n"/>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="50" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="21" t="n"/>
+      <c r="I56" s="21" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="21" t="n"/>
+      <c r="L56" s="21" t="n"/>
+      <c r="M56" s="21" t="n"/>
+      <c r="N56" s="21" t="n"/>
+      <c r="O56" s="21" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="70">
     <mergeCell ref="E53:O53"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="K34:O34"/>
-    <mergeCell ref="E47:O47"/>
+    <mergeCell ref="E45:H45"/>
     <mergeCell ref="E50:O50"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="K33:O33"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E55:O55"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="K36:O36"/>
     <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="K45:O45"/>
     <mergeCell ref="E52:O52"/>
     <mergeCell ref="E37:H37"/>
     <mergeCell ref="E48:O48"/>
     <mergeCell ref="K35:O35"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="E51:O51"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="E43:H43"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A47:O47"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="K32:O32"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="K41:O41"/>
     <mergeCell ref="K44:O44"/>
@@ -2981,10 +3048,10 @@
     <mergeCell ref="K40:O40"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="E39:H39"/>
     <mergeCell ref="K43:O43"/>
     <mergeCell ref="E35:H35"/>
-    <mergeCell ref="A19:O19"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="E38:H38"/>
@@ -2992,38 +3059,39 @@
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="K42:O42"/>
     <mergeCell ref="E49:O49"/>
-    <mergeCell ref="A31:O31"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="K39:O39"/>
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="E40:H40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="E34:H34"/>
     <mergeCell ref="E54:O54"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="K38:O38"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="K37:O37"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="E36:H36"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E20 E21 E22 E24 E25 E26 E27 E28 E29 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G20 G21 G22 G24 G25 G26 G27 G28 G29 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I20 I21 I22 I24 I25 I26 I27 I28 I29 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K20 K21 K22 K24 K25 K26 K27 K28 K29 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M20 M21 M22 M24 M25 M26 M27 M28 M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E21 E22 E23 E25 E26 E27 E28 E29 E30 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G25 G26 G27 G28 G29 G30 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I21 I22 I23 I25 I26 I27 I28 I29 I30 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K21 K22 K23 K25 K26 K27 K28 K29 K30 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M21 M22 M23 M25 M26 M27 M28 M29 M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng như mô tả,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O20 O21 O22 O24 O25 O26 O27 O28 O29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O21 O22 O23 O25 O26 O27 O28 O29 O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chặn hẳn không đi tiếp được,Khó chịu nhưng vẫn làm được,Góp ý cho đẹp hơn"</formula1>
     </dataValidation>
-    <dataValidation sqref="B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3037,7 +3105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3323,7 +3391,7 @@
       <c r="N8" s="46" t="n"/>
       <c r="O8" s="40" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>4</v>
       </c>
@@ -3334,12 +3402,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
+          <t>Hiện tại trường CHƯA nạp học liệu nào nên chỗ này KHÔNG hiện gì, vào thẳng câu hỏi luôn — đúng hiện trạng, không phải lỗi. Nếu bạn LẠI thấy một mục 'Bài học' kèm danh sách tài liệu thì mở thử một mục và ghi lại cảm nhận.</t>
         </is>
       </c>
       <c r="E9" s="42" t="n"/>
@@ -3365,12 +3433,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
+          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
         </is>
       </c>
       <c r="E10" s="42" t="n"/>
@@ -3385,7 +3453,7 @@
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="40" t="n"/>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="41" t="n">
         <v>6</v>
       </c>
@@ -3396,12 +3464,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
+          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
         </is>
       </c>
       <c r="E11" s="42" t="n"/>
@@ -3416,7 +3484,7 @@
       <c r="N11" s="46" t="n"/>
       <c r="O11" s="40" t="n"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="41" t="n">
         <v>7</v>
       </c>
@@ -3427,12 +3495,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
+          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
         </is>
       </c>
       <c r="E12" s="42" t="n"/>
@@ -3447,7 +3515,7 @@
       <c r="N12" s="46" t="n"/>
       <c r="O12" s="40" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="41" t="n">
         <v>8</v>
       </c>
@@ -3458,12 +3526,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
+          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
         </is>
       </c>
       <c r="E13" s="42" t="n"/>
@@ -3489,12 +3557,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
+          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
         </is>
       </c>
       <c r="E14" s="42" t="n"/>
@@ -3520,12 +3588,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
         </is>
       </c>
       <c r="E15" s="42" t="n"/>
@@ -3551,12 +3619,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
+          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
         </is>
       </c>
       <c r="E16" s="42" t="n"/>
@@ -3582,12 +3650,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Quay ra chọn môn, thử TIẾNG ANH 10 vài câu.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Cũng có lộ trình riêng. Câu tiếng Anh có dạng nối cột / sắp xếp / điền — thao tác bằng chạm hoặc kéo thả.</t>
+          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
       <c r="E17" s="42" t="n"/>
@@ -3602,7 +3670,7 @@
       <c r="N17" s="46" t="n"/>
       <c r="O17" s="40" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="41" t="n">
         <v>13</v>
       </c>
@@ -3613,12 +3681,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
         </is>
       </c>
       <c r="E18" s="42" t="n"/>
@@ -3633,59 +3701,59 @@
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="40" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Học Sinh</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="43" t="n"/>
+      <c r="I19" s="44" t="n"/>
+      <c r="J19" s="44" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="40" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>VAI PHỤ HUYNH</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Phụ Huynh</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
-        </is>
-      </c>
-      <c r="E20" s="42" t="n"/>
-      <c r="F20" s="42" t="n"/>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="44" t="n"/>
-      <c r="J20" s="44" t="n"/>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="n"/>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="46" t="n"/>
-      <c r="O20" s="40" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="41" t="n">
         <v>15</v>
       </c>
@@ -3696,12 +3764,12 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
+          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
         </is>
       </c>
       <c r="E21" s="42" t="n"/>
@@ -3716,7 +3784,7 @@
       <c r="N21" s="46" t="n"/>
       <c r="O21" s="40" t="n"/>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="41" t="n">
         <v>16</v>
       </c>
@@ -3727,12 +3795,12 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
         </is>
       </c>
       <c r="E22" s="42" t="n"/>
@@ -3747,57 +3815,57 @@
       <c r="N22" s="46" t="n"/>
       <c r="O22" s="40" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="48" t="inlineStr">
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Phụ Huynh</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="43" t="n"/>
+      <c r="H23" s="43" t="n"/>
+      <c r="I23" s="44" t="n"/>
+      <c r="J23" s="44" t="n"/>
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="45" t="n"/>
+      <c r="M23" s="46" t="n"/>
+      <c r="N23" s="46" t="n"/>
+      <c r="O23" s="40" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>VAI GIÁO VIÊN</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="41" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Giáo Viên</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
-        </is>
-      </c>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
-      <c r="G24" s="43" t="n"/>
-      <c r="H24" s="43" t="n"/>
-      <c r="I24" s="44" t="n"/>
-      <c r="J24" s="44" t="n"/>
-      <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="n"/>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="46" t="n"/>
-      <c r="O24" s="40" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="41" t="n">
@@ -3810,12 +3878,12 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
+          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
         </is>
       </c>
       <c r="E25" s="42" t="n"/>
@@ -3830,7 +3898,7 @@
       <c r="N25" s="46" t="n"/>
       <c r="O25" s="40" t="n"/>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="41" t="n">
         <v>19</v>
       </c>
@@ -3841,12 +3909,12 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
         </is>
       </c>
       <c r="E26" s="42" t="n"/>
@@ -3861,7 +3929,7 @@
       <c r="N26" s="46" t="n"/>
       <c r="O26" s="40" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="41" t="n">
         <v>20</v>
       </c>
@@ -3872,12 +3940,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+          <t>Vào tab CHẤM BÀI.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
+          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
         </is>
       </c>
       <c r="E27" s="42" t="n"/>
@@ -3903,12 +3971,12 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
         </is>
       </c>
       <c r="E28" s="42" t="n"/>
@@ -3934,12 +4002,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
         </is>
       </c>
       <c r="E29" s="42" t="n"/>
@@ -3954,90 +4022,102 @@
       <c r="N29" s="46" t="n"/>
       <c r="O29" s="40" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+        </is>
+      </c>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="43" t="n"/>
+      <c r="I30" s="44" t="n"/>
+      <c r="J30" s="44" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="46" t="n"/>
+      <c r="N30" s="46" t="n"/>
+      <c r="O30" s="40" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>NHẬT KÝ TỰ DO — bất cứ điều gì bạn gặp, kể cả ngoài các chặng trên</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr"/>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr"/>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Đợt</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Vai lúc đó</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Ở màn hình nào / đang làm gì</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Chuyện gì xảy ra</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>Nặng hay nhẹ?</t>
         </is>
       </c>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>Bạn mong nó phải thế nào</t>
         </is>
       </c>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="49" t="n"/>
-      <c r="G33" s="49" t="n"/>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="49" t="n"/>
-      <c r="J33" s="49" t="n"/>
-      <c r="K33" s="49" t="n"/>
-      <c r="L33" s="49" t="n"/>
-      <c r="M33" s="49" t="n"/>
-      <c r="N33" s="49" t="n"/>
-      <c r="O33" s="49" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="49" t="n"/>
       <c r="C34" s="49" t="n"/>
@@ -4056,7 +4136,7 @@
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" s="49" t="n"/>
       <c r="C35" s="49" t="n"/>
@@ -4075,7 +4155,7 @@
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="49" t="n"/>
       <c r="C36" s="49" t="n"/>
@@ -4094,7 +4174,7 @@
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="49" t="n"/>
       <c r="C37" s="49" t="n"/>
@@ -4113,7 +4193,7 @@
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="49" t="n"/>
       <c r="C38" s="49" t="n"/>
@@ -4132,7 +4212,7 @@
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="49" t="n"/>
       <c r="C39" s="49" t="n"/>
@@ -4151,7 +4231,7 @@
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" s="49" t="n"/>
       <c r="C40" s="49" t="n"/>
@@ -4170,7 +4250,7 @@
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" s="49" t="n"/>
       <c r="C41" s="49" t="n"/>
@@ -4189,7 +4269,7 @@
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B42" s="49" t="n"/>
       <c r="C42" s="49" t="n"/>
@@ -4208,7 +4288,7 @@
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="49" t="n"/>
@@ -4227,7 +4307,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="49" t="n"/>
       <c r="C44" s="49" t="n"/>
@@ -4244,52 +4324,50 @@
       <c r="N44" s="49" t="n"/>
       <c r="O44" s="49" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+      <c r="M45" s="49" t="n"/>
+      <c r="N45" s="49" t="n"/>
+      <c r="O45" s="49" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>NÓI THẬT GIÙM CHÚNG TÔI (trả lời sau ĐỢT 1; đợt sau có gì đổi ý thì ghi thêm)</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="50" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Điều bạn THÍCH nhất khi dùng app:</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="50" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48" ht="50" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
+          <t>Điều bạn THÍCH nhất khi dùng app:</t>
         </is>
       </c>
       <c r="B48" s="21" t="n"/>
@@ -4310,7 +4388,7 @@
     <row r="49" ht="50" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
+          <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
         </is>
       </c>
       <c r="B49" s="21" t="n"/>
@@ -4331,7 +4409,7 @@
     <row r="50" ht="50" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
+          <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
         </is>
       </c>
       <c r="B50" s="21" t="n"/>
@@ -4352,7 +4430,7 @@
     <row r="51" ht="50" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
+          <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
         </is>
       </c>
       <c r="B51" s="21" t="n"/>
@@ -4373,7 +4451,7 @@
     <row r="52" ht="50" customHeight="1">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
+          <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
         </is>
       </c>
       <c r="B52" s="21" t="n"/>
@@ -4394,7 +4472,7 @@
     <row r="53" ht="50" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
+          <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
         </is>
       </c>
       <c r="B53" s="21" t="n"/>
@@ -4415,7 +4493,7 @@
     <row r="54" ht="50" customHeight="1">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
+          <t>HỌC LIỆU: bạn muốn mỗi bài kèm sẵn thứ gì trước khi em làm câu hỏi — video ngắn, slide, phiếu in ra làm, đề cương, hay không cần gì? Nguồn lấy từ đâu: cô tự soạn, kho của trường, hay link ngoài (YouTube/Drive)?</t>
         </is>
       </c>
       <c r="B54" s="21" t="n"/>
@@ -4433,34 +4511,77 @@
       <c r="N54" s="21" t="n"/>
       <c r="O54" s="21" t="n"/>
     </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="50" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="21" t="n"/>
+      <c r="L55" s="21" t="n"/>
+      <c r="M55" s="21" t="n"/>
+      <c r="N55" s="21" t="n"/>
+      <c r="O55" s="21" t="n"/>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="50" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="21" t="n"/>
+      <c r="I56" s="21" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="21" t="n"/>
+      <c r="L56" s="21" t="n"/>
+      <c r="M56" s="21" t="n"/>
+      <c r="N56" s="21" t="n"/>
+      <c r="O56" s="21" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="70">
     <mergeCell ref="E53:O53"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="K34:O34"/>
-    <mergeCell ref="E47:O47"/>
+    <mergeCell ref="E45:H45"/>
     <mergeCell ref="E50:O50"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="K33:O33"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E55:O55"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="K36:O36"/>
     <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="K45:O45"/>
     <mergeCell ref="E52:O52"/>
     <mergeCell ref="E37:H37"/>
     <mergeCell ref="E48:O48"/>
     <mergeCell ref="K35:O35"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="E51:O51"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="E43:H43"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A47:O47"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="K32:O32"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="K41:O41"/>
     <mergeCell ref="K44:O44"/>
@@ -4472,10 +4593,10 @@
     <mergeCell ref="K40:O40"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="E39:H39"/>
     <mergeCell ref="K43:O43"/>
     <mergeCell ref="E35:H35"/>
-    <mergeCell ref="A19:O19"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="E38:H38"/>
@@ -4483,38 +4604,39 @@
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="K42:O42"/>
     <mergeCell ref="E49:O49"/>
-    <mergeCell ref="A31:O31"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="K39:O39"/>
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="E40:H40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="E34:H34"/>
     <mergeCell ref="E54:O54"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="K38:O38"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="K37:O37"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="E36:H36"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E20 E21 E22 E24 E25 E26 E27 E28 E29 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G20 G21 G22 G24 G25 G26 G27 G28 G29 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I20 I21 I22 I24 I25 I26 I27 I28 I29 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K20 K21 K22 K24 K25 K26 K27 K28 K29 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M20 M21 M22 M24 M25 M26 M27 M28 M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E21 E22 E23 E25 E26 E27 E28 E29 E30 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G25 G26 G27 G28 G29 G30 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I21 I22 I23 I25 I26 I27 I28 I29 I30 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K21 K22 K23 K25 K26 K27 K28 K29 K30 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M21 M22 M23 M25 M26 M27 M28 M29 M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng như mô tả,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O20 O21 O22 O24 O25 O26 O27 O28 O29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O21 O22 O23 O25 O26 O27 O28 O29 O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chặn hẳn không đi tiếp được,Khó chịu nhưng vẫn làm được,Góp ý cho đẹp hơn"</formula1>
     </dataValidation>
-    <dataValidation sqref="B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4528,7 +4650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4551,7 +4673,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Người thử 3 — giáo viên Tiếng Anh 10A1</t>
+          <t>Người thử 3 — giáo viên bộ môn lớp 10A1</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4814,7 +4936,7 @@
       <c r="N8" s="46" t="n"/>
       <c r="O8" s="40" t="n"/>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>4</v>
       </c>
@@ -4825,12 +4947,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
+          <t>Hiện tại trường CHƯA nạp học liệu nào nên chỗ này KHÔNG hiện gì, vào thẳng câu hỏi luôn — đúng hiện trạng, không phải lỗi. Nếu bạn LẠI thấy một mục 'Bài học' kèm danh sách tài liệu thì mở thử một mục và ghi lại cảm nhận.</t>
         </is>
       </c>
       <c r="E9" s="42" t="n"/>
@@ -4856,12 +4978,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
+          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
         </is>
       </c>
       <c r="E10" s="42" t="n"/>
@@ -4876,7 +4998,7 @@
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="40" t="n"/>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="41" t="n">
         <v>6</v>
       </c>
@@ -4887,12 +5009,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
+          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
         </is>
       </c>
       <c r="E11" s="42" t="n"/>
@@ -4907,7 +5029,7 @@
       <c r="N11" s="46" t="n"/>
       <c r="O11" s="40" t="n"/>
     </row>
-    <row r="12" ht="60" customHeight="1">
+    <row r="12" ht="48" customHeight="1">
       <c r="A12" s="41" t="n">
         <v>7</v>
       </c>
@@ -4918,12 +5040,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
+          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
         </is>
       </c>
       <c r="E12" s="42" t="n"/>
@@ -4938,7 +5060,7 @@
       <c r="N12" s="46" t="n"/>
       <c r="O12" s="40" t="n"/>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="41" t="n">
         <v>8</v>
       </c>
@@ -4949,12 +5071,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
+          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
         </is>
       </c>
       <c r="E13" s="42" t="n"/>
@@ -4980,12 +5102,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
+          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
         </is>
       </c>
       <c r="E14" s="42" t="n"/>
@@ -5011,12 +5133,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
         </is>
       </c>
       <c r="E15" s="42" t="n"/>
@@ -5042,12 +5164,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
+          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
         </is>
       </c>
       <c r="E16" s="42" t="n"/>
@@ -5073,12 +5195,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Quay ra chọn môn, thử TIẾNG ANH 10 vài câu.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Cũng có lộ trình riêng. Câu tiếng Anh có dạng nối cột / sắp xếp / điền — thao tác bằng chạm hoặc kéo thả.</t>
+          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
       <c r="E17" s="42" t="n"/>
@@ -5093,7 +5215,7 @@
       <c r="N17" s="46" t="n"/>
       <c r="O17" s="40" t="n"/>
     </row>
-    <row r="18" ht="30" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="41" t="n">
         <v>13</v>
       </c>
@@ -5104,12 +5226,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
         </is>
       </c>
       <c r="E18" s="42" t="n"/>
@@ -5124,59 +5246,59 @@
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="40" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="47" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="41" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Học Sinh</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+        </is>
+      </c>
+      <c r="E19" s="42" t="n"/>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="43" t="n"/>
+      <c r="H19" s="43" t="n"/>
+      <c r="I19" s="44" t="n"/>
+      <c r="J19" s="44" t="n"/>
+      <c r="K19" s="45" t="n"/>
+      <c r="L19" s="45" t="n"/>
+      <c r="M19" s="46" t="n"/>
+      <c r="N19" s="46" t="n"/>
+      <c r="O19" s="40" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="47" t="inlineStr">
         <is>
           <t>VAI PHỤ HUYNH</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
-      <c r="O19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="41" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Phụ Huynh</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
-        </is>
-      </c>
-      <c r="E20" s="42" t="n"/>
-      <c r="F20" s="42" t="n"/>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="44" t="n"/>
-      <c r="J20" s="44" t="n"/>
-      <c r="K20" s="45" t="n"/>
-      <c r="L20" s="45" t="n"/>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="46" t="n"/>
-      <c r="O20" s="40" t="n"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
+      <c r="J20" s="8" t="n"/>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+      <c r="M20" s="8" t="n"/>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+    </row>
+    <row r="21" ht="48" customHeight="1">
       <c r="A21" s="41" t="n">
         <v>15</v>
       </c>
@@ -5187,12 +5309,12 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
+          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
         </is>
       </c>
       <c r="E21" s="42" t="n"/>
@@ -5207,7 +5329,7 @@
       <c r="N21" s="46" t="n"/>
       <c r="O21" s="40" t="n"/>
     </row>
-    <row r="22" ht="48" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="41" t="n">
         <v>16</v>
       </c>
@@ -5218,12 +5340,12 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
         </is>
       </c>
       <c r="E22" s="42" t="n"/>
@@ -5238,57 +5360,57 @@
       <c r="N22" s="46" t="n"/>
       <c r="O22" s="40" t="n"/>
     </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="48" t="inlineStr">
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="41" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Phụ Huynh</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="43" t="n"/>
+      <c r="H23" s="43" t="n"/>
+      <c r="I23" s="44" t="n"/>
+      <c r="J23" s="44" t="n"/>
+      <c r="K23" s="45" t="n"/>
+      <c r="L23" s="45" t="n"/>
+      <c r="M23" s="46" t="n"/>
+      <c r="N23" s="46" t="n"/>
+      <c r="O23" s="40" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="48" t="inlineStr">
         <is>
           <t>VAI GIÁO VIÊN</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="41" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Giáo Viên</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
-        </is>
-      </c>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
-      <c r="G24" s="43" t="n"/>
-      <c r="H24" s="43" t="n"/>
-      <c r="I24" s="44" t="n"/>
-      <c r="J24" s="44" t="n"/>
-      <c r="K24" s="45" t="n"/>
-      <c r="L24" s="45" t="n"/>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="46" t="n"/>
-      <c r="O24" s="40" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="18" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="41" t="n">
@@ -5301,12 +5423,12 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
+          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
         </is>
       </c>
       <c r="E25" s="42" t="n"/>
@@ -5321,7 +5443,7 @@
       <c r="N25" s="46" t="n"/>
       <c r="O25" s="40" t="n"/>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="41" t="n">
         <v>19</v>
       </c>
@@ -5332,12 +5454,12 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
         </is>
       </c>
       <c r="E26" s="42" t="n"/>
@@ -5352,7 +5474,7 @@
       <c r="N26" s="46" t="n"/>
       <c r="O26" s="40" t="n"/>
     </row>
-    <row r="27" ht="36" customHeight="1">
+    <row r="27" ht="48" customHeight="1">
       <c r="A27" s="41" t="n">
         <v>20</v>
       </c>
@@ -5363,12 +5485,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+          <t>Vào tab CHẤM BÀI.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
+          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
         </is>
       </c>
       <c r="E27" s="42" t="n"/>
@@ -5394,12 +5516,12 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
         </is>
       </c>
       <c r="E28" s="42" t="n"/>
@@ -5425,12 +5547,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
         </is>
       </c>
       <c r="E29" s="42" t="n"/>
@@ -5445,90 +5567,102 @@
       <c r="N29" s="46" t="n"/>
       <c r="O29" s="40" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+        </is>
+      </c>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
+      <c r="G30" s="43" t="n"/>
+      <c r="H30" s="43" t="n"/>
+      <c r="I30" s="44" t="n"/>
+      <c r="J30" s="44" t="n"/>
+      <c r="K30" s="45" t="n"/>
+      <c r="L30" s="45" t="n"/>
+      <c r="M30" s="46" t="n"/>
+      <c r="N30" s="46" t="n"/>
+      <c r="O30" s="40" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>NHẬT KÝ TỰ DO — bất cứ điều gì bạn gặp, kể cả ngoài các chặng trên</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr"/>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr"/>
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Đợt</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Vai lúc đó</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Ở màn hình nào / đang làm gì</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E33" s="12" t="inlineStr">
         <is>
           <t>Chuyện gì xảy ra</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="12" t="inlineStr">
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="12" t="inlineStr">
         <is>
           <t>Nặng hay nhẹ?</t>
         </is>
       </c>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="12" t="inlineStr">
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="12" t="inlineStr">
         <is>
           <t>Bạn mong nó phải thế nào</t>
         </is>
       </c>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="49" t="n"/>
-      <c r="C33" s="49" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="49" t="n"/>
-      <c r="G33" s="49" t="n"/>
-      <c r="H33" s="49" t="n"/>
-      <c r="I33" s="49" t="n"/>
-      <c r="J33" s="49" t="n"/>
-      <c r="K33" s="49" t="n"/>
-      <c r="L33" s="49" t="n"/>
-      <c r="M33" s="49" t="n"/>
-      <c r="N33" s="49" t="n"/>
-      <c r="O33" s="49" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="49" t="n"/>
       <c r="C34" s="49" t="n"/>
@@ -5547,7 +5681,7 @@
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B35" s="49" t="n"/>
       <c r="C35" s="49" t="n"/>
@@ -5566,7 +5700,7 @@
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="49" t="n"/>
       <c r="C36" s="49" t="n"/>
@@ -5585,7 +5719,7 @@
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" s="49" t="n"/>
       <c r="C37" s="49" t="n"/>
@@ -5604,7 +5738,7 @@
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B38" s="49" t="n"/>
       <c r="C38" s="49" t="n"/>
@@ -5623,7 +5757,7 @@
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B39" s="49" t="n"/>
       <c r="C39" s="49" t="n"/>
@@ -5642,7 +5776,7 @@
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B40" s="49" t="n"/>
       <c r="C40" s="49" t="n"/>
@@ -5661,7 +5795,7 @@
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B41" s="49" t="n"/>
       <c r="C41" s="49" t="n"/>
@@ -5680,7 +5814,7 @@
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B42" s="49" t="n"/>
       <c r="C42" s="49" t="n"/>
@@ -5699,7 +5833,7 @@
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="49" t="n"/>
@@ -5718,7 +5852,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" s="49" t="n"/>
       <c r="C44" s="49" t="n"/>
@@ -5735,52 +5869,50 @@
       <c r="N44" s="49" t="n"/>
       <c r="O44" s="49" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B45" s="49" t="n"/>
+      <c r="C45" s="49" t="n"/>
+      <c r="D45" s="49" t="n"/>
+      <c r="E45" s="49" t="n"/>
+      <c r="F45" s="49" t="n"/>
+      <c r="G45" s="49" t="n"/>
+      <c r="H45" s="49" t="n"/>
+      <c r="I45" s="49" t="n"/>
+      <c r="J45" s="49" t="n"/>
+      <c r="K45" s="49" t="n"/>
+      <c r="L45" s="49" t="n"/>
+      <c r="M45" s="49" t="n"/>
+      <c r="N45" s="49" t="n"/>
+      <c r="O45" s="49" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>NÓI THẬT GIÙM CHÚNG TÔI (trả lời sau ĐỢT 1; đợt sau có gì đổi ý thì ghi thêm)</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
-      <c r="G46" s="2" t="n"/>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-    </row>
-    <row r="47" ht="50" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Điều bạn THÍCH nhất khi dùng app:</t>
-        </is>
-      </c>
-      <c r="B47" s="21" t="n"/>
-      <c r="C47" s="21" t="n"/>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="50" t="n"/>
-      <c r="F47" s="21" t="n"/>
-      <c r="G47" s="21" t="n"/>
-      <c r="H47" s="21" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="21" t="n"/>
-      <c r="K47" s="21" t="n"/>
-      <c r="L47" s="21" t="n"/>
-      <c r="M47" s="21" t="n"/>
-      <c r="N47" s="21" t="n"/>
-      <c r="O47" s="21" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
     </row>
     <row r="48" ht="50" customHeight="1">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
+          <t>Điều bạn THÍCH nhất khi dùng app:</t>
         </is>
       </c>
       <c r="B48" s="21" t="n"/>
@@ -5801,7 +5933,7 @@
     <row r="49" ht="50" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
+          <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
         </is>
       </c>
       <c r="B49" s="21" t="n"/>
@@ -5822,7 +5954,7 @@
     <row r="50" ht="50" customHeight="1">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
+          <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
         </is>
       </c>
       <c r="B50" s="21" t="n"/>
@@ -5843,7 +5975,7 @@
     <row r="51" ht="50" customHeight="1">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
+          <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
         </is>
       </c>
       <c r="B51" s="21" t="n"/>
@@ -5864,7 +5996,7 @@
     <row r="52" ht="50" customHeight="1">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
+          <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
         </is>
       </c>
       <c r="B52" s="21" t="n"/>
@@ -5885,7 +6017,7 @@
     <row r="53" ht="50" customHeight="1">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
+          <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
         </is>
       </c>
       <c r="B53" s="21" t="n"/>
@@ -5906,7 +6038,7 @@
     <row r="54" ht="50" customHeight="1">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
+          <t>HỌC LIỆU: bạn muốn mỗi bài kèm sẵn thứ gì trước khi em làm câu hỏi — video ngắn, slide, phiếu in ra làm, đề cương, hay không cần gì? Nguồn lấy từ đâu: cô tự soạn, kho của trường, hay link ngoài (YouTube/Drive)?</t>
         </is>
       </c>
       <c r="B54" s="21" t="n"/>
@@ -5924,34 +6056,77 @@
       <c r="N54" s="21" t="n"/>
       <c r="O54" s="21" t="n"/>
     </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="50" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="21" t="n"/>
+      <c r="L55" s="21" t="n"/>
+      <c r="M55" s="21" t="n"/>
+      <c r="N55" s="21" t="n"/>
+      <c r="O55" s="21" t="n"/>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="50" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="21" t="n"/>
+      <c r="I56" s="21" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="21" t="n"/>
+      <c r="L56" s="21" t="n"/>
+      <c r="M56" s="21" t="n"/>
+      <c r="N56" s="21" t="n"/>
+      <c r="O56" s="21" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="70">
     <mergeCell ref="E53:O53"/>
     <mergeCell ref="I34:J34"/>
     <mergeCell ref="K34:O34"/>
-    <mergeCell ref="E47:O47"/>
+    <mergeCell ref="E45:H45"/>
     <mergeCell ref="E50:O50"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="K33:O33"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A46:O46"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="E55:O55"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="K36:O36"/>
     <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="K45:O45"/>
     <mergeCell ref="E52:O52"/>
     <mergeCell ref="E37:H37"/>
     <mergeCell ref="E48:O48"/>
     <mergeCell ref="K35:O35"/>
     <mergeCell ref="A2:O2"/>
     <mergeCell ref="E51:O51"/>
-    <mergeCell ref="I32:J32"/>
     <mergeCell ref="E43:H43"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="I41:J41"/>
+    <mergeCell ref="A47:O47"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A23:O23"/>
-    <mergeCell ref="K32:O32"/>
+    <mergeCell ref="A32:O32"/>
     <mergeCell ref="I37:J37"/>
     <mergeCell ref="K41:O41"/>
     <mergeCell ref="K44:O44"/>
@@ -5963,10 +6138,10 @@
     <mergeCell ref="K40:O40"/>
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I43:J43"/>
+    <mergeCell ref="A20:O20"/>
     <mergeCell ref="E39:H39"/>
     <mergeCell ref="K43:O43"/>
     <mergeCell ref="E35:H35"/>
-    <mergeCell ref="A19:O19"/>
     <mergeCell ref="I42:J42"/>
     <mergeCell ref="I33:J33"/>
     <mergeCell ref="E38:H38"/>
@@ -5974,38 +6149,39 @@
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="K42:O42"/>
     <mergeCell ref="E49:O49"/>
-    <mergeCell ref="A31:O31"/>
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="I39:J39"/>
     <mergeCell ref="K39:O39"/>
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="E40:H40"/>
+    <mergeCell ref="A24:O24"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="I38:J38"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="E34:H34"/>
     <mergeCell ref="E54:O54"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="K38:O38"/>
+    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="K37:O37"/>
-    <mergeCell ref="A47:D47"/>
     <mergeCell ref="I40:J40"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="E36:H36"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E20 E21 E22 E24 E25 E26 E27 E28 E29 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G20 G21 G22 G24 G25 G26 G27 G28 G29 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I20 I21 I22 I24 I25 I26 I27 I28 I29 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K20 K21 K22 K24 K25 K26 K27 K28 K29 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M20 M21 M22 M24 M25 M26 M27 M28 M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E21 E22 E23 E25 E26 E27 E28 E29 E30 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G25 G26 G27 G28 G29 G30 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I21 I22 I23 I25 I26 I27 I28 I29 I30 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K21 K22 K23 K25 K26 K27 K28 K29 K30 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M21 M22 M23 M25 M26 M27 M28 M29 M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng như mô tả,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O20 O21 O22 O24 O25 O26 O27 O28 O29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O21 O22 O23 O25 O26 O27 O28 O29 O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chặn hẳn không đi tiếp được,Khó chịu nhưng vẫn làm được,Góp ý cho đẹp hơn"</formula1>
     </dataValidation>
-    <dataValidation sqref="B33 B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -53338,7 +53514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -53542,7 +53718,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="41" t="n">
         <v>4</v>
       </c>
@@ -53553,7 +53729,7 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
         </is>
       </c>
       <c r="D7" s="58">
@@ -53592,7 +53768,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D8" s="58">
@@ -53631,7 +53807,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D9" s="58">
@@ -53670,7 +53846,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D10" s="58">
@@ -53709,7 +53885,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D11" s="58">
@@ -53748,7 +53924,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D12" s="58">
@@ -53787,7 +53963,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D13" s="58">
@@ -53826,7 +54002,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
         </is>
       </c>
       <c r="D14" s="58">
@@ -53865,7 +54041,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Quay ra chọn môn, thử TIẾNG ANH 10 vài câu.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D15" s="58">
@@ -53904,7 +54080,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D16" s="58">
@@ -53938,36 +54114,36 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
         </is>
       </c>
       <c r="D17" s="58">
-        <f>COUNTIF('Người thử 1'!E20,"Một phần")+COUNTIF('Người thử 1'!E20,"Không đúng")+COUNTIF('Người thử 2'!E20,"Một phần")+COUNTIF('Người thử 2'!E20,"Không đúng")+COUNTIF('Người thử 3'!E20,"Một phần")+COUNTIF('Người thử 3'!E20,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E19,"Một phần")+COUNTIF('Người thử 1'!E19,"Không đúng")+COUNTIF('Người thử 2'!E19,"Một phần")+COUNTIF('Người thử 2'!E19,"Không đúng")+COUNTIF('Người thử 3'!E19,"Một phần")+COUNTIF('Người thử 3'!E19,"Không đúng")</f>
         <v/>
       </c>
       <c r="E17" s="59">
-        <f>COUNTIF('Người thử 1'!G20,"Một phần")+COUNTIF('Người thử 1'!G20,"Không đúng")+COUNTIF('Người thử 2'!G20,"Một phần")+COUNTIF('Người thử 2'!G20,"Không đúng")+COUNTIF('Người thử 3'!G20,"Một phần")+COUNTIF('Người thử 3'!G20,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G19,"Một phần")+COUNTIF('Người thử 1'!G19,"Không đúng")+COUNTIF('Người thử 2'!G19,"Một phần")+COUNTIF('Người thử 2'!G19,"Không đúng")+COUNTIF('Người thử 3'!G19,"Một phần")+COUNTIF('Người thử 3'!G19,"Không đúng")</f>
         <v/>
       </c>
       <c r="F17" s="60">
-        <f>COUNTIF('Người thử 1'!I20,"Một phần")+COUNTIF('Người thử 1'!I20,"Không đúng")+COUNTIF('Người thử 2'!I20,"Một phần")+COUNTIF('Người thử 2'!I20,"Không đúng")+COUNTIF('Người thử 3'!I20,"Một phần")+COUNTIF('Người thử 3'!I20,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I19,"Một phần")+COUNTIF('Người thử 1'!I19,"Không đúng")+COUNTIF('Người thử 2'!I19,"Một phần")+COUNTIF('Người thử 2'!I19,"Không đúng")+COUNTIF('Người thử 3'!I19,"Một phần")+COUNTIF('Người thử 3'!I19,"Không đúng")</f>
         <v/>
       </c>
       <c r="G17" s="61">
-        <f>COUNTIF('Người thử 1'!K20,"Một phần")+COUNTIF('Người thử 1'!K20,"Không đúng")+COUNTIF('Người thử 2'!K20,"Một phần")+COUNTIF('Người thử 2'!K20,"Không đúng")+COUNTIF('Người thử 3'!K20,"Một phần")+COUNTIF('Người thử 3'!K20,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K19,"Một phần")+COUNTIF('Người thử 1'!K19,"Không đúng")+COUNTIF('Người thử 2'!K19,"Một phần")+COUNTIF('Người thử 2'!K19,"Không đúng")+COUNTIF('Người thử 3'!K19,"Một phần")+COUNTIF('Người thử 3'!K19,"Không đúng")</f>
         <v/>
       </c>
       <c r="H17" s="62">
-        <f>COUNTIF('Người thử 1'!M20,"Một phần")+COUNTIF('Người thử 1'!M20,"Không đúng")+COUNTIF('Người thử 2'!M20,"Một phần")+COUNTIF('Người thử 2'!M20,"Không đúng")+COUNTIF('Người thử 3'!M20,"Một phần")+COUNTIF('Người thử 3'!M20,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M19,"Một phần")+COUNTIF('Người thử 1'!M19,"Không đúng")+COUNTIF('Người thử 2'!M19,"Một phần")+COUNTIF('Người thử 2'!M19,"Không đúng")+COUNTIF('Người thử 3'!M19,"Một phần")+COUNTIF('Người thử 3'!M19,"Không đúng")</f>
         <v/>
       </c>
       <c r="I17" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O20,'Người thử 2'!O20,'Người thử 3'!O20),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O19,'Người thử 2'!O19,'Người thử 3'!O19),1),"")</f>
         <v/>
       </c>
     </row>
@@ -53982,7 +54158,7 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D18" s="58">
@@ -54021,7 +54197,7 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D19" s="58">
@@ -54055,36 +54231,36 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
         </is>
       </c>
       <c r="D20" s="58">
-        <f>COUNTIF('Người thử 1'!E24,"Một phần")+COUNTIF('Người thử 1'!E24,"Không đúng")+COUNTIF('Người thử 2'!E24,"Một phần")+COUNTIF('Người thử 2'!E24,"Không đúng")+COUNTIF('Người thử 3'!E24,"Một phần")+COUNTIF('Người thử 3'!E24,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E23,"Một phần")+COUNTIF('Người thử 1'!E23,"Không đúng")+COUNTIF('Người thử 2'!E23,"Một phần")+COUNTIF('Người thử 2'!E23,"Không đúng")+COUNTIF('Người thử 3'!E23,"Một phần")+COUNTIF('Người thử 3'!E23,"Không đúng")</f>
         <v/>
       </c>
       <c r="E20" s="59">
-        <f>COUNTIF('Người thử 1'!G24,"Một phần")+COUNTIF('Người thử 1'!G24,"Không đúng")+COUNTIF('Người thử 2'!G24,"Một phần")+COUNTIF('Người thử 2'!G24,"Không đúng")+COUNTIF('Người thử 3'!G24,"Một phần")+COUNTIF('Người thử 3'!G24,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G23,"Một phần")+COUNTIF('Người thử 1'!G23,"Không đúng")+COUNTIF('Người thử 2'!G23,"Một phần")+COUNTIF('Người thử 2'!G23,"Không đúng")+COUNTIF('Người thử 3'!G23,"Một phần")+COUNTIF('Người thử 3'!G23,"Không đúng")</f>
         <v/>
       </c>
       <c r="F20" s="60">
-        <f>COUNTIF('Người thử 1'!I24,"Một phần")+COUNTIF('Người thử 1'!I24,"Không đúng")+COUNTIF('Người thử 2'!I24,"Một phần")+COUNTIF('Người thử 2'!I24,"Không đúng")+COUNTIF('Người thử 3'!I24,"Một phần")+COUNTIF('Người thử 3'!I24,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I23,"Một phần")+COUNTIF('Người thử 1'!I23,"Không đúng")+COUNTIF('Người thử 2'!I23,"Một phần")+COUNTIF('Người thử 2'!I23,"Không đúng")+COUNTIF('Người thử 3'!I23,"Một phần")+COUNTIF('Người thử 3'!I23,"Không đúng")</f>
         <v/>
       </c>
       <c r="G20" s="61">
-        <f>COUNTIF('Người thử 1'!K24,"Một phần")+COUNTIF('Người thử 1'!K24,"Không đúng")+COUNTIF('Người thử 2'!K24,"Một phần")+COUNTIF('Người thử 2'!K24,"Không đúng")+COUNTIF('Người thử 3'!K24,"Một phần")+COUNTIF('Người thử 3'!K24,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K23,"Một phần")+COUNTIF('Người thử 1'!K23,"Không đúng")+COUNTIF('Người thử 2'!K23,"Một phần")+COUNTIF('Người thử 2'!K23,"Không đúng")+COUNTIF('Người thử 3'!K23,"Một phần")+COUNTIF('Người thử 3'!K23,"Không đúng")</f>
         <v/>
       </c>
       <c r="H20" s="62">
-        <f>COUNTIF('Người thử 1'!M24,"Một phần")+COUNTIF('Người thử 1'!M24,"Không đúng")+COUNTIF('Người thử 2'!M24,"Một phần")+COUNTIF('Người thử 2'!M24,"Không đúng")+COUNTIF('Người thử 3'!M24,"Một phần")+COUNTIF('Người thử 3'!M24,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M23,"Một phần")+COUNTIF('Người thử 1'!M23,"Không đúng")+COUNTIF('Người thử 2'!M23,"Một phần")+COUNTIF('Người thử 2'!M23,"Không đúng")+COUNTIF('Người thử 3'!M23,"Một phần")+COUNTIF('Người thử 3'!M23,"Không đúng")</f>
         <v/>
       </c>
       <c r="I20" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O24,'Người thử 2'!O24,'Người thử 3'!O24),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O23,'Người thử 2'!O23,'Người thử 3'!O23),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54099,7 +54275,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D21" s="58">
@@ -54138,7 +54314,7 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D22" s="58">
@@ -54177,7 +54353,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+          <t>Vào tab CHẤM BÀI.</t>
         </is>
       </c>
       <c r="D23" s="58">
@@ -54216,7 +54392,7 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
         </is>
       </c>
       <c r="D24" s="58">
@@ -54255,7 +54431,7 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
         </is>
       </c>
       <c r="D25" s="58">
@@ -54283,324 +54459,341 @@
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="41" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D26" s="58">
+        <f>COUNTIF('Người thử 1'!E30,"Một phần")+COUNTIF('Người thử 1'!E30,"Không đúng")+COUNTIF('Người thử 2'!E30,"Một phần")+COUNTIF('Người thử 2'!E30,"Không đúng")+COUNTIF('Người thử 3'!E30,"Một phần")+COUNTIF('Người thử 3'!E30,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E26" s="59">
+        <f>COUNTIF('Người thử 1'!G30,"Một phần")+COUNTIF('Người thử 1'!G30,"Không đúng")+COUNTIF('Người thử 2'!G30,"Một phần")+COUNTIF('Người thử 2'!G30,"Không đúng")+COUNTIF('Người thử 3'!G30,"Một phần")+COUNTIF('Người thử 3'!G30,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F26" s="60">
+        <f>COUNTIF('Người thử 1'!I30,"Một phần")+COUNTIF('Người thử 1'!I30,"Không đúng")+COUNTIF('Người thử 2'!I30,"Một phần")+COUNTIF('Người thử 2'!I30,"Không đúng")+COUNTIF('Người thử 3'!I30,"Một phần")+COUNTIF('Người thử 3'!I30,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G26" s="61">
+        <f>COUNTIF('Người thử 1'!K30,"Một phần")+COUNTIF('Người thử 1'!K30,"Không đúng")+COUNTIF('Người thử 2'!K30,"Một phần")+COUNTIF('Người thử 2'!K30,"Không đúng")+COUNTIF('Người thử 3'!K30,"Một phần")+COUNTIF('Người thử 3'!K30,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H26" s="62">
+        <f>COUNTIF('Người thử 1'!M30,"Một phần")+COUNTIF('Người thử 1'!M30,"Không đúng")+COUNTIF('Người thử 2'!M30,"Một phần")+COUNTIF('Người thử 2'!M30,"Không đúng")+COUNTIF('Người thử 3'!M30,"Một phần")+COUNTIF('Người thử 3'!M30,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I26" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O30,'Người thử 2'!O30,'Người thử 3'!O30),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>KỊCH BẢN PHỐI HỢP</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
-      <c r="I27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="41" t="n">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>KB1 · Ba em cùng nộp bài</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n"/>
-      <c r="D28" s="58">
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E28" s="59">
+      <c r="E29" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F28" s="60">
+      <c r="F29" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G28" s="61">
+      <c r="G29" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H28" s="62">
+      <c r="H29" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I28" s="21" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="41" t="n">
+      <c r="I29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>KB2 · Chấm chéo, trả bài</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="58">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E29" s="59">
+      <c r="E30" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F29" s="60">
+      <c r="F30" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G29" s="61">
+      <c r="G30" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H29" s="62">
+      <c r="H30" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="41" t="n">
+      <c r="I30" s="21" t="n"/>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>KB3 · Nộp lại sau khi bị trả</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="58">
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E30" s="59">
+      <c r="E31" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F30" s="60">
+      <c r="F31" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G30" s="61">
+      <c r="G31" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H30" s="62">
+      <c r="H31" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I30" s="21" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="41" t="n">
+      <c r="I31" s="21" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>KB4 · Hai giáo viên cùng chấm</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="58">
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E31" s="59">
+      <c r="E32" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F31" s="60">
+      <c r="F32" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G31" s="61">
+      <c r="G32" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H31" s="62">
+      <c r="H32" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I31" s="21" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="41" t="n">
+      <c r="I32" s="21" t="n"/>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>KB5 · Phụ huynh không được thấy con nhà khác</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="58">
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E32" s="59">
+      <c r="E33" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F32" s="60">
+      <c r="F33" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G32" s="61">
+      <c r="G33" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H32" s="62">
+      <c r="H33" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="41" t="n">
+      <c r="I33" s="21" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>KB6 · Bảng xếp hạng có đủ ba em</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="58">
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E33" s="59">
+      <c r="E34" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F33" s="60">
+      <c r="F34" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G33" s="61">
+      <c r="G34" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H33" s="62">
+      <c r="H34" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="41" t="n">
+      <c r="I34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>KB7 · Cùng một bài, tiến độ riêng</t>
         </is>
       </c>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="58">
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E34" s="59">
+      <c r="E35" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F34" s="60">
+      <c r="F35" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G34" s="61">
+      <c r="G35" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H34" s="62">
+      <c r="H35" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="41" t="n">
+      <c r="I35" s="21" t="n"/>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>KB8 · Giáo viên bộ môn vs chủ nhiệm</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="58">
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E35" s="59">
+      <c r="E36" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F35" s="60">
+      <c r="F36" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G35" s="61">
+      <c r="G36" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H35" s="62">
+      <c r="H36" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I35" s="21" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="I36" s="21" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>ĐÃ XONG CHƯA? (ba điều kiện dừng)</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>Còn lỗi CHẶN HẲN chưa xử lý</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="53">
-        <f>COUNTIFS('SỔ LỖI'!$F$7:$F$206,"Chặn hẳn",'SỔ LỖI'!$G$7:$G$206,"&lt;&gt;Đã xong")</f>
-        <v/>
-      </c>
-      <c r="E38" s="63" t="inlineStr">
-        <is>
-          <t>phải = 0</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="n"/>
-      <c r="G38" s="21" t="n"/>
-      <c r="H38" s="21" t="n"/>
-      <c r="I38" s="21" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Dòng sổ lỗi chưa đóng</t>
+          <t>Còn lỗi CHẶN HẲN chưa xử lý</t>
         </is>
       </c>
       <c r="B39" s="21" t="n"/>
       <c r="C39" s="21" t="n"/>
       <c r="D39" s="53">
-        <f>COUNTIF('SỔ LỖI'!$G$7:$G$206,"Mới")+COUNTIF('SỔ LỖI'!$G$7:$G$206,"Đang sửa")+COUNTIF('SỔ LỖI'!$G$7:$G$206,"Đã sửa - chờ kiểm")</f>
+        <f>COUNTIFS('SỔ LỖI'!$F$7:$F$206,"Chặn hẳn",'SỔ LỖI'!$G$7:$G$206,"&lt;&gt;Đã xong")</f>
         <v/>
       </c>
       <c r="E39" s="63" t="inlineStr">
@@ -54616,18 +54809,18 @@
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>Số ô 'chưa ổn' của đợt gần nhất</t>
+          <t>Dòng sổ lỗi chưa đóng</t>
         </is>
       </c>
       <c r="B40" s="21" t="n"/>
       <c r="C40" s="21" t="n"/>
       <c r="D40" s="53">
-        <f>SUM(H4:H25)</f>
+        <f>COUNTIF('SỔ LỖI'!$G$7:$G$206,"Mới")+COUNTIF('SỔ LỖI'!$G$7:$G$206,"Đang sửa")+COUNTIF('SỔ LỖI'!$G$7:$G$206,"Đã sửa - chờ kiểm")</f>
         <v/>
       </c>
       <c r="E40" s="63" t="inlineStr">
         <is>
-          <t>càng gần 0 càng tốt</t>
+          <t>phải = 0</t>
         </is>
       </c>
       <c r="F40" s="21" t="n"/>
@@ -54635,26 +54828,48 @@
       <c r="H40" s="21" t="n"/>
       <c r="I40" s="21" t="n"/>
     </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Số ô 'chưa ổn' của đợt gần nhất</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="53">
+        <f>SUM(H4:H26)</f>
+        <v/>
+      </c>
+      <c r="E41" s="63" t="inlineStr">
+        <is>
+          <t>càng gần 0 càng tốt</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="n"/>
+      <c r="H41" s="21" t="n"/>
+      <c r="I41" s="21" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="E40:I40"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E38:I38"/>
-    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B28:C28"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E41:I41"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="E40:I40"/>
+    <mergeCell ref="A38:I38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Phieu-Trai-Nghiem-Tutor.xlsx
+++ b/docs/Phieu-Trai-Nghiem-Tutor.xlsx
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1303,15 +1303,15 @@
       </c>
       <c r="D17" s="21" t="n"/>
     </row>
-    <row r="18" ht="62" customHeight="1">
+    <row r="18" ht="76" customHeight="1">
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>Học liệu đính kèm bài</t>
+          <t>Kho báu học liệu</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>App có sẵn chỗ gắn HỌC LIỆU vào đầu mỗi bài — slide, podcast, video, phiếu bài tập in ra, flashcard — để em xem/nghe trước khi làm câu hỏi. Học liệu là TỰ HỌC, xem xong không cộng điểm gì, chỉ để hiểu bài. HIỆN TẠI trường CHƯA nạp học liệu nào nên vào bài là thấy câu hỏi luôn, không có mục này — đó là đúng hiện trạng. Phiếu có một câu hỏi riêng để bạn nói muốn mỗi bài kèm sẵn thứ gì.</t>
+          <t>Cạnh một số bàn chân có DẤU CHÂN VÀNG hình hộp quà — đó là kho báu: slide, podcast, video, phiếu bài tập, sơ đồ tư duy, câu đố nhanh… do chính thầy cô của trường đăng lên cho bài đó. Xem kho báu KHÔNG cộng điểm, không tính vào bài — thuần để hiểu bài hơn. Kho báu chia BA MỨC và mỗi lần vào chỉ mở thêm MỘT mức: xem xong mức 1 thì mức 2 mở ra cho lần sau. Cố ý như vậy để em có lý do quay lại bài cũ. Bài nào còn KHOÁ thì kho báu của bài đó cũng khoá (hộp quà xám, có ổ khoá).</t>
         </is>
       </c>
       <c r="D18" s="21" t="n"/>
@@ -1425,54 +1425,62 @@
       </c>
       <c r="D29" s="21" t="n"/>
     </row>
-    <row r="30" ht="48" customHeight="1">
+    <row r="30" ht="62" customHeight="1">
       <c r="B30" s="13" t="inlineStr">
         <is>
+          <t>Học liệu</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Chỗ thầy cô TỰ ĐĂNG tài liệu cho từng bài. Cột trái là toàn bộ 204 bài của môn gom theo chương, mỗi bài hiện đã có mấy học liệu; cột phải chia ba mức. Mỗi mục: đặt tên, chọn mức, chọn kiểu, rồi TẢI TỆP LÊN hoặc DÁN LINK (YouTube, Drive, Google Slides đều được). Nút con mắt bật/tắt cho học sinh thấy — bật nhiều kiểu cho cùng một nội dung thì các em thấy SONG SONG, ai hợp nghe thì nghe, hợp nhìn thì nhìn.</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="n"/>
+    </row>
+    <row r="31" ht="62" customHeight="1">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Học liệu</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Chỗ thầy cô TỰ ĐĂNG tài liệu cho từng bài. Cột trái là toàn bộ 204 bài của môn gom theo chương, mỗi bài hiện đã có mấy học liệu; cột phải chia ba mức. Mỗi mục: đặt tên, chọn mức, chọn kiểu, rồi TẢI TỆP LÊN hoặc DÁN LINK (YouTube, Drive, Google Slides đều được). Nút con mắt bật/tắt cho học sinh thấy — bật nhiều kiểu cho cùng một nội dung thì các em thấy song song, ai hợp nghe thì nghe, hợp nhìn thì nhìn.</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
           <t>Chấm bài</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>Hàng đợi bài tự luận học sinh nộp: bài em gõ, ảnh em chụp, đáp án mẫu để đối chiếu, và nhận xét sơ khảo của máy. Thầy cô bấm Đạt hoặc Chưa đạt kèm lời nhắn; chưa đạt thì bàn chân của em chuyển ĐỎ và em được mời làm lại.</t>
         </is>
       </c>
-      <c r="D30" s="21" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="13" t="inlineStr">
+      <c r="D32" s="21" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>Duyệt &amp; nội dung</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>Chỗ duyệt câu hỏi, học liệu trước khi tới tay học sinh. Nội dung nào cũng phải qua mắt người thật.</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="25" t="inlineStr">
+      <c r="D33" s="21" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>APP CỐ Ý KHÔNG LÀM (đừng báo là lỗi)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>· Không đưa đáp án khi em làm sai — kể cả sai nhiều lần.</t>
-        </is>
-      </c>
-      <c r="C34" s="20" t="n"/>
-      <c r="D34" s="20" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>· Không chấm điểm số 8, 9, 10 kiểu bài kiểm tra. Chỉ có 'đã vững / chưa vững'.</t>
         </is>
       </c>
       <c r="C35" s="20" t="n"/>
@@ -1481,7 +1489,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="19" t="inlineStr">
         <is>
-          <t>· Không xếp hạng theo điểm giỏi-dốt; xếp theo nỗ lực.</t>
+          <t>· Không đưa đáp án khi em làm sai — kể cả sai nhiều lần.</t>
         </is>
       </c>
       <c r="C36" s="20" t="n"/>
@@ -1490,7 +1498,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>· Không cho phụ huynh đọc nội dung con trò chuyện với trợ lý.</t>
+          <t>· Không chấm điểm số 8, 9, 10 kiểu bài kiểm tra. Chỉ có 'đã vững / chưa vững'.</t>
         </is>
       </c>
       <c r="C37" s="20" t="n"/>
@@ -1499,31 +1507,69 @@
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>· Không tự động cho qua bài chỉ vì em làm hết số câu.</t>
+          <t>· Không xếp hạng theo điểm giỏi-dốt; xếp theo nỗ lực.</t>
         </is>
       </c>
       <c r="C38" s="20" t="n"/>
       <c r="D38" s="20" t="n"/>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="B40" s="26" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>· Không cho phụ huynh đọc nội dung con trò chuyện với trợ lý.</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>· Không tự động cho qua bài chỉ vì em làm hết số câu.</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>· Không mở toang cả ba mức kho báu trong một lần — mỗi lượt vào chỉ thêm một mức.</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>· Không mở toang cả ba mức kho báu trong một lần — mỗi lượt chỉ thêm một mức.</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Bạn đang thử một bản CHẠY THỬ. Nó chưa hoàn thiện — đó là lý do có phiếu này. Thấy gì lạ cứ ghi, kể cả khi bạn không chắc đó là lỗi hay do mình chưa quen.</t>
         </is>
       </c>
-      <c r="C40" s="24" t="n"/>
-      <c r="D40" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="37">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B34:D34"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C10:D10"/>
@@ -1533,9 +1579,9 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="B35:D35"/>
@@ -1545,10 +1591,12 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1560,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1846,7 +1894,7 @@
       <c r="N8" s="46" t="n"/>
       <c r="O8" s="40" t="n"/>
     </row>
-    <row r="9" ht="72" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>4</v>
       </c>
@@ -1857,12 +1905,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
+          <t>Nhìn CẠNH bàn chân bài đầu tiên — tìm dấu chân vàng hình hộp quà (kho báu học liệu).</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Hiện tại trường CHƯA nạp học liệu nào nên chỗ này KHÔNG hiện gì, vào thẳng câu hỏi luôn — đúng hiện trạng, không phải lỗi. Nếu bạn LẠI thấy một mục 'Bài học' kèm danh sách tài liệu thì mở thử một mục và ghi lại cảm nhận.</t>
+          <t>Có hộp quà vàng ghi 0/1 (hoặc 0/2, 0/3 tuỳ thầy cô đăng mấy mức). Bài nào thầy cô chưa đăng gì thì không có hộp quà — đó là bình thường, không phải lỗi.</t>
         </is>
       </c>
       <c r="E9" s="42" t="n"/>
@@ -1877,7 +1925,7 @@
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="40" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="41" t="n">
         <v>5</v>
       </c>
@@ -1888,12 +1936,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Bấm vào hộp quà vàng.</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
+          <t>Mở màn 'Kho báu của bài': trên cùng là bậc thang Mức 1/2/3, dưới là học liệu của mức đang mở. Nếu thầy cô bật nhiều kiểu cho cùng một nội dung (ví dụ vừa podcast vừa sơ đồ) thì hiện SONG SONG, bấm chọn từng cái để xem.</t>
         </is>
       </c>
       <c r="E10" s="42" t="n"/>
@@ -1908,7 +1956,7 @@
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="40" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="41" t="n">
         <v>6</v>
       </c>
@@ -1919,12 +1967,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Mở thử từng kiểu học liệu: nghe podcast, xem ảnh sơ đồ, mở video, tải phiếu bài tập.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
+          <t>Podcast có nút play nghe ngay · ảnh hiện trọn khung, bấm phóng to · video phát tại chỗ · tệp Word/PowerPoint hiện thẻ TẢI VỀ (trình duyệt không mở được loại đó tại chỗ) · PDF xem ngay kèm nút tải.</t>
         </is>
       </c>
       <c r="E11" s="42" t="n"/>
@@ -1939,7 +1987,7 @@
       <c r="N11" s="46" t="n"/>
       <c r="O11" s="40" t="n"/>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="41" t="n">
         <v>7</v>
       </c>
@@ -1950,12 +1998,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>Bấm 'XEM XONG MỨC 1', rồi thử mở lại kho báu ngay lập tức.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
+          <t>Sư tử khen và nói mức sau đã mở. Bậc thang: mức 1 có dấu tích, mức 2 sáng lên. Mỗi lượt vào chỉ mở thêm MỘT mức — muốn lấy tiếp phải quay lại lần sau, đó là cố ý.</t>
         </is>
       </c>
       <c r="E12" s="42" t="n"/>
@@ -1970,7 +2018,7 @@
       <c r="N12" s="46" t="n"/>
       <c r="O12" s="40" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="41" t="n">
         <v>8</v>
       </c>
@@ -1981,12 +2029,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Cuộn xuống một bài còn KHOÁ ở phía sau, thử bấm kho báu của bài đó.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
+          <t>Hộp quà xám, có hình ổ khoá, bấm không vào được, hiện lời nhắc 'học xong bài phía trước là mở được'.</t>
         </is>
       </c>
       <c r="E13" s="42" t="n"/>
@@ -2012,12 +2060,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
+          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
         </is>
       </c>
       <c r="E14" s="42" t="n"/>
@@ -2043,12 +2091,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
+          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
         </is>
       </c>
       <c r="E15" s="42" t="n"/>
@@ -2063,7 +2111,7 @@
       <c r="N15" s="46" t="n"/>
       <c r="O15" s="40" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="41" t="n">
         <v>11</v>
       </c>
@@ -2074,12 +2122,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
         </is>
       </c>
       <c r="E16" s="42" t="n"/>
@@ -2094,7 +2142,7 @@
       <c r="N16" s="46" t="n"/>
       <c r="O16" s="40" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="41" t="n">
         <v>12</v>
       </c>
@@ -2105,12 +2153,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
+          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
         </is>
       </c>
       <c r="E17" s="42" t="n"/>
@@ -2136,12 +2184,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
+          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
         </is>
       </c>
       <c r="E18" s="42" t="n"/>
@@ -2156,7 +2204,7 @@
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="40" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="41" t="n">
         <v>14</v>
       </c>
@@ -2167,12 +2215,12 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
         </is>
       </c>
       <c r="E19" s="42" t="n"/>
@@ -2187,44 +2235,54 @@
       <c r="N19" s="46" t="n"/>
       <c r="O19" s="40" t="n"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>VAI PHỤ HUYNH</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Học Sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="43" t="n"/>
+      <c r="H20" s="43" t="n"/>
+      <c r="I20" s="44" t="n"/>
+      <c r="J20" s="44" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="46" t="n"/>
+      <c r="N20" s="46" t="n"/>
+      <c r="O20" s="40" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
+          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
       <c r="E21" s="42" t="n"/>
@@ -2241,21 +2299,21 @@
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
+          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
         </is>
       </c>
       <c r="E22" s="42" t="n"/>
@@ -2270,23 +2328,23 @@
       <c r="N22" s="46" t="n"/>
       <c r="O22" s="40" t="n"/>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
         </is>
       </c>
       <c r="E23" s="42" t="n"/>
@@ -2302,43 +2360,43 @@
       <c r="O23" s="40" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="48" t="inlineStr">
-        <is>
-          <t>VAI GIÁO VIÊN</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="n"/>
-      <c r="I24" s="18" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="18" t="n"/>
-      <c r="O24" s="18" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="A24" s="47" t="inlineStr">
+        <is>
+          <t>VAI PHỤ HUYNH</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
+          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
         </is>
       </c>
       <c r="E25" s="42" t="n"/>
@@ -2355,21 +2413,21 @@
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
+          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
         </is>
       </c>
       <c r="E26" s="42" t="n"/>
@@ -2386,21 +2444,21 @@
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
         </is>
       </c>
       <c r="E27" s="42" t="n"/>
@@ -2415,36 +2473,26 @@
       <c r="N27" s="46" t="n"/>
       <c r="O27" s="40" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="41" t="n">
-        <v>21</v>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Giáo Viên</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
-        </is>
-      </c>
-      <c r="E28" s="42" t="n"/>
-      <c r="F28" s="42" t="n"/>
-      <c r="G28" s="43" t="n"/>
-      <c r="H28" s="43" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="44" t="n"/>
-      <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="n"/>
-      <c r="M28" s="46" t="n"/>
-      <c r="N28" s="46" t="n"/>
-      <c r="O28" s="40" t="n"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>VAI GIÁO VIÊN</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="41" t="n">
@@ -2457,12 +2505,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+          <t>Trang giáo viên có 6 tab: Tổng quan · Học sinh · Chủ đề · Học liệu · Chấm bài · Duyệt &amp; nội dung.</t>
         </is>
       </c>
       <c r="E29" s="42" t="n"/>
@@ -2488,12 +2536,12 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
         </is>
       </c>
       <c r="E30" s="42" t="n"/>
@@ -2508,242 +2556,350 @@
       <c r="N30" s="46" t="n"/>
       <c r="O30" s="40" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab CHẤM BÀI.</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+        </is>
+      </c>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="43" t="n"/>
+      <c r="I31" s="44" t="n"/>
+      <c r="J31" s="44" t="n"/>
+      <c r="K31" s="45" t="n"/>
+      <c r="L31" s="45" t="n"/>
+      <c r="M31" s="46" t="n"/>
+      <c r="N31" s="46" t="n"/>
+      <c r="O31" s="40" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="43" t="n"/>
+      <c r="H32" s="43" t="n"/>
+      <c r="I32" s="44" t="n"/>
+      <c r="J32" s="44" t="n"/>
+      <c r="K32" s="45" t="n"/>
+      <c r="L32" s="45" t="n"/>
+      <c r="M32" s="46" t="n"/>
+      <c r="N32" s="46" t="n"/>
+      <c r="O32" s="40" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab HỌC LIỆU.</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Cột trái: toàn bộ bài của môn gom theo chương, có ô tìm; mỗi bài ghi rõ đã có mấy học liệu đang hiện trên tổng số, và bao nhiêu câu hỏi. Bài chưa có gì thì ghi 'chưa có'.</t>
+        </is>
+      </c>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="43" t="n"/>
+      <c r="I33" s="44" t="n"/>
+      <c r="J33" s="44" t="n"/>
+      <c r="K33" s="45" t="n"/>
+      <c r="L33" s="45" t="n"/>
+      <c r="M33" s="46" t="n"/>
+      <c r="N33" s="46" t="n"/>
+      <c r="O33" s="40" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Chọn bài 'Khái niệm mệnh đề logic'. Ở khung 'Thêm học liệu': đặt tên, để MỨC 1, chọn kiểu 'Phim ngắn', DÁN một link YouTube, bấm THÊM VÀO BÀI.</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Mục vừa thêm hiện ngay trong khối 'Mức 1' bên trên, kèm tên tệp/ghi chú 'link ngoài'. Số đếm ở cột trái tăng lên.</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="43" t="n"/>
+      <c r="H34" s="43" t="n"/>
+      <c r="I34" s="44" t="n"/>
+      <c r="J34" s="44" t="n"/>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="45" t="n"/>
+      <c r="M34" s="46" t="n"/>
+      <c r="N34" s="46" t="n"/>
+      <c r="O34" s="40" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Thêm mục THỨ HAI cũng ở MỨC 1 nhưng TẢI TỆP LÊN (ảnh, PDF hoặc file Word bất kỳ).</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Tệp tải lên xong hiện thành mục thứ hai trong Mức 1. Hai mục cùng mức nghĩa là học sinh sẽ thấy cả hai SONG SONG.</t>
+        </is>
+      </c>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="43" t="n"/>
+      <c r="I35" s="44" t="n"/>
+      <c r="J35" s="44" t="n"/>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="45" t="n"/>
+      <c r="M35" s="46" t="n"/>
+      <c r="N35" s="46" t="n"/>
+      <c r="O35" s="40" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Bấm nút CON MẮT ở một trong hai mục để tắt.</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Mục đó mờ đi (vẫn nằm đó cho bạn bật lại), số 'đang hiện' ở cột trái giảm 1. Học sinh sẽ không còn thấy mục này nữa.</t>
+        </is>
+      </c>
+      <c r="E36" s="42" t="n"/>
+      <c r="F36" s="42" t="n"/>
+      <c r="G36" s="43" t="n"/>
+      <c r="H36" s="43" t="n"/>
+      <c r="I36" s="44" t="n"/>
+      <c r="J36" s="44" t="n"/>
+      <c r="K36" s="45" t="n"/>
+      <c r="L36" s="45" t="n"/>
+      <c r="M36" s="46" t="n"/>
+      <c r="N36" s="46" t="n"/>
+      <c r="O36" s="40" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Thêm một mục nữa nhưng chọn MỨC 2.</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Nó rơi vào khối 'Mức 2 — mở sau khi xem xong mức 1'. Học sinh phải xem hết mức 1 rồi quay lại mới thấy.</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="43" t="n"/>
+      <c r="H37" s="43" t="n"/>
+      <c r="I37" s="44" t="n"/>
+      <c r="J37" s="44" t="n"/>
+      <c r="K37" s="45" t="n"/>
+      <c r="L37" s="45" t="n"/>
+      <c r="M37" s="46" t="n"/>
+      <c r="N37" s="46" t="n"/>
+      <c r="O37" s="40" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+        </is>
+      </c>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="43" t="n"/>
+      <c r="H38" s="43" t="n"/>
+      <c r="I38" s="44" t="n"/>
+      <c r="J38" s="44" t="n"/>
+      <c r="K38" s="45" t="n"/>
+      <c r="L38" s="45" t="n"/>
+      <c r="M38" s="46" t="n"/>
+      <c r="N38" s="46" t="n"/>
+      <c r="O38" s="40" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+        </is>
+      </c>
+      <c r="E39" s="42" t="n"/>
+      <c r="F39" s="42" t="n"/>
+      <c r="G39" s="43" t="n"/>
+      <c r="H39" s="43" t="n"/>
+      <c r="I39" s="44" t="n"/>
+      <c r="J39" s="44" t="n"/>
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="45" t="n"/>
+      <c r="M39" s="46" t="n"/>
+      <c r="N39" s="46" t="n"/>
+      <c r="O39" s="40" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>NHẬT KÝ TỰ DO — bất cứ điều gì bạn gặp, kể cả ngoài các chặng trên</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr"/>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr"/>
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Đợt</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Vai lúc đó</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Ở màn hình nào / đang làm gì</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Chuyện gì xảy ra</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>Nặng hay nhẹ?</t>
         </is>
       </c>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>Bạn mong nó phải thế nào</t>
         </is>
       </c>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="49" t="n"/>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
-      <c r="E34" s="49" t="n"/>
-      <c r="F34" s="49" t="n"/>
-      <c r="G34" s="49" t="n"/>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="49" t="n"/>
-      <c r="J34" s="49" t="n"/>
-      <c r="K34" s="49" t="n"/>
-      <c r="L34" s="49" t="n"/>
-      <c r="M34" s="49" t="n"/>
-      <c r="N34" s="49" t="n"/>
-      <c r="O34" s="49" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
-      <c r="G35" s="49" t="n"/>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="49" t="n"/>
-      <c r="J35" s="49" t="n"/>
-      <c r="K35" s="49" t="n"/>
-      <c r="L35" s="49" t="n"/>
-      <c r="M35" s="49" t="n"/>
-      <c r="N35" s="49" t="n"/>
-      <c r="O35" s="49" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="49" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="49" t="n"/>
-      <c r="F36" s="49" t="n"/>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
-      <c r="J36" s="49" t="n"/>
-      <c r="K36" s="49" t="n"/>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="49" t="n"/>
-      <c r="N36" s="49" t="n"/>
-      <c r="O36" s="49" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
-      <c r="J37" s="49" t="n"/>
-      <c r="K37" s="49" t="n"/>
-      <c r="L37" s="49" t="n"/>
-      <c r="M37" s="49" t="n"/>
-      <c r="N37" s="49" t="n"/>
-      <c r="O37" s="49" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" s="49" t="n"/>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="49" t="n"/>
-      <c r="F38" s="49" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
-      <c r="J38" s="49" t="n"/>
-      <c r="K38" s="49" t="n"/>
-      <c r="L38" s="49" t="n"/>
-      <c r="M38" s="49" t="n"/>
-      <c r="N38" s="49" t="n"/>
-      <c r="O38" s="49" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="49" t="n"/>
-      <c r="G39" s="49" t="n"/>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
-      <c r="J39" s="49" t="n"/>
-      <c r="K39" s="49" t="n"/>
-      <c r="L39" s="49" t="n"/>
-      <c r="M39" s="49" t="n"/>
-      <c r="N39" s="49" t="n"/>
-      <c r="O39" s="49" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="49" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
-      <c r="E40" s="49" t="n"/>
-      <c r="F40" s="49" t="n"/>
-      <c r="G40" s="49" t="n"/>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
-      <c r="J40" s="49" t="n"/>
-      <c r="K40" s="49" t="n"/>
-      <c r="L40" s="49" t="n"/>
-      <c r="M40" s="49" t="n"/>
-      <c r="N40" s="49" t="n"/>
-      <c r="O40" s="49" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="49" t="n"/>
-      <c r="E41" s="49" t="n"/>
-      <c r="F41" s="49" t="n"/>
-      <c r="G41" s="49" t="n"/>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
-      <c r="J41" s="49" t="n"/>
-      <c r="K41" s="49" t="n"/>
-      <c r="L41" s="49" t="n"/>
-      <c r="M41" s="49" t="n"/>
-      <c r="N41" s="49" t="n"/>
-      <c r="O41" s="49" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="B42" s="49" t="n"/>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="49" t="n"/>
-      <c r="E42" s="49" t="n"/>
-      <c r="F42" s="49" t="n"/>
-      <c r="G42" s="49" t="n"/>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
-      <c r="J42" s="49" t="n"/>
-      <c r="K42" s="49" t="n"/>
-      <c r="L42" s="49" t="n"/>
-      <c r="M42" s="49" t="n"/>
-      <c r="N42" s="49" t="n"/>
-      <c r="O42" s="49" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="11" t="n"/>
+      <c r="O42" s="11" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="49" t="n"/>
@@ -2762,7 +2918,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="41" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B44" s="49" t="n"/>
       <c r="C44" s="49" t="n"/>
@@ -2781,7 +2937,7 @@
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B45" s="49" t="n"/>
       <c r="C45" s="49" t="n"/>
@@ -2798,300 +2954,494 @@
       <c r="N45" s="49" t="n"/>
       <c r="O45" s="49" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="49" t="n"/>
+      <c r="C46" s="49" t="n"/>
+      <c r="D46" s="49" t="n"/>
+      <c r="E46" s="49" t="n"/>
+      <c r="F46" s="49" t="n"/>
+      <c r="G46" s="49" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
+      <c r="J46" s="49" t="n"/>
+      <c r="K46" s="49" t="n"/>
+      <c r="L46" s="49" t="n"/>
+      <c r="M46" s="49" t="n"/>
+      <c r="N46" s="49" t="n"/>
+      <c r="O46" s="49" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="49" t="n"/>
+      <c r="D47" s="49" t="n"/>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="n"/>
+      <c r="G47" s="49" t="n"/>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="49" t="n"/>
+      <c r="J47" s="49" t="n"/>
+      <c r="K47" s="49" t="n"/>
+      <c r="L47" s="49" t="n"/>
+      <c r="M47" s="49" t="n"/>
+      <c r="N47" s="49" t="n"/>
+      <c r="O47" s="49" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="49" t="n"/>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
+      <c r="G48" s="49" t="n"/>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="49" t="n"/>
+      <c r="J48" s="49" t="n"/>
+      <c r="K48" s="49" t="n"/>
+      <c r="L48" s="49" t="n"/>
+      <c r="M48" s="49" t="n"/>
+      <c r="N48" s="49" t="n"/>
+      <c r="O48" s="49" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="49" t="n"/>
+      <c r="D49" s="49" t="n"/>
+      <c r="E49" s="49" t="n"/>
+      <c r="F49" s="49" t="n"/>
+      <c r="G49" s="49" t="n"/>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="49" t="n"/>
+      <c r="J49" s="49" t="n"/>
+      <c r="K49" s="49" t="n"/>
+      <c r="L49" s="49" t="n"/>
+      <c r="M49" s="49" t="n"/>
+      <c r="N49" s="49" t="n"/>
+      <c r="O49" s="49" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="49" t="n"/>
+      <c r="C50" s="49" t="n"/>
+      <c r="D50" s="49" t="n"/>
+      <c r="E50" s="49" t="n"/>
+      <c r="F50" s="49" t="n"/>
+      <c r="G50" s="49" t="n"/>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="49" t="n"/>
+      <c r="J50" s="49" t="n"/>
+      <c r="K50" s="49" t="n"/>
+      <c r="L50" s="49" t="n"/>
+      <c r="M50" s="49" t="n"/>
+      <c r="N50" s="49" t="n"/>
+      <c r="O50" s="49" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="49" t="n"/>
+      <c r="D51" s="49" t="n"/>
+      <c r="E51" s="49" t="n"/>
+      <c r="F51" s="49" t="n"/>
+      <c r="G51" s="49" t="n"/>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="49" t="n"/>
+      <c r="J51" s="49" t="n"/>
+      <c r="K51" s="49" t="n"/>
+      <c r="L51" s="49" t="n"/>
+      <c r="M51" s="49" t="n"/>
+      <c r="N51" s="49" t="n"/>
+      <c r="O51" s="49" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="49" t="n"/>
+      <c r="C52" s="49" t="n"/>
+      <c r="D52" s="49" t="n"/>
+      <c r="E52" s="49" t="n"/>
+      <c r="F52" s="49" t="n"/>
+      <c r="G52" s="49" t="n"/>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="49" t="n"/>
+      <c r="J52" s="49" t="n"/>
+      <c r="K52" s="49" t="n"/>
+      <c r="L52" s="49" t="n"/>
+      <c r="M52" s="49" t="n"/>
+      <c r="N52" s="49" t="n"/>
+      <c r="O52" s="49" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="49" t="n"/>
+      <c r="D53" s="49" t="n"/>
+      <c r="E53" s="49" t="n"/>
+      <c r="F53" s="49" t="n"/>
+      <c r="G53" s="49" t="n"/>
+      <c r="H53" s="49" t="n"/>
+      <c r="I53" s="49" t="n"/>
+      <c r="J53" s="49" t="n"/>
+      <c r="K53" s="49" t="n"/>
+      <c r="L53" s="49" t="n"/>
+      <c r="M53" s="49" t="n"/>
+      <c r="N53" s="49" t="n"/>
+      <c r="O53" s="49" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" s="49" t="n"/>
+      <c r="C54" s="49" t="n"/>
+      <c r="D54" s="49" t="n"/>
+      <c r="E54" s="49" t="n"/>
+      <c r="F54" s="49" t="n"/>
+      <c r="G54" s="49" t="n"/>
+      <c r="H54" s="49" t="n"/>
+      <c r="I54" s="49" t="n"/>
+      <c r="J54" s="49" t="n"/>
+      <c r="K54" s="49" t="n"/>
+      <c r="L54" s="49" t="n"/>
+      <c r="M54" s="49" t="n"/>
+      <c r="N54" s="49" t="n"/>
+      <c r="O54" s="49" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>NÓI THẬT GIÙM CHÚNG TÔI (trả lời sau ĐỢT 1; đợt sau có gì đổi ý thì ghi thêm)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="50" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Điều bạn THÍCH nhất khi dùng app:</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="50" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
-      <c r="O48" s="21" t="n"/>
-    </row>
-    <row r="49" ht="50" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="50" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="21" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="21" t="n"/>
+      <c r="L57" s="21" t="n"/>
+      <c r="M57" s="21" t="n"/>
+      <c r="N57" s="21" t="n"/>
+      <c r="O57" s="21" t="n"/>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="50" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
-      <c r="H49" s="21" t="n"/>
-      <c r="I49" s="21" t="n"/>
-      <c r="J49" s="21" t="n"/>
-      <c r="K49" s="21" t="n"/>
-      <c r="L49" s="21" t="n"/>
-      <c r="M49" s="21" t="n"/>
-      <c r="N49" s="21" t="n"/>
-      <c r="O49" s="21" t="n"/>
-    </row>
-    <row r="50" ht="50" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="50" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="21" t="n"/>
+      <c r="I58" s="21" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="21" t="n"/>
+      <c r="L58" s="21" t="n"/>
+      <c r="M58" s="21" t="n"/>
+      <c r="N58" s="21" t="n"/>
+      <c r="O58" s="21" t="n"/>
+    </row>
+    <row r="59" ht="50" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
-      <c r="H50" s="21" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="J50" s="21" t="n"/>
-      <c r="K50" s="21" t="n"/>
-      <c r="L50" s="21" t="n"/>
-      <c r="M50" s="21" t="n"/>
-      <c r="N50" s="21" t="n"/>
-      <c r="O50" s="21" t="n"/>
-    </row>
-    <row r="51" ht="50" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="50" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="21" t="n"/>
+      <c r="L59" s="21" t="n"/>
+      <c r="M59" s="21" t="n"/>
+      <c r="N59" s="21" t="n"/>
+      <c r="O59" s="21" t="n"/>
+    </row>
+    <row r="60" ht="50" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
-      <c r="J51" s="21" t="n"/>
-      <c r="K51" s="21" t="n"/>
-      <c r="L51" s="21" t="n"/>
-      <c r="M51" s="21" t="n"/>
-      <c r="N51" s="21" t="n"/>
-      <c r="O51" s="21" t="n"/>
-    </row>
-    <row r="52" ht="50" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="50" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
+      <c r="J60" s="21" t="n"/>
+      <c r="K60" s="21" t="n"/>
+      <c r="L60" s="21" t="n"/>
+      <c r="M60" s="21" t="n"/>
+      <c r="N60" s="21" t="n"/>
+      <c r="O60" s="21" t="n"/>
+    </row>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
-      <c r="K52" s="21" t="n"/>
-      <c r="L52" s="21" t="n"/>
-      <c r="M52" s="21" t="n"/>
-      <c r="N52" s="21" t="n"/>
-      <c r="O52" s="21" t="n"/>
-    </row>
-    <row r="53" ht="50" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="B61" s="21" t="n"/>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="50" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="21" t="n"/>
+      <c r="J61" s="21" t="n"/>
+      <c r="K61" s="21" t="n"/>
+      <c r="L61" s="21" t="n"/>
+      <c r="M61" s="21" t="n"/>
+      <c r="N61" s="21" t="n"/>
+      <c r="O61" s="21" t="n"/>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
         </is>
       </c>
-      <c r="B53" s="21" t="n"/>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
-      <c r="H53" s="21" t="n"/>
-      <c r="I53" s="21" t="n"/>
-      <c r="J53" s="21" t="n"/>
-      <c r="K53" s="21" t="n"/>
-      <c r="L53" s="21" t="n"/>
-      <c r="M53" s="21" t="n"/>
-      <c r="N53" s="21" t="n"/>
-      <c r="O53" s="21" t="n"/>
-    </row>
-    <row r="54" ht="50" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>HỌC LIỆU: bạn muốn mỗi bài kèm sẵn thứ gì trước khi em làm câu hỏi — video ngắn, slide, phiếu in ra làm, đề cương, hay không cần gì? Nguồn lấy từ đâu: cô tự soạn, kho của trường, hay link ngoài (YouTube/Drive)?</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="21" t="n"/>
-      <c r="K54" s="21" t="n"/>
-      <c r="L54" s="21" t="n"/>
-      <c r="M54" s="21" t="n"/>
-      <c r="N54" s="21" t="n"/>
-      <c r="O54" s="21" t="n"/>
-    </row>
-    <row r="55" ht="50" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="50" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+      <c r="J62" s="21" t="n"/>
+      <c r="K62" s="21" t="n"/>
+      <c r="L62" s="21" t="n"/>
+      <c r="M62" s="21" t="n"/>
+      <c r="N62" s="21" t="n"/>
+      <c r="O62" s="21" t="n"/>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>HỌC LIỆU: đăng tài liệu cho một bài mất bao lâu, có chỗ nào rối không? Bạn có thật sự sẽ làm việc này cho từng bài mình dạy không, hay cần trường soạn sẵn rồi bạn chỉ chọn?</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n"/>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="50" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="21" t="n"/>
+      <c r="L63" s="21" t="n"/>
+      <c r="M63" s="21" t="n"/>
+      <c r="N63" s="21" t="n"/>
+      <c r="O63" s="21" t="n"/>
+    </row>
+    <row r="64" ht="50" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>BA MỨC kho báu: cách chia mức 1-2-3 có hợp với cách bạn dạy không? Mỗi lần chỉ mở một mức (bắt em quay lại) là hay hay phiền? Bạn sẽ xếp thứ gì vào mức 1, thứ gì để mức 3?</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="21" t="n"/>
+      <c r="E64" s="50" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="21" t="n"/>
+      <c r="I64" s="21" t="n"/>
+      <c r="J64" s="21" t="n"/>
+      <c r="K64" s="21" t="n"/>
+      <c r="L64" s="21" t="n"/>
+      <c r="M64" s="21" t="n"/>
+      <c r="N64" s="21" t="n"/>
+      <c r="O64" s="21" t="n"/>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
         </is>
       </c>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="n"/>
-      <c r="H55" s="21" t="n"/>
-      <c r="I55" s="21" t="n"/>
-      <c r="J55" s="21" t="n"/>
-      <c r="K55" s="21" t="n"/>
-      <c r="L55" s="21" t="n"/>
-      <c r="M55" s="21" t="n"/>
-      <c r="N55" s="21" t="n"/>
-      <c r="O55" s="21" t="n"/>
-    </row>
-    <row r="56" ht="50" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="B65" s="21" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="50" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="21" t="n"/>
+      <c r="K65" s="21" t="n"/>
+      <c r="L65" s="21" t="n"/>
+      <c r="M65" s="21" t="n"/>
+      <c r="N65" s="21" t="n"/>
+      <c r="O65" s="21" t="n"/>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
         </is>
       </c>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="21" t="n"/>
-      <c r="I56" s="21" t="n"/>
-      <c r="J56" s="21" t="n"/>
-      <c r="K56" s="21" t="n"/>
-      <c r="L56" s="21" t="n"/>
-      <c r="M56" s="21" t="n"/>
-      <c r="N56" s="21" t="n"/>
-      <c r="O56" s="21" t="n"/>
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="50" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="21" t="n"/>
+      <c r="K66" s="21" t="n"/>
+      <c r="L66" s="21" t="n"/>
+      <c r="M66" s="21" t="n"/>
+      <c r="N66" s="21" t="n"/>
+      <c r="O66" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="E53:O53"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:O34"/>
+  <mergeCells count="72">
     <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E50:O50"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="K33:O33"/>
-    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E58:O58"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E54:H54"/>
     <mergeCell ref="I45:J45"/>
-    <mergeCell ref="E55:O55"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:O36"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="E62:O62"/>
+    <mergeCell ref="K54:O54"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="K45:O45"/>
-    <mergeCell ref="E52:O52"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E48:O48"/>
-    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="E64:O64"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="E51:O51"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="E53:H53"/>
     <mergeCell ref="E43:H43"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A47:O47"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="K44:O44"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E63:O63"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="E42:H42"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E60:O60"/>
     <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E65:O65"/>
+    <mergeCell ref="K52:O52"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="K43:O43"/>
-    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="A28:O28"/>
     <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E59:O59"/>
     <mergeCell ref="E44:H44"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="K42:O42"/>
-    <mergeCell ref="E49:O49"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="E61:O61"/>
     <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E54:O54"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K53:O53"/>
+    <mergeCell ref="E57:O57"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K38:O38"/>
-    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="K37:O37"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E66:O66"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="K49:O49"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E21 E22 E23 E25 E26 E27 E28 E29 E30 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G25 G26 G27 G28 G29 G30 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I21 I22 I23 I25 I26 I27 I28 I29 I30 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K21 K22 K23 K25 K26 K27 K28 K29 K30 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M21 M22 M23 M25 M26 M27 M28 M29 M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E25 E26 E27 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G25 G26 G27 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I25 I26 I27 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K25 K26 K27 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M25 M26 M27 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng như mô tả,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O21 O22 O23 O25 O26 O27 O28 O29 O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O25 O26 O27 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chặn hẳn không đi tiếp được,Khó chịu nhưng vẫn làm được,Góp ý cho đẹp hơn"</formula1>
     </dataValidation>
-    <dataValidation sqref="B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3105,7 +3455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3391,7 +3741,7 @@
       <c r="N8" s="46" t="n"/>
       <c r="O8" s="40" t="n"/>
     </row>
-    <row r="9" ht="72" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>4</v>
       </c>
@@ -3402,12 +3752,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
+          <t>Nhìn CẠNH bàn chân bài đầu tiên — tìm dấu chân vàng hình hộp quà (kho báu học liệu).</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Hiện tại trường CHƯA nạp học liệu nào nên chỗ này KHÔNG hiện gì, vào thẳng câu hỏi luôn — đúng hiện trạng, không phải lỗi. Nếu bạn LẠI thấy một mục 'Bài học' kèm danh sách tài liệu thì mở thử một mục và ghi lại cảm nhận.</t>
+          <t>Có hộp quà vàng ghi 0/1 (hoặc 0/2, 0/3 tuỳ thầy cô đăng mấy mức). Bài nào thầy cô chưa đăng gì thì không có hộp quà — đó là bình thường, không phải lỗi.</t>
         </is>
       </c>
       <c r="E9" s="42" t="n"/>
@@ -3422,7 +3772,7 @@
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="40" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="41" t="n">
         <v>5</v>
       </c>
@@ -3433,12 +3783,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Bấm vào hộp quà vàng.</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
+          <t>Mở màn 'Kho báu của bài': trên cùng là bậc thang Mức 1/2/3, dưới là học liệu của mức đang mở. Nếu thầy cô bật nhiều kiểu cho cùng một nội dung (ví dụ vừa podcast vừa sơ đồ) thì hiện SONG SONG, bấm chọn từng cái để xem.</t>
         </is>
       </c>
       <c r="E10" s="42" t="n"/>
@@ -3453,7 +3803,7 @@
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="40" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="41" t="n">
         <v>6</v>
       </c>
@@ -3464,12 +3814,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Mở thử từng kiểu học liệu: nghe podcast, xem ảnh sơ đồ, mở video, tải phiếu bài tập.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
+          <t>Podcast có nút play nghe ngay · ảnh hiện trọn khung, bấm phóng to · video phát tại chỗ · tệp Word/PowerPoint hiện thẻ TẢI VỀ (trình duyệt không mở được loại đó tại chỗ) · PDF xem ngay kèm nút tải.</t>
         </is>
       </c>
       <c r="E11" s="42" t="n"/>
@@ -3484,7 +3834,7 @@
       <c r="N11" s="46" t="n"/>
       <c r="O11" s="40" t="n"/>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="41" t="n">
         <v>7</v>
       </c>
@@ -3495,12 +3845,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>Bấm 'XEM XONG MỨC 1', rồi thử mở lại kho báu ngay lập tức.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
+          <t>Sư tử khen và nói mức sau đã mở. Bậc thang: mức 1 có dấu tích, mức 2 sáng lên. Mỗi lượt vào chỉ mở thêm MỘT mức — muốn lấy tiếp phải quay lại lần sau, đó là cố ý.</t>
         </is>
       </c>
       <c r="E12" s="42" t="n"/>
@@ -3515,7 +3865,7 @@
       <c r="N12" s="46" t="n"/>
       <c r="O12" s="40" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="41" t="n">
         <v>8</v>
       </c>
@@ -3526,12 +3876,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Cuộn xuống một bài còn KHOÁ ở phía sau, thử bấm kho báu của bài đó.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
+          <t>Hộp quà xám, có hình ổ khoá, bấm không vào được, hiện lời nhắc 'học xong bài phía trước là mở được'.</t>
         </is>
       </c>
       <c r="E13" s="42" t="n"/>
@@ -3557,12 +3907,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
+          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
         </is>
       </c>
       <c r="E14" s="42" t="n"/>
@@ -3588,12 +3938,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
+          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
         </is>
       </c>
       <c r="E15" s="42" t="n"/>
@@ -3608,7 +3958,7 @@
       <c r="N15" s="46" t="n"/>
       <c r="O15" s="40" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="41" t="n">
         <v>11</v>
       </c>
@@ -3619,12 +3969,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
         </is>
       </c>
       <c r="E16" s="42" t="n"/>
@@ -3639,7 +3989,7 @@
       <c r="N16" s="46" t="n"/>
       <c r="O16" s="40" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="41" t="n">
         <v>12</v>
       </c>
@@ -3650,12 +4000,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
+          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
         </is>
       </c>
       <c r="E17" s="42" t="n"/>
@@ -3681,12 +4031,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
+          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
         </is>
       </c>
       <c r="E18" s="42" t="n"/>
@@ -3701,7 +4051,7 @@
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="40" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="41" t="n">
         <v>14</v>
       </c>
@@ -3712,12 +4062,12 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
         </is>
       </c>
       <c r="E19" s="42" t="n"/>
@@ -3732,44 +4082,54 @@
       <c r="N19" s="46" t="n"/>
       <c r="O19" s="40" t="n"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>VAI PHỤ HUYNH</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Học Sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="43" t="n"/>
+      <c r="H20" s="43" t="n"/>
+      <c r="I20" s="44" t="n"/>
+      <c r="J20" s="44" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="46" t="n"/>
+      <c r="N20" s="46" t="n"/>
+      <c r="O20" s="40" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
+          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
       <c r="E21" s="42" t="n"/>
@@ -3786,21 +4146,21 @@
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
+          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
         </is>
       </c>
       <c r="E22" s="42" t="n"/>
@@ -3815,23 +4175,23 @@
       <c r="N22" s="46" t="n"/>
       <c r="O22" s="40" t="n"/>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
         </is>
       </c>
       <c r="E23" s="42" t="n"/>
@@ -3847,43 +4207,43 @@
       <c r="O23" s="40" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="48" t="inlineStr">
-        <is>
-          <t>VAI GIÁO VIÊN</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="n"/>
-      <c r="I24" s="18" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="18" t="n"/>
-      <c r="O24" s="18" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="A24" s="47" t="inlineStr">
+        <is>
+          <t>VAI PHỤ HUYNH</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
+          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
         </is>
       </c>
       <c r="E25" s="42" t="n"/>
@@ -3900,21 +4260,21 @@
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
+          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
         </is>
       </c>
       <c r="E26" s="42" t="n"/>
@@ -3931,21 +4291,21 @@
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
         </is>
       </c>
       <c r="E27" s="42" t="n"/>
@@ -3960,36 +4320,26 @@
       <c r="N27" s="46" t="n"/>
       <c r="O27" s="40" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="41" t="n">
-        <v>21</v>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Giáo Viên</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
-        </is>
-      </c>
-      <c r="E28" s="42" t="n"/>
-      <c r="F28" s="42" t="n"/>
-      <c r="G28" s="43" t="n"/>
-      <c r="H28" s="43" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="44" t="n"/>
-      <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="n"/>
-      <c r="M28" s="46" t="n"/>
-      <c r="N28" s="46" t="n"/>
-      <c r="O28" s="40" t="n"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>VAI GIÁO VIÊN</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="41" t="n">
@@ -4002,12 +4352,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+          <t>Trang giáo viên có 6 tab: Tổng quan · Học sinh · Chủ đề · Học liệu · Chấm bài · Duyệt &amp; nội dung.</t>
         </is>
       </c>
       <c r="E29" s="42" t="n"/>
@@ -4033,12 +4383,12 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
         </is>
       </c>
       <c r="E30" s="42" t="n"/>
@@ -4053,242 +4403,350 @@
       <c r="N30" s="46" t="n"/>
       <c r="O30" s="40" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab CHẤM BÀI.</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+        </is>
+      </c>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="43" t="n"/>
+      <c r="I31" s="44" t="n"/>
+      <c r="J31" s="44" t="n"/>
+      <c r="K31" s="45" t="n"/>
+      <c r="L31" s="45" t="n"/>
+      <c r="M31" s="46" t="n"/>
+      <c r="N31" s="46" t="n"/>
+      <c r="O31" s="40" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="43" t="n"/>
+      <c r="H32" s="43" t="n"/>
+      <c r="I32" s="44" t="n"/>
+      <c r="J32" s="44" t="n"/>
+      <c r="K32" s="45" t="n"/>
+      <c r="L32" s="45" t="n"/>
+      <c r="M32" s="46" t="n"/>
+      <c r="N32" s="46" t="n"/>
+      <c r="O32" s="40" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab HỌC LIỆU.</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Cột trái: toàn bộ bài của môn gom theo chương, có ô tìm; mỗi bài ghi rõ đã có mấy học liệu đang hiện trên tổng số, và bao nhiêu câu hỏi. Bài chưa có gì thì ghi 'chưa có'.</t>
+        </is>
+      </c>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="43" t="n"/>
+      <c r="I33" s="44" t="n"/>
+      <c r="J33" s="44" t="n"/>
+      <c r="K33" s="45" t="n"/>
+      <c r="L33" s="45" t="n"/>
+      <c r="M33" s="46" t="n"/>
+      <c r="N33" s="46" t="n"/>
+      <c r="O33" s="40" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Chọn bài 'Khái niệm mệnh đề logic'. Ở khung 'Thêm học liệu': đặt tên, để MỨC 1, chọn kiểu 'Phim ngắn', DÁN một link YouTube, bấm THÊM VÀO BÀI.</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Mục vừa thêm hiện ngay trong khối 'Mức 1' bên trên, kèm tên tệp/ghi chú 'link ngoài'. Số đếm ở cột trái tăng lên.</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="43" t="n"/>
+      <c r="H34" s="43" t="n"/>
+      <c r="I34" s="44" t="n"/>
+      <c r="J34" s="44" t="n"/>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="45" t="n"/>
+      <c r="M34" s="46" t="n"/>
+      <c r="N34" s="46" t="n"/>
+      <c r="O34" s="40" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Thêm mục THỨ HAI cũng ở MỨC 1 nhưng TẢI TỆP LÊN (ảnh, PDF hoặc file Word bất kỳ).</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Tệp tải lên xong hiện thành mục thứ hai trong Mức 1. Hai mục cùng mức nghĩa là học sinh sẽ thấy cả hai SONG SONG.</t>
+        </is>
+      </c>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="43" t="n"/>
+      <c r="I35" s="44" t="n"/>
+      <c r="J35" s="44" t="n"/>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="45" t="n"/>
+      <c r="M35" s="46" t="n"/>
+      <c r="N35" s="46" t="n"/>
+      <c r="O35" s="40" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Bấm nút CON MẮT ở một trong hai mục để tắt.</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Mục đó mờ đi (vẫn nằm đó cho bạn bật lại), số 'đang hiện' ở cột trái giảm 1. Học sinh sẽ không còn thấy mục này nữa.</t>
+        </is>
+      </c>
+      <c r="E36" s="42" t="n"/>
+      <c r="F36" s="42" t="n"/>
+      <c r="G36" s="43" t="n"/>
+      <c r="H36" s="43" t="n"/>
+      <c r="I36" s="44" t="n"/>
+      <c r="J36" s="44" t="n"/>
+      <c r="K36" s="45" t="n"/>
+      <c r="L36" s="45" t="n"/>
+      <c r="M36" s="46" t="n"/>
+      <c r="N36" s="46" t="n"/>
+      <c r="O36" s="40" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Thêm một mục nữa nhưng chọn MỨC 2.</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Nó rơi vào khối 'Mức 2 — mở sau khi xem xong mức 1'. Học sinh phải xem hết mức 1 rồi quay lại mới thấy.</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="43" t="n"/>
+      <c r="H37" s="43" t="n"/>
+      <c r="I37" s="44" t="n"/>
+      <c r="J37" s="44" t="n"/>
+      <c r="K37" s="45" t="n"/>
+      <c r="L37" s="45" t="n"/>
+      <c r="M37" s="46" t="n"/>
+      <c r="N37" s="46" t="n"/>
+      <c r="O37" s="40" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+        </is>
+      </c>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="43" t="n"/>
+      <c r="H38" s="43" t="n"/>
+      <c r="I38" s="44" t="n"/>
+      <c r="J38" s="44" t="n"/>
+      <c r="K38" s="45" t="n"/>
+      <c r="L38" s="45" t="n"/>
+      <c r="M38" s="46" t="n"/>
+      <c r="N38" s="46" t="n"/>
+      <c r="O38" s="40" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+        </is>
+      </c>
+      <c r="E39" s="42" t="n"/>
+      <c r="F39" s="42" t="n"/>
+      <c r="G39" s="43" t="n"/>
+      <c r="H39" s="43" t="n"/>
+      <c r="I39" s="44" t="n"/>
+      <c r="J39" s="44" t="n"/>
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="45" t="n"/>
+      <c r="M39" s="46" t="n"/>
+      <c r="N39" s="46" t="n"/>
+      <c r="O39" s="40" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>NHẬT KÝ TỰ DO — bất cứ điều gì bạn gặp, kể cả ngoài các chặng trên</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr"/>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr"/>
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Đợt</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Vai lúc đó</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Ở màn hình nào / đang làm gì</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Chuyện gì xảy ra</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>Nặng hay nhẹ?</t>
         </is>
       </c>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>Bạn mong nó phải thế nào</t>
         </is>
       </c>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="49" t="n"/>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
-      <c r="E34" s="49" t="n"/>
-      <c r="F34" s="49" t="n"/>
-      <c r="G34" s="49" t="n"/>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="49" t="n"/>
-      <c r="J34" s="49" t="n"/>
-      <c r="K34" s="49" t="n"/>
-      <c r="L34" s="49" t="n"/>
-      <c r="M34" s="49" t="n"/>
-      <c r="N34" s="49" t="n"/>
-      <c r="O34" s="49" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
-      <c r="G35" s="49" t="n"/>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="49" t="n"/>
-      <c r="J35" s="49" t="n"/>
-      <c r="K35" s="49" t="n"/>
-      <c r="L35" s="49" t="n"/>
-      <c r="M35" s="49" t="n"/>
-      <c r="N35" s="49" t="n"/>
-      <c r="O35" s="49" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="49" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="49" t="n"/>
-      <c r="F36" s="49" t="n"/>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
-      <c r="J36" s="49" t="n"/>
-      <c r="K36" s="49" t="n"/>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="49" t="n"/>
-      <c r="N36" s="49" t="n"/>
-      <c r="O36" s="49" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
-      <c r="J37" s="49" t="n"/>
-      <c r="K37" s="49" t="n"/>
-      <c r="L37" s="49" t="n"/>
-      <c r="M37" s="49" t="n"/>
-      <c r="N37" s="49" t="n"/>
-      <c r="O37" s="49" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" s="49" t="n"/>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="49" t="n"/>
-      <c r="F38" s="49" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
-      <c r="J38" s="49" t="n"/>
-      <c r="K38" s="49" t="n"/>
-      <c r="L38" s="49" t="n"/>
-      <c r="M38" s="49" t="n"/>
-      <c r="N38" s="49" t="n"/>
-      <c r="O38" s="49" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="49" t="n"/>
-      <c r="G39" s="49" t="n"/>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
-      <c r="J39" s="49" t="n"/>
-      <c r="K39" s="49" t="n"/>
-      <c r="L39" s="49" t="n"/>
-      <c r="M39" s="49" t="n"/>
-      <c r="N39" s="49" t="n"/>
-      <c r="O39" s="49" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="49" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
-      <c r="E40" s="49" t="n"/>
-      <c r="F40" s="49" t="n"/>
-      <c r="G40" s="49" t="n"/>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
-      <c r="J40" s="49" t="n"/>
-      <c r="K40" s="49" t="n"/>
-      <c r="L40" s="49" t="n"/>
-      <c r="M40" s="49" t="n"/>
-      <c r="N40" s="49" t="n"/>
-      <c r="O40" s="49" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="49" t="n"/>
-      <c r="E41" s="49" t="n"/>
-      <c r="F41" s="49" t="n"/>
-      <c r="G41" s="49" t="n"/>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
-      <c r="J41" s="49" t="n"/>
-      <c r="K41" s="49" t="n"/>
-      <c r="L41" s="49" t="n"/>
-      <c r="M41" s="49" t="n"/>
-      <c r="N41" s="49" t="n"/>
-      <c r="O41" s="49" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="B42" s="49" t="n"/>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="49" t="n"/>
-      <c r="E42" s="49" t="n"/>
-      <c r="F42" s="49" t="n"/>
-      <c r="G42" s="49" t="n"/>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
-      <c r="J42" s="49" t="n"/>
-      <c r="K42" s="49" t="n"/>
-      <c r="L42" s="49" t="n"/>
-      <c r="M42" s="49" t="n"/>
-      <c r="N42" s="49" t="n"/>
-      <c r="O42" s="49" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="11" t="n"/>
+      <c r="O42" s="11" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="49" t="n"/>
@@ -4307,7 +4765,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="41" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B44" s="49" t="n"/>
       <c r="C44" s="49" t="n"/>
@@ -4326,7 +4784,7 @@
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B45" s="49" t="n"/>
       <c r="C45" s="49" t="n"/>
@@ -4343,300 +4801,494 @@
       <c r="N45" s="49" t="n"/>
       <c r="O45" s="49" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="49" t="n"/>
+      <c r="C46" s="49" t="n"/>
+      <c r="D46" s="49" t="n"/>
+      <c r="E46" s="49" t="n"/>
+      <c r="F46" s="49" t="n"/>
+      <c r="G46" s="49" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
+      <c r="J46" s="49" t="n"/>
+      <c r="K46" s="49" t="n"/>
+      <c r="L46" s="49" t="n"/>
+      <c r="M46" s="49" t="n"/>
+      <c r="N46" s="49" t="n"/>
+      <c r="O46" s="49" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="49" t="n"/>
+      <c r="D47" s="49" t="n"/>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="n"/>
+      <c r="G47" s="49" t="n"/>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="49" t="n"/>
+      <c r="J47" s="49" t="n"/>
+      <c r="K47" s="49" t="n"/>
+      <c r="L47" s="49" t="n"/>
+      <c r="M47" s="49" t="n"/>
+      <c r="N47" s="49" t="n"/>
+      <c r="O47" s="49" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="49" t="n"/>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
+      <c r="G48" s="49" t="n"/>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="49" t="n"/>
+      <c r="J48" s="49" t="n"/>
+      <c r="K48" s="49" t="n"/>
+      <c r="L48" s="49" t="n"/>
+      <c r="M48" s="49" t="n"/>
+      <c r="N48" s="49" t="n"/>
+      <c r="O48" s="49" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="49" t="n"/>
+      <c r="D49" s="49" t="n"/>
+      <c r="E49" s="49" t="n"/>
+      <c r="F49" s="49" t="n"/>
+      <c r="G49" s="49" t="n"/>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="49" t="n"/>
+      <c r="J49" s="49" t="n"/>
+      <c r="K49" s="49" t="n"/>
+      <c r="L49" s="49" t="n"/>
+      <c r="M49" s="49" t="n"/>
+      <c r="N49" s="49" t="n"/>
+      <c r="O49" s="49" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="49" t="n"/>
+      <c r="C50" s="49" t="n"/>
+      <c r="D50" s="49" t="n"/>
+      <c r="E50" s="49" t="n"/>
+      <c r="F50" s="49" t="n"/>
+      <c r="G50" s="49" t="n"/>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="49" t="n"/>
+      <c r="J50" s="49" t="n"/>
+      <c r="K50" s="49" t="n"/>
+      <c r="L50" s="49" t="n"/>
+      <c r="M50" s="49" t="n"/>
+      <c r="N50" s="49" t="n"/>
+      <c r="O50" s="49" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="49" t="n"/>
+      <c r="D51" s="49" t="n"/>
+      <c r="E51" s="49" t="n"/>
+      <c r="F51" s="49" t="n"/>
+      <c r="G51" s="49" t="n"/>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="49" t="n"/>
+      <c r="J51" s="49" t="n"/>
+      <c r="K51" s="49" t="n"/>
+      <c r="L51" s="49" t="n"/>
+      <c r="M51" s="49" t="n"/>
+      <c r="N51" s="49" t="n"/>
+      <c r="O51" s="49" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="49" t="n"/>
+      <c r="C52" s="49" t="n"/>
+      <c r="D52" s="49" t="n"/>
+      <c r="E52" s="49" t="n"/>
+      <c r="F52" s="49" t="n"/>
+      <c r="G52" s="49" t="n"/>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="49" t="n"/>
+      <c r="J52" s="49" t="n"/>
+      <c r="K52" s="49" t="n"/>
+      <c r="L52" s="49" t="n"/>
+      <c r="M52" s="49" t="n"/>
+      <c r="N52" s="49" t="n"/>
+      <c r="O52" s="49" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="49" t="n"/>
+      <c r="D53" s="49" t="n"/>
+      <c r="E53" s="49" t="n"/>
+      <c r="F53" s="49" t="n"/>
+      <c r="G53" s="49" t="n"/>
+      <c r="H53" s="49" t="n"/>
+      <c r="I53" s="49" t="n"/>
+      <c r="J53" s="49" t="n"/>
+      <c r="K53" s="49" t="n"/>
+      <c r="L53" s="49" t="n"/>
+      <c r="M53" s="49" t="n"/>
+      <c r="N53" s="49" t="n"/>
+      <c r="O53" s="49" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" s="49" t="n"/>
+      <c r="C54" s="49" t="n"/>
+      <c r="D54" s="49" t="n"/>
+      <c r="E54" s="49" t="n"/>
+      <c r="F54" s="49" t="n"/>
+      <c r="G54" s="49" t="n"/>
+      <c r="H54" s="49" t="n"/>
+      <c r="I54" s="49" t="n"/>
+      <c r="J54" s="49" t="n"/>
+      <c r="K54" s="49" t="n"/>
+      <c r="L54" s="49" t="n"/>
+      <c r="M54" s="49" t="n"/>
+      <c r="N54" s="49" t="n"/>
+      <c r="O54" s="49" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>NÓI THẬT GIÙM CHÚNG TÔI (trả lời sau ĐỢT 1; đợt sau có gì đổi ý thì ghi thêm)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="50" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Điều bạn THÍCH nhất khi dùng app:</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="50" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
-      <c r="O48" s="21" t="n"/>
-    </row>
-    <row r="49" ht="50" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="50" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="21" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="21" t="n"/>
+      <c r="L57" s="21" t="n"/>
+      <c r="M57" s="21" t="n"/>
+      <c r="N57" s="21" t="n"/>
+      <c r="O57" s="21" t="n"/>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="50" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
-      <c r="H49" s="21" t="n"/>
-      <c r="I49" s="21" t="n"/>
-      <c r="J49" s="21" t="n"/>
-      <c r="K49" s="21" t="n"/>
-      <c r="L49" s="21" t="n"/>
-      <c r="M49" s="21" t="n"/>
-      <c r="N49" s="21" t="n"/>
-      <c r="O49" s="21" t="n"/>
-    </row>
-    <row r="50" ht="50" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="50" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="21" t="n"/>
+      <c r="I58" s="21" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="21" t="n"/>
+      <c r="L58" s="21" t="n"/>
+      <c r="M58" s="21" t="n"/>
+      <c r="N58" s="21" t="n"/>
+      <c r="O58" s="21" t="n"/>
+    </row>
+    <row r="59" ht="50" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
-      <c r="H50" s="21" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="J50" s="21" t="n"/>
-      <c r="K50" s="21" t="n"/>
-      <c r="L50" s="21" t="n"/>
-      <c r="M50" s="21" t="n"/>
-      <c r="N50" s="21" t="n"/>
-      <c r="O50" s="21" t="n"/>
-    </row>
-    <row r="51" ht="50" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="50" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="21" t="n"/>
+      <c r="L59" s="21" t="n"/>
+      <c r="M59" s="21" t="n"/>
+      <c r="N59" s="21" t="n"/>
+      <c r="O59" s="21" t="n"/>
+    </row>
+    <row r="60" ht="50" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
-      <c r="J51" s="21" t="n"/>
-      <c r="K51" s="21" t="n"/>
-      <c r="L51" s="21" t="n"/>
-      <c r="M51" s="21" t="n"/>
-      <c r="N51" s="21" t="n"/>
-      <c r="O51" s="21" t="n"/>
-    </row>
-    <row r="52" ht="50" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="50" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
+      <c r="J60" s="21" t="n"/>
+      <c r="K60" s="21" t="n"/>
+      <c r="L60" s="21" t="n"/>
+      <c r="M60" s="21" t="n"/>
+      <c r="N60" s="21" t="n"/>
+      <c r="O60" s="21" t="n"/>
+    </row>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
-      <c r="K52" s="21" t="n"/>
-      <c r="L52" s="21" t="n"/>
-      <c r="M52" s="21" t="n"/>
-      <c r="N52" s="21" t="n"/>
-      <c r="O52" s="21" t="n"/>
-    </row>
-    <row r="53" ht="50" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="B61" s="21" t="n"/>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="50" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="21" t="n"/>
+      <c r="J61" s="21" t="n"/>
+      <c r="K61" s="21" t="n"/>
+      <c r="L61" s="21" t="n"/>
+      <c r="M61" s="21" t="n"/>
+      <c r="N61" s="21" t="n"/>
+      <c r="O61" s="21" t="n"/>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
         </is>
       </c>
-      <c r="B53" s="21" t="n"/>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
-      <c r="H53" s="21" t="n"/>
-      <c r="I53" s="21" t="n"/>
-      <c r="J53" s="21" t="n"/>
-      <c r="K53" s="21" t="n"/>
-      <c r="L53" s="21" t="n"/>
-      <c r="M53" s="21" t="n"/>
-      <c r="N53" s="21" t="n"/>
-      <c r="O53" s="21" t="n"/>
-    </row>
-    <row r="54" ht="50" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>HỌC LIỆU: bạn muốn mỗi bài kèm sẵn thứ gì trước khi em làm câu hỏi — video ngắn, slide, phiếu in ra làm, đề cương, hay không cần gì? Nguồn lấy từ đâu: cô tự soạn, kho của trường, hay link ngoài (YouTube/Drive)?</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="21" t="n"/>
-      <c r="K54" s="21" t="n"/>
-      <c r="L54" s="21" t="n"/>
-      <c r="M54" s="21" t="n"/>
-      <c r="N54" s="21" t="n"/>
-      <c r="O54" s="21" t="n"/>
-    </row>
-    <row r="55" ht="50" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="50" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+      <c r="J62" s="21" t="n"/>
+      <c r="K62" s="21" t="n"/>
+      <c r="L62" s="21" t="n"/>
+      <c r="M62" s="21" t="n"/>
+      <c r="N62" s="21" t="n"/>
+      <c r="O62" s="21" t="n"/>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>HỌC LIỆU: đăng tài liệu cho một bài mất bao lâu, có chỗ nào rối không? Bạn có thật sự sẽ làm việc này cho từng bài mình dạy không, hay cần trường soạn sẵn rồi bạn chỉ chọn?</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n"/>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="50" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="21" t="n"/>
+      <c r="L63" s="21" t="n"/>
+      <c r="M63" s="21" t="n"/>
+      <c r="N63" s="21" t="n"/>
+      <c r="O63" s="21" t="n"/>
+    </row>
+    <row r="64" ht="50" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>BA MỨC kho báu: cách chia mức 1-2-3 có hợp với cách bạn dạy không? Mỗi lần chỉ mở một mức (bắt em quay lại) là hay hay phiền? Bạn sẽ xếp thứ gì vào mức 1, thứ gì để mức 3?</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="21" t="n"/>
+      <c r="E64" s="50" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="21" t="n"/>
+      <c r="I64" s="21" t="n"/>
+      <c r="J64" s="21" t="n"/>
+      <c r="K64" s="21" t="n"/>
+      <c r="L64" s="21" t="n"/>
+      <c r="M64" s="21" t="n"/>
+      <c r="N64" s="21" t="n"/>
+      <c r="O64" s="21" t="n"/>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
         </is>
       </c>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="n"/>
-      <c r="H55" s="21" t="n"/>
-      <c r="I55" s="21" t="n"/>
-      <c r="J55" s="21" t="n"/>
-      <c r="K55" s="21" t="n"/>
-      <c r="L55" s="21" t="n"/>
-      <c r="M55" s="21" t="n"/>
-      <c r="N55" s="21" t="n"/>
-      <c r="O55" s="21" t="n"/>
-    </row>
-    <row r="56" ht="50" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="B65" s="21" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="50" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="21" t="n"/>
+      <c r="K65" s="21" t="n"/>
+      <c r="L65" s="21" t="n"/>
+      <c r="M65" s="21" t="n"/>
+      <c r="N65" s="21" t="n"/>
+      <c r="O65" s="21" t="n"/>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
         </is>
       </c>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="21" t="n"/>
-      <c r="I56" s="21" t="n"/>
-      <c r="J56" s="21" t="n"/>
-      <c r="K56" s="21" t="n"/>
-      <c r="L56" s="21" t="n"/>
-      <c r="M56" s="21" t="n"/>
-      <c r="N56" s="21" t="n"/>
-      <c r="O56" s="21" t="n"/>
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="50" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="21" t="n"/>
+      <c r="K66" s="21" t="n"/>
+      <c r="L66" s="21" t="n"/>
+      <c r="M66" s="21" t="n"/>
+      <c r="N66" s="21" t="n"/>
+      <c r="O66" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="E53:O53"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:O34"/>
+  <mergeCells count="72">
     <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E50:O50"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="K33:O33"/>
-    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E58:O58"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E54:H54"/>
     <mergeCell ref="I45:J45"/>
-    <mergeCell ref="E55:O55"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:O36"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="E62:O62"/>
+    <mergeCell ref="K54:O54"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="K45:O45"/>
-    <mergeCell ref="E52:O52"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E48:O48"/>
-    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="E64:O64"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="E51:O51"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="E53:H53"/>
     <mergeCell ref="E43:H43"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A47:O47"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="K44:O44"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E63:O63"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="E42:H42"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E60:O60"/>
     <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E65:O65"/>
+    <mergeCell ref="K52:O52"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="K43:O43"/>
-    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="A28:O28"/>
     <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E59:O59"/>
     <mergeCell ref="E44:H44"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="K42:O42"/>
-    <mergeCell ref="E49:O49"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="E61:O61"/>
     <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E54:O54"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K53:O53"/>
+    <mergeCell ref="E57:O57"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K38:O38"/>
-    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="K37:O37"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E66:O66"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="K49:O49"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E21 E22 E23 E25 E26 E27 E28 E29 E30 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G25 G26 G27 G28 G29 G30 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I21 I22 I23 I25 I26 I27 I28 I29 I30 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K21 K22 K23 K25 K26 K27 K28 K29 K30 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M21 M22 M23 M25 M26 M27 M28 M29 M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E25 E26 E27 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G25 G26 G27 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I25 I26 I27 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K25 K26 K27 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M25 M26 M27 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng như mô tả,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O21 O22 O23 O25 O26 O27 O28 O29 O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O25 O26 O27 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chặn hẳn không đi tiếp được,Khó chịu nhưng vẫn làm được,Góp ý cho đẹp hơn"</formula1>
     </dataValidation>
-    <dataValidation sqref="B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4650,7 +5302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4936,7 +5588,7 @@
       <c r="N8" s="46" t="n"/>
       <c r="O8" s="40" t="n"/>
     </row>
-    <row r="9" ht="72" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>4</v>
       </c>
@@ -4947,12 +5599,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
+          <t>Nhìn CẠNH bàn chân bài đầu tiên — tìm dấu chân vàng hình hộp quà (kho báu học liệu).</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Hiện tại trường CHƯA nạp học liệu nào nên chỗ này KHÔNG hiện gì, vào thẳng câu hỏi luôn — đúng hiện trạng, không phải lỗi. Nếu bạn LẠI thấy một mục 'Bài học' kèm danh sách tài liệu thì mở thử một mục và ghi lại cảm nhận.</t>
+          <t>Có hộp quà vàng ghi 0/1 (hoặc 0/2, 0/3 tuỳ thầy cô đăng mấy mức). Bài nào thầy cô chưa đăng gì thì không có hộp quà — đó là bình thường, không phải lỗi.</t>
         </is>
       </c>
       <c r="E9" s="42" t="n"/>
@@ -4967,7 +5619,7 @@
       <c r="N9" s="46" t="n"/>
       <c r="O9" s="40" t="n"/>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="41" t="n">
         <v>5</v>
       </c>
@@ -4978,12 +5630,12 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Bấm vào hộp quà vàng.</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
+          <t>Mở màn 'Kho báu của bài': trên cùng là bậc thang Mức 1/2/3, dưới là học liệu của mức đang mở. Nếu thầy cô bật nhiều kiểu cho cùng một nội dung (ví dụ vừa podcast vừa sơ đồ) thì hiện SONG SONG, bấm chọn từng cái để xem.</t>
         </is>
       </c>
       <c r="E10" s="42" t="n"/>
@@ -4998,7 +5650,7 @@
       <c r="N10" s="46" t="n"/>
       <c r="O10" s="40" t="n"/>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="41" t="n">
         <v>6</v>
       </c>
@@ -5009,12 +5661,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Mở thử từng kiểu học liệu: nghe podcast, xem ảnh sơ đồ, mở video, tải phiếu bài tập.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
+          <t>Podcast có nút play nghe ngay · ảnh hiện trọn khung, bấm phóng to · video phát tại chỗ · tệp Word/PowerPoint hiện thẻ TẢI VỀ (trình duyệt không mở được loại đó tại chỗ) · PDF xem ngay kèm nút tải.</t>
         </is>
       </c>
       <c r="E11" s="42" t="n"/>
@@ -5029,7 +5681,7 @@
       <c r="N11" s="46" t="n"/>
       <c r="O11" s="40" t="n"/>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="41" t="n">
         <v>7</v>
       </c>
@@ -5040,12 +5692,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>Bấm 'XEM XONG MỨC 1', rồi thử mở lại kho báu ngay lập tức.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
+          <t>Sư tử khen và nói mức sau đã mở. Bậc thang: mức 1 có dấu tích, mức 2 sáng lên. Mỗi lượt vào chỉ mở thêm MỘT mức — muốn lấy tiếp phải quay lại lần sau, đó là cố ý.</t>
         </is>
       </c>
       <c r="E12" s="42" t="n"/>
@@ -5060,7 +5712,7 @@
       <c r="N12" s="46" t="n"/>
       <c r="O12" s="40" t="n"/>
     </row>
-    <row r="13" ht="60" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="41" t="n">
         <v>8</v>
       </c>
@@ -5071,12 +5723,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Cuộn xuống một bài còn KHOÁ ở phía sau, thử bấm kho báu của bài đó.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
+          <t>Hộp quà xám, có hình ổ khoá, bấm không vào được, hiện lời nhắc 'học xong bài phía trước là mở được'.</t>
         </is>
       </c>
       <c r="E13" s="42" t="n"/>
@@ -5102,12 +5754,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
+          <t>Câu 1 và 4 bấm chọn 1 trong 4 ô; câu 2 chọn Đúng/Sai cho từng ý a→d; câu 3 gõ chữ. Đúng thì sư tử reo và cộng XP.</t>
         </is>
       </c>
       <c r="E14" s="42" t="n"/>
@@ -5133,12 +5785,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
+          <t>Sư tử hiện kèm lời nhắc thử lại — KHÔNG cho đáp án, chỉ đẩy mình nghĩ lại. Bấm THỬ LẠI là làm tiếp được.</t>
         </is>
       </c>
       <c r="E15" s="42" t="n"/>
@@ -5153,7 +5805,7 @@
       <c r="N15" s="46" t="n"/>
       <c r="O15" s="40" t="n"/>
     </row>
-    <row r="16" ht="36" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="41" t="n">
         <v>11</v>
       </c>
@@ -5164,12 +5816,12 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+          <t>Mỗi bước một thẻ riêng. Bước có (Có/Không) hiện hai nút to; trả lời xong bước này mới mở bước sau; bước cuối có ô gõ kết luận.</t>
         </is>
       </c>
       <c r="E16" s="42" t="n"/>
@@ -5184,7 +5836,7 @@
       <c r="N16" s="46" t="n"/>
       <c r="O16" s="40" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="41" t="n">
         <v>12</v>
       </c>
@@ -5195,12 +5847,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
+          <t>Ô lớn 'Viết bài làm của em ở đây', dưới có dòng 'Đính kèm ảnh bài làm' (tuỳ chọn). Nộp xong hiện 'Đang suy nghĩ…' vài giây rồi trợ lý nhận xét đủ ý hay thiếu ý gì.</t>
         </is>
       </c>
       <c r="E17" s="42" t="n"/>
@@ -5226,12 +5878,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
+          <t>Bài cũ vẫn nằm nguyên trong ô để sửa tiếp, có nút NỘP LẠI ngay dưới. Không phải gõ lại từ đầu.</t>
         </is>
       </c>
       <c r="E18" s="42" t="n"/>
@@ -5246,7 +5898,7 @@
       <c r="N18" s="46" t="n"/>
       <c r="O18" s="40" t="n"/>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="41" t="n">
         <v>14</v>
       </c>
@@ -5257,12 +5909,12 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
+          <t>Tên tệp hiện cạnh cái kẹp giấy, có nút X để gỡ. Nộp xong app nói đã nhận, chờ thầy cô chấm.</t>
         </is>
       </c>
       <c r="E19" s="42" t="n"/>
@@ -5277,44 +5929,54 @@
       <c r="N19" s="46" t="n"/>
       <c r="O19" s="40" t="n"/>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t>VAI PHỤ HUYNH</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n"/>
-      <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="48" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Học Sinh</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Bàn chân bài vừa học hiện số câu đã làm (ví dụ 6/8) và nhãn 'chờ chấm' nếu còn bài đợi thầy cô.</t>
+        </is>
+      </c>
+      <c r="E20" s="42" t="n"/>
+      <c r="F20" s="42" t="n"/>
+      <c r="G20" s="43" t="n"/>
+      <c r="H20" s="43" t="n"/>
+      <c r="I20" s="44" t="n"/>
+      <c r="J20" s="44" t="n"/>
+      <c r="K20" s="45" t="n"/>
+      <c r="L20" s="45" t="n"/>
+      <c r="M20" s="46" t="n"/>
+      <c r="N20" s="46" t="n"/>
+      <c r="O20" s="40" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
+          <t>Ôn tập: câu từng sai. Hạng: xếp hạng + XP. Mục tiêu: việc cần làm. Tôi: hồ sơ, đổi mật khẩu.</t>
         </is>
       </c>
       <c r="E21" s="42" t="n"/>
@@ -5331,21 +5993,21 @@
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
+          <t>Lộ trình gom theo chương, cuộn được tới cuối, tên bài đọc ra là hiểu đang học ý gì. Bài xa phía sau đều bị khoá.</t>
         </is>
       </c>
       <c r="E22" s="42" t="n"/>
@@ -5360,23 +6022,23 @@
       <c r="N22" s="46" t="n"/>
       <c r="O22" s="40" t="n"/>
     </row>
-    <row r="23" ht="48" customHeight="1">
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
+          <t>Chữ đủ to, nút không dính nhau, bàn phím không che nút, không phải kéo ngang.</t>
         </is>
       </c>
       <c r="E23" s="42" t="n"/>
@@ -5392,43 +6054,43 @@
       <c r="O23" s="40" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="48" t="inlineStr">
-        <is>
-          <t>VAI GIÁO VIÊN</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="18" t="n"/>
-      <c r="I24" s="18" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="18" t="n"/>
-      <c r="O24" s="18" t="n"/>
-    </row>
-    <row r="25" ht="36" customHeight="1">
+      <c r="A24" s="47" t="inlineStr">
+        <is>
+          <t>VAI PHỤ HUYNH</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="8" t="n"/>
+      <c r="J24" s="8" t="n"/>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+    </row>
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>Trang giáo viên có 5 tab: Tổng quan · Học sinh · Chủ đề · Chấm bài · Duyệt &amp; nội dung.</t>
+          <t>Vào trang 'Theo dõi con' → 'Báo cáo tuần' của ĐÚNG con bạn: tên con, số điểm đã thành thạo / đang luyện thêm, tiến độ mục tiêu.</t>
         </is>
       </c>
       <c r="E25" s="42" t="n"/>
@@ -5445,21 +6107,21 @@
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="41" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
+          <t>CHỈ ĐÚNG MỘT tên — con của bạn. Thấy tên em khác là lỗi bảo mật, ghi lại và báo ngay lập tức.</t>
         </is>
       </c>
       <c r="E26" s="42" t="n"/>
@@ -5476,21 +6138,21 @@
     </row>
     <row r="27" ht="48" customHeight="1">
       <c r="A27" s="41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+          <t>Báo cáo nói về NỖ LỰC và TIẾN BỘ, không có nội dung con trò chuyện với trợ lý. Bạn có hiểu con đang mạnh/yếu chỗ nào không?</t>
         </is>
       </c>
       <c r="E27" s="42" t="n"/>
@@ -5505,36 +6167,26 @@
       <c r="N27" s="46" t="n"/>
       <c r="O27" s="40" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="41" t="n">
-        <v>21</v>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Giáo Viên</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
-        </is>
-      </c>
-      <c r="E28" s="42" t="n"/>
-      <c r="F28" s="42" t="n"/>
-      <c r="G28" s="43" t="n"/>
-      <c r="H28" s="43" t="n"/>
-      <c r="I28" s="44" t="n"/>
-      <c r="J28" s="44" t="n"/>
-      <c r="K28" s="45" t="n"/>
-      <c r="L28" s="45" t="n"/>
-      <c r="M28" s="46" t="n"/>
-      <c r="N28" s="46" t="n"/>
-      <c r="O28" s="40" t="n"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>VAI GIÁO VIÊN</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="41" t="n">
@@ -5547,12 +6199,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+          <t>Trang giáo viên có 6 tab: Tổng quan · Học sinh · Chủ đề · Học liệu · Chấm bài · Duyệt &amp; nội dung.</t>
         </is>
       </c>
       <c r="E29" s="42" t="n"/>
@@ -5578,12 +6230,12 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+          <t>Danh sách học sinh kèm mức thành thạo, độ chính xác, nỗ lực. Ba em thử (A, B, C) đều phải có mặt.</t>
         </is>
       </c>
       <c r="E30" s="42" t="n"/>
@@ -5598,242 +6250,350 @@
       <c r="N30" s="46" t="n"/>
       <c r="O30" s="40" t="n"/>
     </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab CHẤM BÀI.</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Có con số bài đang chờ trên tab. Mỗi bài hiện: tên học sinh, đề bài, bài làm em gõ, đáp án mẫu để đối chiếu, và dòng 'AI sơ khảo' đã chấm trước.</t>
+        </is>
+      </c>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
+      <c r="G31" s="43" t="n"/>
+      <c r="H31" s="43" t="n"/>
+      <c r="I31" s="44" t="n"/>
+      <c r="J31" s="44" t="n"/>
+      <c r="K31" s="45" t="n"/>
+      <c r="L31" s="45" t="n"/>
+      <c r="M31" s="46" t="n"/>
+      <c r="N31" s="46" t="n"/>
+      <c r="O31" s="40" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Chấm xong bài rời khỏi hàng đợi. Một câu học sinh nộp nhiều lần chỉ hiện MỘT dòng — không phải chấm trùng.</t>
+        </is>
+      </c>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="43" t="n"/>
+      <c r="H32" s="43" t="n"/>
+      <c r="I32" s="44" t="n"/>
+      <c r="J32" s="44" t="n"/>
+      <c r="K32" s="45" t="n"/>
+      <c r="L32" s="45" t="n"/>
+      <c r="M32" s="46" t="n"/>
+      <c r="N32" s="46" t="n"/>
+      <c r="O32" s="40" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab HỌC LIỆU.</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Cột trái: toàn bộ bài của môn gom theo chương, có ô tìm; mỗi bài ghi rõ đã có mấy học liệu đang hiện trên tổng số, và bao nhiêu câu hỏi. Bài chưa có gì thì ghi 'chưa có'.</t>
+        </is>
+      </c>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="43" t="n"/>
+      <c r="I33" s="44" t="n"/>
+      <c r="J33" s="44" t="n"/>
+      <c r="K33" s="45" t="n"/>
+      <c r="L33" s="45" t="n"/>
+      <c r="M33" s="46" t="n"/>
+      <c r="N33" s="46" t="n"/>
+      <c r="O33" s="40" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Chọn bài 'Khái niệm mệnh đề logic'. Ở khung 'Thêm học liệu': đặt tên, để MỨC 1, chọn kiểu 'Phim ngắn', DÁN một link YouTube, bấm THÊM VÀO BÀI.</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Mục vừa thêm hiện ngay trong khối 'Mức 1' bên trên, kèm tên tệp/ghi chú 'link ngoài'. Số đếm ở cột trái tăng lên.</t>
+        </is>
+      </c>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="43" t="n"/>
+      <c r="H34" s="43" t="n"/>
+      <c r="I34" s="44" t="n"/>
+      <c r="J34" s="44" t="n"/>
+      <c r="K34" s="45" t="n"/>
+      <c r="L34" s="45" t="n"/>
+      <c r="M34" s="46" t="n"/>
+      <c r="N34" s="46" t="n"/>
+      <c r="O34" s="40" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Thêm mục THỨ HAI cũng ở MỨC 1 nhưng TẢI TỆP LÊN (ảnh, PDF hoặc file Word bất kỳ).</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Tệp tải lên xong hiện thành mục thứ hai trong Mức 1. Hai mục cùng mức nghĩa là học sinh sẽ thấy cả hai SONG SONG.</t>
+        </is>
+      </c>
+      <c r="E35" s="42" t="n"/>
+      <c r="F35" s="42" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="43" t="n"/>
+      <c r="I35" s="44" t="n"/>
+      <c r="J35" s="44" t="n"/>
+      <c r="K35" s="45" t="n"/>
+      <c r="L35" s="45" t="n"/>
+      <c r="M35" s="46" t="n"/>
+      <c r="N35" s="46" t="n"/>
+      <c r="O35" s="40" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Bấm nút CON MẮT ở một trong hai mục để tắt.</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Mục đó mờ đi (vẫn nằm đó cho bạn bật lại), số 'đang hiện' ở cột trái giảm 1. Học sinh sẽ không còn thấy mục này nữa.</t>
+        </is>
+      </c>
+      <c r="E36" s="42" t="n"/>
+      <c r="F36" s="42" t="n"/>
+      <c r="G36" s="43" t="n"/>
+      <c r="H36" s="43" t="n"/>
+      <c r="I36" s="44" t="n"/>
+      <c r="J36" s="44" t="n"/>
+      <c r="K36" s="45" t="n"/>
+      <c r="L36" s="45" t="n"/>
+      <c r="M36" s="46" t="n"/>
+      <c r="N36" s="46" t="n"/>
+      <c r="O36" s="40" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Thêm một mục nữa nhưng chọn MỨC 2.</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Nó rơi vào khối 'Mức 2 — mở sau khi xem xong mức 1'. Học sinh phải xem hết mức 1 rồi quay lại mới thấy.</t>
+        </is>
+      </c>
+      <c r="E37" s="42" t="n"/>
+      <c r="F37" s="42" t="n"/>
+      <c r="G37" s="43" t="n"/>
+      <c r="H37" s="43" t="n"/>
+      <c r="I37" s="44" t="n"/>
+      <c r="J37" s="44" t="n"/>
+      <c r="K37" s="45" t="n"/>
+      <c r="L37" s="45" t="n"/>
+      <c r="M37" s="46" t="n"/>
+      <c r="N37" s="46" t="n"/>
+      <c r="O37" s="40" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Tổng quan: đang học lúc này, hoạt động 7 ngày, đến hạn ôn, bài chờ chấm. Chủ đề: bài nào cả lớp đang yếu.</t>
+        </is>
+      </c>
+      <c r="E38" s="42" t="n"/>
+      <c r="F38" s="42" t="n"/>
+      <c r="G38" s="43" t="n"/>
+      <c r="H38" s="43" t="n"/>
+      <c r="I38" s="44" t="n"/>
+      <c r="J38" s="44" t="n"/>
+      <c r="K38" s="45" t="n"/>
+      <c r="L38" s="45" t="n"/>
+      <c r="M38" s="46" t="n"/>
+      <c r="N38" s="46" t="n"/>
+      <c r="O38" s="40" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Bài bị chấm 'chưa đạt' hiện BÀN CHÂN ĐỎ kèm lời mời làm lại. Bài chấm 'đạt' được tính, XP tăng.</t>
+        </is>
+      </c>
+      <c r="E39" s="42" t="n"/>
+      <c r="F39" s="42" t="n"/>
+      <c r="G39" s="43" t="n"/>
+      <c r="H39" s="43" t="n"/>
+      <c r="I39" s="44" t="n"/>
+      <c r="J39" s="44" t="n"/>
+      <c r="K39" s="45" t="n"/>
+      <c r="L39" s="45" t="n"/>
+      <c r="M39" s="46" t="n"/>
+      <c r="N39" s="46" t="n"/>
+      <c r="O39" s="40" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>NHẬT KÝ TỰ DO — bất cứ điều gì bạn gặp, kể cả ngoài các chặng trên</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr"/>
-      <c r="B33" s="12" t="inlineStr">
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr"/>
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Đợt</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>Vai lúc đó</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Ở màn hình nào / đang làm gì</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>Chuyện gì xảy ra</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="n"/>
-      <c r="I33" s="12" t="inlineStr">
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>Nặng hay nhẹ?</t>
         </is>
       </c>
-      <c r="J33" s="11" t="n"/>
-      <c r="K33" s="12" t="inlineStr">
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>Bạn mong nó phải thế nào</t>
         </is>
       </c>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="49" t="n"/>
-      <c r="C34" s="49" t="n"/>
-      <c r="D34" s="49" t="n"/>
-      <c r="E34" s="49" t="n"/>
-      <c r="F34" s="49" t="n"/>
-      <c r="G34" s="49" t="n"/>
-      <c r="H34" s="49" t="n"/>
-      <c r="I34" s="49" t="n"/>
-      <c r="J34" s="49" t="n"/>
-      <c r="K34" s="49" t="n"/>
-      <c r="L34" s="49" t="n"/>
-      <c r="M34" s="49" t="n"/>
-      <c r="N34" s="49" t="n"/>
-      <c r="O34" s="49" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="49" t="n"/>
-      <c r="C35" s="49" t="n"/>
-      <c r="D35" s="49" t="n"/>
-      <c r="E35" s="49" t="n"/>
-      <c r="F35" s="49" t="n"/>
-      <c r="G35" s="49" t="n"/>
-      <c r="H35" s="49" t="n"/>
-      <c r="I35" s="49" t="n"/>
-      <c r="J35" s="49" t="n"/>
-      <c r="K35" s="49" t="n"/>
-      <c r="L35" s="49" t="n"/>
-      <c r="M35" s="49" t="n"/>
-      <c r="N35" s="49" t="n"/>
-      <c r="O35" s="49" t="n"/>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="49" t="n"/>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
-      <c r="E36" s="49" t="n"/>
-      <c r="F36" s="49" t="n"/>
-      <c r="G36" s="49" t="n"/>
-      <c r="H36" s="49" t="n"/>
-      <c r="I36" s="49" t="n"/>
-      <c r="J36" s="49" t="n"/>
-      <c r="K36" s="49" t="n"/>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="49" t="n"/>
-      <c r="N36" s="49" t="n"/>
-      <c r="O36" s="49" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="49" t="n"/>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
-      <c r="E37" s="49" t="n"/>
-      <c r="F37" s="49" t="n"/>
-      <c r="G37" s="49" t="n"/>
-      <c r="H37" s="49" t="n"/>
-      <c r="I37" s="49" t="n"/>
-      <c r="J37" s="49" t="n"/>
-      <c r="K37" s="49" t="n"/>
-      <c r="L37" s="49" t="n"/>
-      <c r="M37" s="49" t="n"/>
-      <c r="N37" s="49" t="n"/>
-      <c r="O37" s="49" t="n"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B38" s="49" t="n"/>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
-      <c r="E38" s="49" t="n"/>
-      <c r="F38" s="49" t="n"/>
-      <c r="G38" s="49" t="n"/>
-      <c r="H38" s="49" t="n"/>
-      <c r="I38" s="49" t="n"/>
-      <c r="J38" s="49" t="n"/>
-      <c r="K38" s="49" t="n"/>
-      <c r="L38" s="49" t="n"/>
-      <c r="M38" s="49" t="n"/>
-      <c r="N38" s="49" t="n"/>
-      <c r="O38" s="49" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B39" s="49" t="n"/>
-      <c r="C39" s="49" t="n"/>
-      <c r="D39" s="49" t="n"/>
-      <c r="E39" s="49" t="n"/>
-      <c r="F39" s="49" t="n"/>
-      <c r="G39" s="49" t="n"/>
-      <c r="H39" s="49" t="n"/>
-      <c r="I39" s="49" t="n"/>
-      <c r="J39" s="49" t="n"/>
-      <c r="K39" s="49" t="n"/>
-      <c r="L39" s="49" t="n"/>
-      <c r="M39" s="49" t="n"/>
-      <c r="N39" s="49" t="n"/>
-      <c r="O39" s="49" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B40" s="49" t="n"/>
-      <c r="C40" s="49" t="n"/>
-      <c r="D40" s="49" t="n"/>
-      <c r="E40" s="49" t="n"/>
-      <c r="F40" s="49" t="n"/>
-      <c r="G40" s="49" t="n"/>
-      <c r="H40" s="49" t="n"/>
-      <c r="I40" s="49" t="n"/>
-      <c r="J40" s="49" t="n"/>
-      <c r="K40" s="49" t="n"/>
-      <c r="L40" s="49" t="n"/>
-      <c r="M40" s="49" t="n"/>
-      <c r="N40" s="49" t="n"/>
-      <c r="O40" s="49" t="n"/>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="B41" s="49" t="n"/>
-      <c r="C41" s="49" t="n"/>
-      <c r="D41" s="49" t="n"/>
-      <c r="E41" s="49" t="n"/>
-      <c r="F41" s="49" t="n"/>
-      <c r="G41" s="49" t="n"/>
-      <c r="H41" s="49" t="n"/>
-      <c r="I41" s="49" t="n"/>
-      <c r="J41" s="49" t="n"/>
-      <c r="K41" s="49" t="n"/>
-      <c r="L41" s="49" t="n"/>
-      <c r="M41" s="49" t="n"/>
-      <c r="N41" s="49" t="n"/>
-      <c r="O41" s="49" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="B42" s="49" t="n"/>
-      <c r="C42" s="49" t="n"/>
-      <c r="D42" s="49" t="n"/>
-      <c r="E42" s="49" t="n"/>
-      <c r="F42" s="49" t="n"/>
-      <c r="G42" s="49" t="n"/>
-      <c r="H42" s="49" t="n"/>
-      <c r="I42" s="49" t="n"/>
-      <c r="J42" s="49" t="n"/>
-      <c r="K42" s="49" t="n"/>
-      <c r="L42" s="49" t="n"/>
-      <c r="M42" s="49" t="n"/>
-      <c r="N42" s="49" t="n"/>
-      <c r="O42" s="49" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="11" t="n"/>
+      <c r="O42" s="11" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="49" t="n"/>
@@ -5852,7 +6612,7 @@
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="41" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B44" s="49" t="n"/>
       <c r="C44" s="49" t="n"/>
@@ -5871,7 +6631,7 @@
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B45" s="49" t="n"/>
       <c r="C45" s="49" t="n"/>
@@ -5888,300 +6648,494 @@
       <c r="N45" s="49" t="n"/>
       <c r="O45" s="49" t="n"/>
     </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="49" t="n"/>
+      <c r="C46" s="49" t="n"/>
+      <c r="D46" s="49" t="n"/>
+      <c r="E46" s="49" t="n"/>
+      <c r="F46" s="49" t="n"/>
+      <c r="G46" s="49" t="n"/>
+      <c r="H46" s="49" t="n"/>
+      <c r="I46" s="49" t="n"/>
+      <c r="J46" s="49" t="n"/>
+      <c r="K46" s="49" t="n"/>
+      <c r="L46" s="49" t="n"/>
+      <c r="M46" s="49" t="n"/>
+      <c r="N46" s="49" t="n"/>
+      <c r="O46" s="49" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="49" t="n"/>
+      <c r="C47" s="49" t="n"/>
+      <c r="D47" s="49" t="n"/>
+      <c r="E47" s="49" t="n"/>
+      <c r="F47" s="49" t="n"/>
+      <c r="G47" s="49" t="n"/>
+      <c r="H47" s="49" t="n"/>
+      <c r="I47" s="49" t="n"/>
+      <c r="J47" s="49" t="n"/>
+      <c r="K47" s="49" t="n"/>
+      <c r="L47" s="49" t="n"/>
+      <c r="M47" s="49" t="n"/>
+      <c r="N47" s="49" t="n"/>
+      <c r="O47" s="49" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="49" t="n"/>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="49" t="n"/>
+      <c r="G48" s="49" t="n"/>
+      <c r="H48" s="49" t="n"/>
+      <c r="I48" s="49" t="n"/>
+      <c r="J48" s="49" t="n"/>
+      <c r="K48" s="49" t="n"/>
+      <c r="L48" s="49" t="n"/>
+      <c r="M48" s="49" t="n"/>
+      <c r="N48" s="49" t="n"/>
+      <c r="O48" s="49" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="41" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="49" t="n"/>
+      <c r="C49" s="49" t="n"/>
+      <c r="D49" s="49" t="n"/>
+      <c r="E49" s="49" t="n"/>
+      <c r="F49" s="49" t="n"/>
+      <c r="G49" s="49" t="n"/>
+      <c r="H49" s="49" t="n"/>
+      <c r="I49" s="49" t="n"/>
+      <c r="J49" s="49" t="n"/>
+      <c r="K49" s="49" t="n"/>
+      <c r="L49" s="49" t="n"/>
+      <c r="M49" s="49" t="n"/>
+      <c r="N49" s="49" t="n"/>
+      <c r="O49" s="49" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="49" t="n"/>
+      <c r="C50" s="49" t="n"/>
+      <c r="D50" s="49" t="n"/>
+      <c r="E50" s="49" t="n"/>
+      <c r="F50" s="49" t="n"/>
+      <c r="G50" s="49" t="n"/>
+      <c r="H50" s="49" t="n"/>
+      <c r="I50" s="49" t="n"/>
+      <c r="J50" s="49" t="n"/>
+      <c r="K50" s="49" t="n"/>
+      <c r="L50" s="49" t="n"/>
+      <c r="M50" s="49" t="n"/>
+      <c r="N50" s="49" t="n"/>
+      <c r="O50" s="49" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="49" t="n"/>
+      <c r="C51" s="49" t="n"/>
+      <c r="D51" s="49" t="n"/>
+      <c r="E51" s="49" t="n"/>
+      <c r="F51" s="49" t="n"/>
+      <c r="G51" s="49" t="n"/>
+      <c r="H51" s="49" t="n"/>
+      <c r="I51" s="49" t="n"/>
+      <c r="J51" s="49" t="n"/>
+      <c r="K51" s="49" t="n"/>
+      <c r="L51" s="49" t="n"/>
+      <c r="M51" s="49" t="n"/>
+      <c r="N51" s="49" t="n"/>
+      <c r="O51" s="49" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="49" t="n"/>
+      <c r="C52" s="49" t="n"/>
+      <c r="D52" s="49" t="n"/>
+      <c r="E52" s="49" t="n"/>
+      <c r="F52" s="49" t="n"/>
+      <c r="G52" s="49" t="n"/>
+      <c r="H52" s="49" t="n"/>
+      <c r="I52" s="49" t="n"/>
+      <c r="J52" s="49" t="n"/>
+      <c r="K52" s="49" t="n"/>
+      <c r="L52" s="49" t="n"/>
+      <c r="M52" s="49" t="n"/>
+      <c r="N52" s="49" t="n"/>
+      <c r="O52" s="49" t="n"/>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" s="49" t="n"/>
+      <c r="C53" s="49" t="n"/>
+      <c r="D53" s="49" t="n"/>
+      <c r="E53" s="49" t="n"/>
+      <c r="F53" s="49" t="n"/>
+      <c r="G53" s="49" t="n"/>
+      <c r="H53" s="49" t="n"/>
+      <c r="I53" s="49" t="n"/>
+      <c r="J53" s="49" t="n"/>
+      <c r="K53" s="49" t="n"/>
+      <c r="L53" s="49" t="n"/>
+      <c r="M53" s="49" t="n"/>
+      <c r="N53" s="49" t="n"/>
+      <c r="O53" s="49" t="n"/>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" s="49" t="n"/>
+      <c r="C54" s="49" t="n"/>
+      <c r="D54" s="49" t="n"/>
+      <c r="E54" s="49" t="n"/>
+      <c r="F54" s="49" t="n"/>
+      <c r="G54" s="49" t="n"/>
+      <c r="H54" s="49" t="n"/>
+      <c r="I54" s="49" t="n"/>
+      <c r="J54" s="49" t="n"/>
+      <c r="K54" s="49" t="n"/>
+      <c r="L54" s="49" t="n"/>
+      <c r="M54" s="49" t="n"/>
+      <c r="N54" s="49" t="n"/>
+      <c r="O54" s="49" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>NÓI THẬT GIÙM CHÚNG TÔI (trả lời sau ĐỢT 1; đợt sau có gì đổi ý thì ghi thêm)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="50" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+    </row>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>Điều bạn THÍCH nhất khi dùng app:</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n"/>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="50" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="21" t="n"/>
-      <c r="K48" s="21" t="n"/>
-      <c r="L48" s="21" t="n"/>
-      <c r="M48" s="21" t="n"/>
-      <c r="N48" s="21" t="n"/>
-      <c r="O48" s="21" t="n"/>
-    </row>
-    <row r="49" ht="50" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="50" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="21" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="21" t="n"/>
+      <c r="L57" s="21" t="n"/>
+      <c r="M57" s="21" t="n"/>
+      <c r="N57" s="21" t="n"/>
+      <c r="O57" s="21" t="n"/>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Điều làm bạn KHÓ CHỊU nhất (dù nhỏ xíu):</t>
         </is>
       </c>
-      <c r="B49" s="21" t="n"/>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="50" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
-      <c r="H49" s="21" t="n"/>
-      <c r="I49" s="21" t="n"/>
-      <c r="J49" s="21" t="n"/>
-      <c r="K49" s="21" t="n"/>
-      <c r="L49" s="21" t="n"/>
-      <c r="M49" s="21" t="n"/>
-      <c r="N49" s="21" t="n"/>
-      <c r="O49" s="21" t="n"/>
-    </row>
-    <row r="50" ht="50" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="50" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="21" t="n"/>
+      <c r="I58" s="21" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="21" t="n"/>
+      <c r="L58" s="21" t="n"/>
+      <c r="M58" s="21" t="n"/>
+      <c r="N58" s="21" t="n"/>
+      <c r="O58" s="21" t="n"/>
+    </row>
+    <row r="59" ht="50" customHeight="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Chỗ nào bạn nghĩ học sinh lớp 10 sẽ khựng lại, không biết phải làm gì?</t>
         </is>
       </c>
-      <c r="B50" s="21" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="21" t="n"/>
-      <c r="E50" s="50" t="n"/>
-      <c r="F50" s="21" t="n"/>
-      <c r="G50" s="21" t="n"/>
-      <c r="H50" s="21" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="J50" s="21" t="n"/>
-      <c r="K50" s="21" t="n"/>
-      <c r="L50" s="21" t="n"/>
-      <c r="M50" s="21" t="n"/>
-      <c r="N50" s="21" t="n"/>
-      <c r="O50" s="21" t="n"/>
-    </row>
-    <row r="51" ht="50" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="50" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="21" t="n"/>
+      <c r="L59" s="21" t="n"/>
+      <c r="M59" s="21" t="n"/>
+      <c r="N59" s="21" t="n"/>
+      <c r="O59" s="21" t="n"/>
+    </row>
+    <row r="60" ht="50" customHeight="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Có chỗ nào app nói năng chưa đúng giọng nhà trường, hoặc trẻ con quá / khô khan quá?</t>
         </is>
       </c>
-      <c r="B51" s="21" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
-      <c r="J51" s="21" t="n"/>
-      <c r="K51" s="21" t="n"/>
-      <c r="L51" s="21" t="n"/>
-      <c r="M51" s="21" t="n"/>
-      <c r="N51" s="21" t="n"/>
-      <c r="O51" s="21" t="n"/>
-    </row>
-    <row r="52" ht="50" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="50" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
+      <c r="J60" s="21" t="n"/>
+      <c r="K60" s="21" t="n"/>
+      <c r="L60" s="21" t="n"/>
+      <c r="M60" s="21" t="n"/>
+      <c r="N60" s="21" t="n"/>
+      <c r="O60" s="21" t="n"/>
+    </row>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Nhìn với con mắt PHỤ HUYNH: báo cáo đã đủ để bạn yên tâm chưa? Thiếu gì?</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="50" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="21" t="n"/>
-      <c r="K52" s="21" t="n"/>
-      <c r="L52" s="21" t="n"/>
-      <c r="M52" s="21" t="n"/>
-      <c r="N52" s="21" t="n"/>
-      <c r="O52" s="21" t="n"/>
-    </row>
-    <row r="53" ht="50" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="B61" s="21" t="n"/>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="50" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="21" t="n"/>
+      <c r="J61" s="21" t="n"/>
+      <c r="K61" s="21" t="n"/>
+      <c r="L61" s="21" t="n"/>
+      <c r="M61" s="21" t="n"/>
+      <c r="N61" s="21" t="n"/>
+      <c r="O61" s="21" t="n"/>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Nhìn với con mắt GIÁO VIÊN: chấm bài trên app nhanh hơn hay chậm hơn chấm giấy? Vì sao?</t>
         </is>
       </c>
-      <c r="B53" s="21" t="n"/>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="50" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
-      <c r="H53" s="21" t="n"/>
-      <c r="I53" s="21" t="n"/>
-      <c r="J53" s="21" t="n"/>
-      <c r="K53" s="21" t="n"/>
-      <c r="L53" s="21" t="n"/>
-      <c r="M53" s="21" t="n"/>
-      <c r="N53" s="21" t="n"/>
-      <c r="O53" s="21" t="n"/>
-    </row>
-    <row r="54" ht="50" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>HỌC LIỆU: bạn muốn mỗi bài kèm sẵn thứ gì trước khi em làm câu hỏi — video ngắn, slide, phiếu in ra làm, đề cương, hay không cần gì? Nguồn lấy từ đâu: cô tự soạn, kho của trường, hay link ngoài (YouTube/Drive)?</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="50" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="21" t="n"/>
-      <c r="K54" s="21" t="n"/>
-      <c r="L54" s="21" t="n"/>
-      <c r="M54" s="21" t="n"/>
-      <c r="N54" s="21" t="n"/>
-      <c r="O54" s="21" t="n"/>
-    </row>
-    <row r="55" ht="50" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="50" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+      <c r="J62" s="21" t="n"/>
+      <c r="K62" s="21" t="n"/>
+      <c r="L62" s="21" t="n"/>
+      <c r="M62" s="21" t="n"/>
+      <c r="N62" s="21" t="n"/>
+      <c r="O62" s="21" t="n"/>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>HỌC LIỆU: đăng tài liệu cho một bài mất bao lâu, có chỗ nào rối không? Bạn có thật sự sẽ làm việc này cho từng bài mình dạy không, hay cần trường soạn sẵn rồi bạn chỉ chọn?</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="n"/>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="50" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="21" t="n"/>
+      <c r="L63" s="21" t="n"/>
+      <c r="M63" s="21" t="n"/>
+      <c r="N63" s="21" t="n"/>
+      <c r="O63" s="21" t="n"/>
+    </row>
+    <row r="64" ht="50" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>BA MỨC kho báu: cách chia mức 1-2-3 có hợp với cách bạn dạy không? Mỗi lần chỉ mở một mức (bắt em quay lại) là hay hay phiền? Bạn sẽ xếp thứ gì vào mức 1, thứ gì để mức 3?</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="21" t="n"/>
+      <c r="E64" s="50" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="21" t="n"/>
+      <c r="I64" s="21" t="n"/>
+      <c r="J64" s="21" t="n"/>
+      <c r="K64" s="21" t="n"/>
+      <c r="L64" s="21" t="n"/>
+      <c r="M64" s="21" t="n"/>
+      <c r="N64" s="21" t="n"/>
+      <c r="O64" s="21" t="n"/>
+    </row>
+    <row r="65" ht="50" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Bạn có sẵn sàng cho lớp mình dùng app này không? Nếu chưa, cần sửa gì trước?</t>
         </is>
       </c>
-      <c r="B55" s="21" t="n"/>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="50" t="n"/>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="n"/>
-      <c r="H55" s="21" t="n"/>
-      <c r="I55" s="21" t="n"/>
-      <c r="J55" s="21" t="n"/>
-      <c r="K55" s="21" t="n"/>
-      <c r="L55" s="21" t="n"/>
-      <c r="M55" s="21" t="n"/>
-      <c r="N55" s="21" t="n"/>
-      <c r="O55" s="21" t="n"/>
-    </row>
-    <row r="56" ht="50" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="B65" s="21" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="50" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="21" t="n"/>
+      <c r="K65" s="21" t="n"/>
+      <c r="L65" s="21" t="n"/>
+      <c r="M65" s="21" t="n"/>
+      <c r="N65" s="21" t="n"/>
+      <c r="O65" s="21" t="n"/>
+    </row>
+    <row r="66" ht="50" customHeight="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Nếu chỉ được sửa MỘT thứ trước khi cho học sinh dùng thật, bạn chọn sửa gì?</t>
         </is>
       </c>
-      <c r="B56" s="21" t="n"/>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="50" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="21" t="n"/>
-      <c r="I56" s="21" t="n"/>
-      <c r="J56" s="21" t="n"/>
-      <c r="K56" s="21" t="n"/>
-      <c r="L56" s="21" t="n"/>
-      <c r="M56" s="21" t="n"/>
-      <c r="N56" s="21" t="n"/>
-      <c r="O56" s="21" t="n"/>
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="50" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="21" t="n"/>
+      <c r="K66" s="21" t="n"/>
+      <c r="L66" s="21" t="n"/>
+      <c r="M66" s="21" t="n"/>
+      <c r="N66" s="21" t="n"/>
+      <c r="O66" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
-    <mergeCell ref="E53:O53"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:O34"/>
+  <mergeCells count="72">
     <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E50:O50"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="K33:O33"/>
-    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E58:O58"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="A41:O41"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="E54:H54"/>
     <mergeCell ref="I45:J45"/>
-    <mergeCell ref="E55:O55"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="K36:O36"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E56:O56"/>
+    <mergeCell ref="E62:O62"/>
+    <mergeCell ref="K54:O54"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="K45:O45"/>
-    <mergeCell ref="E52:O52"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E48:O48"/>
-    <mergeCell ref="K35:O35"/>
+    <mergeCell ref="A56:O56"/>
+    <mergeCell ref="E64:O64"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="E51:O51"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="K51:O51"/>
+    <mergeCell ref="E53:H53"/>
     <mergeCell ref="E43:H43"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="A47:O47"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="I54:J54"/>
+    <mergeCell ref="K47:O47"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K41:O41"/>
+    <mergeCell ref="K50:O50"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="K44:O44"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="E63:O63"/>
+    <mergeCell ref="I53:J53"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="K46:O46"/>
+    <mergeCell ref="E42:H42"/>
     <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="K40:O40"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="I3:J3"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E60:O60"/>
     <mergeCell ref="I43:J43"/>
-    <mergeCell ref="A20:O20"/>
-    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E65:O65"/>
+    <mergeCell ref="K52:O52"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="K43:O43"/>
-    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="A28:O28"/>
     <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E59:O59"/>
     <mergeCell ref="E44:H44"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="K42:O42"/>
-    <mergeCell ref="E49:O49"/>
+    <mergeCell ref="A65:D65"/>
     <mergeCell ref="M3:N3"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="A66:D66"/>
     <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="E61:O61"/>
     <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E54:O54"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="K53:O53"/>
+    <mergeCell ref="E57:O57"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="K38:O38"/>
-    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="K37:O37"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E66:O66"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="K49:O49"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E21 E22 E23 E25 E26 E27 E28 E29 E30 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G21 G22 G23 G25 G26 G27 G28 G29 G30 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I21 I22 I23 I25 I26 I27 I28 I29 I30 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K21 K22 K23 K25 K26 K27 K28 K29 K30 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M21 M22 M23 M25 M26 M27 M28 M29 M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E25 E26 E27 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G25 G26 G27 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I25 I26 I27 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K25 K26 K27 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M25 M26 M27 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng như mô tả,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O21 O22 O23 O25 O26 O27 O28 O29 O30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O25 O26 O27 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation sqref="I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Chặn hẳn không đi tiếp được,Khó chịu nhưng vẫn làm được,Góp ý cho đẹp hơn"</formula1>
     </dataValidation>
-    <dataValidation sqref="B34 B35 B36 B37 B38 B39 B40 B41 B42 B43 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B43 B44 B45 B46 B47 B48 B49 B50 B51 B52 B53 B54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6195,7 +7149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6696,6 +7650,126 @@
       <c r="O12" s="46" t="n"/>
       <c r="P12" s="46" t="n"/>
     </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>KB9 · Thầy cô đăng, cả lớp cùng thấy</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Vào gv1 → tab Học liệu → thêm MỘT học liệu mức 1 cho bài 'Khái niệm mệnh đề logic'.</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs2, mở lộ trình, tìm hộp quà vàng cạnh bài đó.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs3, mở lộ trình, tìm hộp quà vàng cạnh bài đó.</t>
+        </is>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>Cả hai em đều thấy hộp quà mới (học liệu gắn theo BÀI nên mọi lớp học bài đó đều thấy). Không phải tạo lại cho từng lớp.</t>
+        </is>
+      </c>
+      <c r="G13" s="42" t="n"/>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="43" t="n"/>
+      <c r="J13" s="43" t="n"/>
+      <c r="K13" s="44" t="n"/>
+      <c r="L13" s="44" t="n"/>
+      <c r="M13" s="45" t="n"/>
+      <c r="N13" s="45" t="n"/>
+      <c r="O13" s="46" t="n"/>
+      <c r="P13" s="46" t="n"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>KB10 · Mỗi em một tiến trình kho báu</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs1 → mở kho báu → bấm XEM XONG MỨC 1 → thoát ra, mở lại → bấm XEM XONG MỨC 2.</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs2 → mở kho báu → bấm XEM XONG MỨC 1 rồi thôi.</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs3 → chỉ mở kho báu xem, KHÔNG bấm xem xong.</t>
+        </is>
+      </c>
+      <c r="F14" s="51" t="inlineStr">
+        <is>
+          <t>Ba hộp quà đọc ba số khác nhau (2/3 · 1/3 · 0/3). Không em nào bị ảnh hưởng bởi tiến trình của em khác.</t>
+        </is>
+      </c>
+      <c r="G14" s="42" t="n"/>
+      <c r="H14" s="42" t="n"/>
+      <c r="I14" s="43" t="n"/>
+      <c r="J14" s="43" t="n"/>
+      <c r="K14" s="44" t="n"/>
+      <c r="L14" s="44" t="n"/>
+      <c r="M14" s="45" t="n"/>
+      <c r="N14" s="45" t="n"/>
+      <c r="O14" s="46" t="n"/>
+      <c r="P14" s="46" t="n"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>KB11 · Tắt con mắt là học sinh hết thấy</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Vào gv1 → tab Học liệu → bấm con mắt TẮT một mục ở mức 1 của bài đó.</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs2, mở lại kho báu bài đó (tải lại trang).</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Vào hs3, mở lại kho báu bài đó (tải lại trang).</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="inlineStr">
+        <is>
+          <t>Mục vừa tắt biến mất khỏi màn hình cả hai em, các mục còn lại vẫn nguyên. Bật lại thì nó hiện lại.</t>
+        </is>
+      </c>
+      <c r="G15" s="42" t="n"/>
+      <c r="H15" s="42" t="n"/>
+      <c r="I15" s="43" t="n"/>
+      <c r="J15" s="43" t="n"/>
+      <c r="K15" s="44" t="n"/>
+      <c r="L15" s="44" t="n"/>
+      <c r="M15" s="45" t="n"/>
+      <c r="N15" s="45" t="n"/>
+      <c r="O15" s="46" t="n"/>
+      <c r="P15" s="46" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="O3:P3"/>
@@ -6708,7 +7782,7 @@
     <mergeCell ref="I3:J3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 I5 I6 I7 I8 I9 I10 I11 I12 K5 K6 K7 K8 K9 K10 K11 K12 M5 M6 M7 M8 M9 M10 M11 M12 O5 O6 O7 O8 O9 O10 O11 O12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Đúng vậy,Một phần,Không đúng,Chưa thử"</formula1>
     </dataValidation>
   </dataValidations>
@@ -53514,7 +54588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -53729,7 +54803,7 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Nhìn phần ĐẦU bài, phía trên câu hỏi đầu tiên — chỗ dành cho học liệu (slide, video, podcast, phiếu bài tập).</t>
+          <t>Nhìn CẠNH bàn chân bài đầu tiên — tìm dấu chân vàng hình hộp quà (kho báu học liệu).</t>
         </is>
       </c>
       <c r="D7" s="58">
@@ -53768,7 +54842,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
+          <t>Bấm vào hộp quà vàng.</t>
         </is>
       </c>
       <c r="D8" s="58">
@@ -53796,7 +54870,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="41" t="n">
         <v>6</v>
       </c>
@@ -53807,7 +54881,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>CỐ TÌNH chọn sai một câu.</t>
+          <t>Mở thử từng kiểu học liệu: nghe podcast, xem ảnh sơ đồ, mở video, tải phiếu bài tập.</t>
         </is>
       </c>
       <c r="D9" s="58">
@@ -53846,7 +54920,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
+          <t>Bấm 'XEM XONG MỨC 1', rồi thử mở lại kho báu ngay lập tức.</t>
         </is>
       </c>
       <c r="D10" s="58">
@@ -53885,7 +54959,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
+          <t>Cuộn xuống một bài còn KHOÁ ở phía sau, thử bấm kho báu của bài đó.</t>
         </is>
       </c>
       <c r="D11" s="58">
@@ -53924,7 +54998,7 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
+          <t>Làm câu 1 → 4 (tra sheet ĐÁP ÁN TOÁN 10, lọc cột 'Bài').</t>
         </is>
       </c>
       <c r="D12" s="58">
@@ -53963,7 +55037,7 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
+          <t>CỐ TÌNH chọn sai một câu.</t>
         </is>
       </c>
       <c r="D13" s="58">
@@ -54002,7 +55076,7 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
+          <t>Làm câu 5 — đề chia Bước 1 / Bước 2 / Bước 3.</t>
         </is>
       </c>
       <c r="D14" s="58">
@@ -54041,7 +55115,7 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
+          <t>Câu 6 là dạng NỘP BÀI. Gõ vài câu vào ô rồi bấm NỘP BÀI.</t>
         </is>
       </c>
       <c r="D15" s="58">
@@ -54080,7 +55154,7 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
+          <t>Nếu trợ lý bảo còn thiếu ý — bổ sung rồi bấm NỘP LẠI.</t>
         </is>
       </c>
       <c r="D16" s="58">
@@ -54119,7 +55193,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
+          <t>Câu 7 hoặc 8: nộp bằng ẢNH (chụp hoặc chọn ảnh bất kỳ).</t>
         </is>
       </c>
       <c r="D17" s="58">
@@ -54153,36 +55227,36 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
+          <t>Làm nốt các câu còn lại rồi thoát ra lộ trình.</t>
         </is>
       </c>
       <c r="D18" s="58">
-        <f>COUNTIF('Người thử 1'!E21,"Một phần")+COUNTIF('Người thử 1'!E21,"Không đúng")+COUNTIF('Người thử 2'!E21,"Một phần")+COUNTIF('Người thử 2'!E21,"Không đúng")+COUNTIF('Người thử 3'!E21,"Một phần")+COUNTIF('Người thử 3'!E21,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E20,"Một phần")+COUNTIF('Người thử 1'!E20,"Không đúng")+COUNTIF('Người thử 2'!E20,"Một phần")+COUNTIF('Người thử 2'!E20,"Không đúng")+COUNTIF('Người thử 3'!E20,"Một phần")+COUNTIF('Người thử 3'!E20,"Không đúng")</f>
         <v/>
       </c>
       <c r="E18" s="59">
-        <f>COUNTIF('Người thử 1'!G21,"Một phần")+COUNTIF('Người thử 1'!G21,"Không đúng")+COUNTIF('Người thử 2'!G21,"Một phần")+COUNTIF('Người thử 2'!G21,"Không đúng")+COUNTIF('Người thử 3'!G21,"Một phần")+COUNTIF('Người thử 3'!G21,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G20,"Một phần")+COUNTIF('Người thử 1'!G20,"Không đúng")+COUNTIF('Người thử 2'!G20,"Một phần")+COUNTIF('Người thử 2'!G20,"Không đúng")+COUNTIF('Người thử 3'!G20,"Một phần")+COUNTIF('Người thử 3'!G20,"Không đúng")</f>
         <v/>
       </c>
       <c r="F18" s="60">
-        <f>COUNTIF('Người thử 1'!I21,"Một phần")+COUNTIF('Người thử 1'!I21,"Không đúng")+COUNTIF('Người thử 2'!I21,"Một phần")+COUNTIF('Người thử 2'!I21,"Không đúng")+COUNTIF('Người thử 3'!I21,"Một phần")+COUNTIF('Người thử 3'!I21,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I20,"Một phần")+COUNTIF('Người thử 1'!I20,"Không đúng")+COUNTIF('Người thử 2'!I20,"Một phần")+COUNTIF('Người thử 2'!I20,"Không đúng")+COUNTIF('Người thử 3'!I20,"Một phần")+COUNTIF('Người thử 3'!I20,"Không đúng")</f>
         <v/>
       </c>
       <c r="G18" s="61">
-        <f>COUNTIF('Người thử 1'!K21,"Một phần")+COUNTIF('Người thử 1'!K21,"Không đúng")+COUNTIF('Người thử 2'!K21,"Một phần")+COUNTIF('Người thử 2'!K21,"Không đúng")+COUNTIF('Người thử 3'!K21,"Một phần")+COUNTIF('Người thử 3'!K21,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K20,"Một phần")+COUNTIF('Người thử 1'!K20,"Không đúng")+COUNTIF('Người thử 2'!K20,"Một phần")+COUNTIF('Người thử 2'!K20,"Không đúng")+COUNTIF('Người thử 3'!K20,"Một phần")+COUNTIF('Người thử 3'!K20,"Không đúng")</f>
         <v/>
       </c>
       <c r="H18" s="62">
-        <f>COUNTIF('Người thử 1'!M21,"Một phần")+COUNTIF('Người thử 1'!M21,"Không đúng")+COUNTIF('Người thử 2'!M21,"Một phần")+COUNTIF('Người thử 2'!M21,"Không đúng")+COUNTIF('Người thử 3'!M21,"Một phần")+COUNTIF('Người thử 3'!M21,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M20,"Một phần")+COUNTIF('Người thử 1'!M20,"Không đúng")+COUNTIF('Người thử 2'!M20,"Một phần")+COUNTIF('Người thử 2'!M20,"Không đúng")+COUNTIF('Người thử 3'!M20,"Một phần")+COUNTIF('Người thử 3'!M20,"Không đúng")</f>
         <v/>
       </c>
       <c r="I18" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O21,'Người thử 2'!O21,'Người thử 3'!O21),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O20,'Người thử 2'!O20,'Người thử 3'!O20),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54192,36 +55266,36 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
+          <t>Bấm lần lượt 4 mục dưới cùng: Ôn tập · Hạng · Mục tiêu · Tôi.</t>
         </is>
       </c>
       <c r="D19" s="58">
-        <f>COUNTIF('Người thử 1'!E22,"Một phần")+COUNTIF('Người thử 1'!E22,"Không đúng")+COUNTIF('Người thử 2'!E22,"Một phần")+COUNTIF('Người thử 2'!E22,"Không đúng")+COUNTIF('Người thử 3'!E22,"Một phần")+COUNTIF('Người thử 3'!E22,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E21,"Một phần")+COUNTIF('Người thử 1'!E21,"Không đúng")+COUNTIF('Người thử 2'!E21,"Một phần")+COUNTIF('Người thử 2'!E21,"Không đúng")+COUNTIF('Người thử 3'!E21,"Một phần")+COUNTIF('Người thử 3'!E21,"Không đúng")</f>
         <v/>
       </c>
       <c r="E19" s="59">
-        <f>COUNTIF('Người thử 1'!G22,"Một phần")+COUNTIF('Người thử 1'!G22,"Không đúng")+COUNTIF('Người thử 2'!G22,"Một phần")+COUNTIF('Người thử 2'!G22,"Không đúng")+COUNTIF('Người thử 3'!G22,"Một phần")+COUNTIF('Người thử 3'!G22,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G21,"Một phần")+COUNTIF('Người thử 1'!G21,"Không đúng")+COUNTIF('Người thử 2'!G21,"Một phần")+COUNTIF('Người thử 2'!G21,"Không đúng")+COUNTIF('Người thử 3'!G21,"Một phần")+COUNTIF('Người thử 3'!G21,"Không đúng")</f>
         <v/>
       </c>
       <c r="F19" s="60">
-        <f>COUNTIF('Người thử 1'!I22,"Một phần")+COUNTIF('Người thử 1'!I22,"Không đúng")+COUNTIF('Người thử 2'!I22,"Một phần")+COUNTIF('Người thử 2'!I22,"Không đúng")+COUNTIF('Người thử 3'!I22,"Một phần")+COUNTIF('Người thử 3'!I22,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I21,"Một phần")+COUNTIF('Người thử 1'!I21,"Không đúng")+COUNTIF('Người thử 2'!I21,"Một phần")+COUNTIF('Người thử 2'!I21,"Không đúng")+COUNTIF('Người thử 3'!I21,"Một phần")+COUNTIF('Người thử 3'!I21,"Không đúng")</f>
         <v/>
       </c>
       <c r="G19" s="61">
-        <f>COUNTIF('Người thử 1'!K22,"Một phần")+COUNTIF('Người thử 1'!K22,"Không đúng")+COUNTIF('Người thử 2'!K22,"Một phần")+COUNTIF('Người thử 2'!K22,"Không đúng")+COUNTIF('Người thử 3'!K22,"Một phần")+COUNTIF('Người thử 3'!K22,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K21,"Một phần")+COUNTIF('Người thử 1'!K21,"Không đúng")+COUNTIF('Người thử 2'!K21,"Một phần")+COUNTIF('Người thử 2'!K21,"Không đúng")+COUNTIF('Người thử 3'!K21,"Một phần")+COUNTIF('Người thử 3'!K21,"Không đúng")</f>
         <v/>
       </c>
       <c r="H19" s="62">
-        <f>COUNTIF('Người thử 1'!M22,"Một phần")+COUNTIF('Người thử 1'!M22,"Không đúng")+COUNTIF('Người thử 2'!M22,"Một phần")+COUNTIF('Người thử 2'!M22,"Không đúng")+COUNTIF('Người thử 3'!M22,"Một phần")+COUNTIF('Người thử 3'!M22,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M21,"Một phần")+COUNTIF('Người thử 1'!M21,"Không đúng")+COUNTIF('Người thử 2'!M21,"Một phần")+COUNTIF('Người thử 2'!M21,"Không đúng")+COUNTIF('Người thử 3'!M21,"Một phần")+COUNTIF('Người thử 3'!M21,"Không đúng")</f>
         <v/>
       </c>
       <c r="I19" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O22,'Người thử 2'!O22,'Người thử 3'!O22),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O21,'Người thử 2'!O21,'Người thử 3'!O21),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54231,36 +55305,36 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Phụ Huynh</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
+          <t>Cuộn hết lộ trình từ đầu tới cuối, xem qua tên các bài của cả 9 chương.</t>
         </is>
       </c>
       <c r="D20" s="58">
-        <f>COUNTIF('Người thử 1'!E23,"Một phần")+COUNTIF('Người thử 1'!E23,"Không đúng")+COUNTIF('Người thử 2'!E23,"Một phần")+COUNTIF('Người thử 2'!E23,"Không đúng")+COUNTIF('Người thử 3'!E23,"Một phần")+COUNTIF('Người thử 3'!E23,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E22,"Một phần")+COUNTIF('Người thử 1'!E22,"Không đúng")+COUNTIF('Người thử 2'!E22,"Một phần")+COUNTIF('Người thử 2'!E22,"Không đúng")+COUNTIF('Người thử 3'!E22,"Một phần")+COUNTIF('Người thử 3'!E22,"Không đúng")</f>
         <v/>
       </c>
       <c r="E20" s="59">
-        <f>COUNTIF('Người thử 1'!G23,"Một phần")+COUNTIF('Người thử 1'!G23,"Không đúng")+COUNTIF('Người thử 2'!G23,"Một phần")+COUNTIF('Người thử 2'!G23,"Không đúng")+COUNTIF('Người thử 3'!G23,"Một phần")+COUNTIF('Người thử 3'!G23,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G22,"Một phần")+COUNTIF('Người thử 1'!G22,"Không đúng")+COUNTIF('Người thử 2'!G22,"Một phần")+COUNTIF('Người thử 2'!G22,"Không đúng")+COUNTIF('Người thử 3'!G22,"Một phần")+COUNTIF('Người thử 3'!G22,"Không đúng")</f>
         <v/>
       </c>
       <c r="F20" s="60">
-        <f>COUNTIF('Người thử 1'!I23,"Một phần")+COUNTIF('Người thử 1'!I23,"Không đúng")+COUNTIF('Người thử 2'!I23,"Một phần")+COUNTIF('Người thử 2'!I23,"Không đúng")+COUNTIF('Người thử 3'!I23,"Một phần")+COUNTIF('Người thử 3'!I23,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I22,"Một phần")+COUNTIF('Người thử 1'!I22,"Không đúng")+COUNTIF('Người thử 2'!I22,"Một phần")+COUNTIF('Người thử 2'!I22,"Không đúng")+COUNTIF('Người thử 3'!I22,"Một phần")+COUNTIF('Người thử 3'!I22,"Không đúng")</f>
         <v/>
       </c>
       <c r="G20" s="61">
-        <f>COUNTIF('Người thử 1'!K23,"Một phần")+COUNTIF('Người thử 1'!K23,"Không đúng")+COUNTIF('Người thử 2'!K23,"Một phần")+COUNTIF('Người thử 2'!K23,"Không đúng")+COUNTIF('Người thử 3'!K23,"Một phần")+COUNTIF('Người thử 3'!K23,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K22,"Một phần")+COUNTIF('Người thử 1'!K22,"Không đúng")+COUNTIF('Người thử 2'!K22,"Một phần")+COUNTIF('Người thử 2'!K22,"Không đúng")+COUNTIF('Người thử 3'!K22,"Một phần")+COUNTIF('Người thử 3'!K22,"Không đúng")</f>
         <v/>
       </c>
       <c r="H20" s="62">
-        <f>COUNTIF('Người thử 1'!M23,"Một phần")+COUNTIF('Người thử 1'!M23,"Không đúng")+COUNTIF('Người thử 2'!M23,"Một phần")+COUNTIF('Người thử 2'!M23,"Không đúng")+COUNTIF('Người thử 3'!M23,"Một phần")+COUNTIF('Người thử 3'!M23,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M22,"Một phần")+COUNTIF('Người thử 1'!M22,"Không đúng")+COUNTIF('Người thử 2'!M22,"Một phần")+COUNTIF('Người thử 2'!M22,"Không đúng")+COUNTIF('Người thử 3'!M22,"Một phần")+COUNTIF('Người thử 3'!M22,"Không đúng")</f>
         <v/>
       </c>
       <c r="I20" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O23,'Người thử 2'!O23,'Người thử 3'!O23),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O22,'Người thử 2'!O22,'Người thử 3'!O22),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54270,36 +55344,36 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Học Sinh</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
+          <t>Mở lại app bằng ĐIỆN THOẠI, làm 2–3 câu.</t>
         </is>
       </c>
       <c r="D21" s="58">
-        <f>COUNTIF('Người thử 1'!E25,"Một phần")+COUNTIF('Người thử 1'!E25,"Không đúng")+COUNTIF('Người thử 2'!E25,"Một phần")+COUNTIF('Người thử 2'!E25,"Không đúng")+COUNTIF('Người thử 3'!E25,"Một phần")+COUNTIF('Người thử 3'!E25,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E23,"Một phần")+COUNTIF('Người thử 1'!E23,"Không đúng")+COUNTIF('Người thử 2'!E23,"Một phần")+COUNTIF('Người thử 2'!E23,"Không đúng")+COUNTIF('Người thử 3'!E23,"Một phần")+COUNTIF('Người thử 3'!E23,"Không đúng")</f>
         <v/>
       </c>
       <c r="E21" s="59">
-        <f>COUNTIF('Người thử 1'!G25,"Một phần")+COUNTIF('Người thử 1'!G25,"Không đúng")+COUNTIF('Người thử 2'!G25,"Một phần")+COUNTIF('Người thử 2'!G25,"Không đúng")+COUNTIF('Người thử 3'!G25,"Một phần")+COUNTIF('Người thử 3'!G25,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G23,"Một phần")+COUNTIF('Người thử 1'!G23,"Không đúng")+COUNTIF('Người thử 2'!G23,"Một phần")+COUNTIF('Người thử 2'!G23,"Không đúng")+COUNTIF('Người thử 3'!G23,"Một phần")+COUNTIF('Người thử 3'!G23,"Không đúng")</f>
         <v/>
       </c>
       <c r="F21" s="60">
-        <f>COUNTIF('Người thử 1'!I25,"Một phần")+COUNTIF('Người thử 1'!I25,"Không đúng")+COUNTIF('Người thử 2'!I25,"Một phần")+COUNTIF('Người thử 2'!I25,"Không đúng")+COUNTIF('Người thử 3'!I25,"Một phần")+COUNTIF('Người thử 3'!I25,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I23,"Một phần")+COUNTIF('Người thử 1'!I23,"Không đúng")+COUNTIF('Người thử 2'!I23,"Một phần")+COUNTIF('Người thử 2'!I23,"Không đúng")+COUNTIF('Người thử 3'!I23,"Một phần")+COUNTIF('Người thử 3'!I23,"Không đúng")</f>
         <v/>
       </c>
       <c r="G21" s="61">
-        <f>COUNTIF('Người thử 1'!K25,"Một phần")+COUNTIF('Người thử 1'!K25,"Không đúng")+COUNTIF('Người thử 2'!K25,"Một phần")+COUNTIF('Người thử 2'!K25,"Không đúng")+COUNTIF('Người thử 3'!K25,"Một phần")+COUNTIF('Người thử 3'!K25,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K23,"Một phần")+COUNTIF('Người thử 1'!K23,"Không đúng")+COUNTIF('Người thử 2'!K23,"Một phần")+COUNTIF('Người thử 2'!K23,"Không đúng")+COUNTIF('Người thử 3'!K23,"Một phần")+COUNTIF('Người thử 3'!K23,"Không đúng")</f>
         <v/>
       </c>
       <c r="H21" s="62">
-        <f>COUNTIF('Người thử 1'!M25,"Một phần")+COUNTIF('Người thử 1'!M25,"Không đúng")+COUNTIF('Người thử 2'!M25,"Một phần")+COUNTIF('Người thử 2'!M25,"Không đúng")+COUNTIF('Người thử 3'!M25,"Một phần")+COUNTIF('Người thử 3'!M25,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M23,"Một phần")+COUNTIF('Người thử 1'!M23,"Không đúng")+COUNTIF('Người thử 2'!M23,"Một phần")+COUNTIF('Người thử 2'!M23,"Không đúng")+COUNTIF('Người thử 3'!M23,"Một phần")+COUNTIF('Người thử 3'!M23,"Không đúng")</f>
         <v/>
       </c>
       <c r="I21" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O25,'Người thử 2'!O25,'Người thử 3'!O25),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O23,'Người thử 2'!O23,'Người thử 3'!O23),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54309,36 +55383,36 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Vào tab HỌC SINH.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản PHỤ HUYNH của bạn.</t>
         </is>
       </c>
       <c r="D22" s="58">
-        <f>COUNTIF('Người thử 1'!E26,"Một phần")+COUNTIF('Người thử 1'!E26,"Không đúng")+COUNTIF('Người thử 2'!E26,"Một phần")+COUNTIF('Người thử 2'!E26,"Không đúng")+COUNTIF('Người thử 3'!E26,"Một phần")+COUNTIF('Người thử 3'!E26,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E25,"Một phần")+COUNTIF('Người thử 1'!E25,"Không đúng")+COUNTIF('Người thử 2'!E25,"Một phần")+COUNTIF('Người thử 2'!E25,"Không đúng")+COUNTIF('Người thử 3'!E25,"Một phần")+COUNTIF('Người thử 3'!E25,"Không đúng")</f>
         <v/>
       </c>
       <c r="E22" s="59">
-        <f>COUNTIF('Người thử 1'!G26,"Một phần")+COUNTIF('Người thử 1'!G26,"Không đúng")+COUNTIF('Người thử 2'!G26,"Một phần")+COUNTIF('Người thử 2'!G26,"Không đúng")+COUNTIF('Người thử 3'!G26,"Một phần")+COUNTIF('Người thử 3'!G26,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G25,"Một phần")+COUNTIF('Người thử 1'!G25,"Không đúng")+COUNTIF('Người thử 2'!G25,"Một phần")+COUNTIF('Người thử 2'!G25,"Không đúng")+COUNTIF('Người thử 3'!G25,"Một phần")+COUNTIF('Người thử 3'!G25,"Không đúng")</f>
         <v/>
       </c>
       <c r="F22" s="60">
-        <f>COUNTIF('Người thử 1'!I26,"Một phần")+COUNTIF('Người thử 1'!I26,"Không đúng")+COUNTIF('Người thử 2'!I26,"Một phần")+COUNTIF('Người thử 2'!I26,"Không đúng")+COUNTIF('Người thử 3'!I26,"Một phần")+COUNTIF('Người thử 3'!I26,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I25,"Một phần")+COUNTIF('Người thử 1'!I25,"Không đúng")+COUNTIF('Người thử 2'!I25,"Một phần")+COUNTIF('Người thử 2'!I25,"Không đúng")+COUNTIF('Người thử 3'!I25,"Một phần")+COUNTIF('Người thử 3'!I25,"Không đúng")</f>
         <v/>
       </c>
       <c r="G22" s="61">
-        <f>COUNTIF('Người thử 1'!K26,"Một phần")+COUNTIF('Người thử 1'!K26,"Không đúng")+COUNTIF('Người thử 2'!K26,"Một phần")+COUNTIF('Người thử 2'!K26,"Không đúng")+COUNTIF('Người thử 3'!K26,"Một phần")+COUNTIF('Người thử 3'!K26,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K25,"Một phần")+COUNTIF('Người thử 1'!K25,"Không đúng")+COUNTIF('Người thử 2'!K25,"Một phần")+COUNTIF('Người thử 2'!K25,"Không đúng")+COUNTIF('Người thử 3'!K25,"Một phần")+COUNTIF('Người thử 3'!K25,"Không đúng")</f>
         <v/>
       </c>
       <c r="H22" s="62">
-        <f>COUNTIF('Người thử 1'!M26,"Một phần")+COUNTIF('Người thử 1'!M26,"Không đúng")+COUNTIF('Người thử 2'!M26,"Một phần")+COUNTIF('Người thử 2'!M26,"Không đúng")+COUNTIF('Người thử 3'!M26,"Một phần")+COUNTIF('Người thử 3'!M26,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M25,"Một phần")+COUNTIF('Người thử 1'!M25,"Không đúng")+COUNTIF('Người thử 2'!M25,"Một phần")+COUNTIF('Người thử 2'!M25,"Không đúng")+COUNTIF('Người thử 3'!M25,"Một phần")+COUNTIF('Người thử 3'!M25,"Không đúng")</f>
         <v/>
       </c>
       <c r="I22" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O26,'Người thử 2'!O26,'Người thử 3'!O26),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O25,'Người thử 2'!O25,'Người thử 3'!O25),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54348,36 +55422,36 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Vào tab CHẤM BÀI.</t>
+          <t>⚠ Đếm xem có bao nhiêu tên học sinh hiện ra.</t>
         </is>
       </c>
       <c r="D23" s="58">
-        <f>COUNTIF('Người thử 1'!E27,"Một phần")+COUNTIF('Người thử 1'!E27,"Không đúng")+COUNTIF('Người thử 2'!E27,"Một phần")+COUNTIF('Người thử 2'!E27,"Không đúng")+COUNTIF('Người thử 3'!E27,"Một phần")+COUNTIF('Người thử 3'!E27,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E26,"Một phần")+COUNTIF('Người thử 1'!E26,"Không đúng")+COUNTIF('Người thử 2'!E26,"Một phần")+COUNTIF('Người thử 2'!E26,"Không đúng")+COUNTIF('Người thử 3'!E26,"Một phần")+COUNTIF('Người thử 3'!E26,"Không đúng")</f>
         <v/>
       </c>
       <c r="E23" s="59">
-        <f>COUNTIF('Người thử 1'!G27,"Một phần")+COUNTIF('Người thử 1'!G27,"Không đúng")+COUNTIF('Người thử 2'!G27,"Một phần")+COUNTIF('Người thử 2'!G27,"Không đúng")+COUNTIF('Người thử 3'!G27,"Một phần")+COUNTIF('Người thử 3'!G27,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G26,"Một phần")+COUNTIF('Người thử 1'!G26,"Không đúng")+COUNTIF('Người thử 2'!G26,"Một phần")+COUNTIF('Người thử 2'!G26,"Không đúng")+COUNTIF('Người thử 3'!G26,"Một phần")+COUNTIF('Người thử 3'!G26,"Không đúng")</f>
         <v/>
       </c>
       <c r="F23" s="60">
-        <f>COUNTIF('Người thử 1'!I27,"Một phần")+COUNTIF('Người thử 1'!I27,"Không đúng")+COUNTIF('Người thử 2'!I27,"Một phần")+COUNTIF('Người thử 2'!I27,"Không đúng")+COUNTIF('Người thử 3'!I27,"Một phần")+COUNTIF('Người thử 3'!I27,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I26,"Một phần")+COUNTIF('Người thử 1'!I26,"Không đúng")+COUNTIF('Người thử 2'!I26,"Một phần")+COUNTIF('Người thử 2'!I26,"Không đúng")+COUNTIF('Người thử 3'!I26,"Một phần")+COUNTIF('Người thử 3'!I26,"Không đúng")</f>
         <v/>
       </c>
       <c r="G23" s="61">
-        <f>COUNTIF('Người thử 1'!K27,"Một phần")+COUNTIF('Người thử 1'!K27,"Không đúng")+COUNTIF('Người thử 2'!K27,"Một phần")+COUNTIF('Người thử 2'!K27,"Không đúng")+COUNTIF('Người thử 3'!K27,"Một phần")+COUNTIF('Người thử 3'!K27,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K26,"Một phần")+COUNTIF('Người thử 1'!K26,"Không đúng")+COUNTIF('Người thử 2'!K26,"Một phần")+COUNTIF('Người thử 2'!K26,"Không đúng")+COUNTIF('Người thử 3'!K26,"Một phần")+COUNTIF('Người thử 3'!K26,"Không đúng")</f>
         <v/>
       </c>
       <c r="H23" s="62">
-        <f>COUNTIF('Người thử 1'!M27,"Một phần")+COUNTIF('Người thử 1'!M27,"Không đúng")+COUNTIF('Người thử 2'!M27,"Một phần")+COUNTIF('Người thử 2'!M27,"Không đúng")+COUNTIF('Người thử 3'!M27,"Một phần")+COUNTIF('Người thử 3'!M27,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M26,"Một phần")+COUNTIF('Người thử 1'!M26,"Không đúng")+COUNTIF('Người thử 2'!M26,"Một phần")+COUNTIF('Người thử 2'!M26,"Không đúng")+COUNTIF('Người thử 3'!M26,"Một phần")+COUNTIF('Người thử 3'!M26,"Không đúng")</f>
         <v/>
       </c>
       <c r="I23" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O27,'Người thử 2'!O27,'Người thử 3'!O27),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O26,'Người thử 2'!O26,'Người thử 3'!O26),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54387,36 +55461,36 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Giáo Viên</t>
+          <t>Phụ Huynh</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+          <t>Đọc kỹ báo cáo bằng con mắt phụ huynh thật.</t>
         </is>
       </c>
       <c r="D24" s="58">
-        <f>COUNTIF('Người thử 1'!E28,"Một phần")+COUNTIF('Người thử 1'!E28,"Không đúng")+COUNTIF('Người thử 2'!E28,"Một phần")+COUNTIF('Người thử 2'!E28,"Không đúng")+COUNTIF('Người thử 3'!E28,"Một phần")+COUNTIF('Người thử 3'!E28,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!E27,"Một phần")+COUNTIF('Người thử 1'!E27,"Không đúng")+COUNTIF('Người thử 2'!E27,"Một phần")+COUNTIF('Người thử 2'!E27,"Không đúng")+COUNTIF('Người thử 3'!E27,"Một phần")+COUNTIF('Người thử 3'!E27,"Không đúng")</f>
         <v/>
       </c>
       <c r="E24" s="59">
-        <f>COUNTIF('Người thử 1'!G28,"Một phần")+COUNTIF('Người thử 1'!G28,"Không đúng")+COUNTIF('Người thử 2'!G28,"Một phần")+COUNTIF('Người thử 2'!G28,"Không đúng")+COUNTIF('Người thử 3'!G28,"Một phần")+COUNTIF('Người thử 3'!G28,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!G27,"Một phần")+COUNTIF('Người thử 1'!G27,"Không đúng")+COUNTIF('Người thử 2'!G27,"Một phần")+COUNTIF('Người thử 2'!G27,"Không đúng")+COUNTIF('Người thử 3'!G27,"Một phần")+COUNTIF('Người thử 3'!G27,"Không đúng")</f>
         <v/>
       </c>
       <c r="F24" s="60">
-        <f>COUNTIF('Người thử 1'!I28,"Một phần")+COUNTIF('Người thử 1'!I28,"Không đúng")+COUNTIF('Người thử 2'!I28,"Một phần")+COUNTIF('Người thử 2'!I28,"Không đúng")+COUNTIF('Người thử 3'!I28,"Một phần")+COUNTIF('Người thử 3'!I28,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!I27,"Một phần")+COUNTIF('Người thử 1'!I27,"Không đúng")+COUNTIF('Người thử 2'!I27,"Một phần")+COUNTIF('Người thử 2'!I27,"Không đúng")+COUNTIF('Người thử 3'!I27,"Một phần")+COUNTIF('Người thử 3'!I27,"Không đúng")</f>
         <v/>
       </c>
       <c r="G24" s="61">
-        <f>COUNTIF('Người thử 1'!K28,"Một phần")+COUNTIF('Người thử 1'!K28,"Không đúng")+COUNTIF('Người thử 2'!K28,"Một phần")+COUNTIF('Người thử 2'!K28,"Không đúng")+COUNTIF('Người thử 3'!K28,"Một phần")+COUNTIF('Người thử 3'!K28,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!K27,"Một phần")+COUNTIF('Người thử 1'!K27,"Không đúng")+COUNTIF('Người thử 2'!K27,"Một phần")+COUNTIF('Người thử 2'!K27,"Không đúng")+COUNTIF('Người thử 3'!K27,"Một phần")+COUNTIF('Người thử 3'!K27,"Không đúng")</f>
         <v/>
       </c>
       <c r="H24" s="62">
-        <f>COUNTIF('Người thử 1'!M28,"Một phần")+COUNTIF('Người thử 1'!M28,"Không đúng")+COUNTIF('Người thử 2'!M28,"Một phần")+COUNTIF('Người thử 2'!M28,"Không đúng")+COUNTIF('Người thử 3'!M28,"Một phần")+COUNTIF('Người thử 3'!M28,"Không đúng")</f>
+        <f>COUNTIF('Người thử 1'!M27,"Một phần")+COUNTIF('Người thử 1'!M27,"Không đúng")+COUNTIF('Người thử 2'!M27,"Một phần")+COUNTIF('Người thử 2'!M27,"Không đúng")+COUNTIF('Người thử 3'!M27,"Một phần")+COUNTIF('Người thử 3'!M27,"Không đúng")</f>
         <v/>
       </c>
       <c r="I24" s="57">
-        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O28,'Người thử 2'!O28,'Người thử 3'!O28),1),"")</f>
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O27,'Người thử 2'!O27,'Người thử 3'!O27),1),"")</f>
         <v/>
       </c>
     </row>
@@ -54431,7 +55505,7 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+          <t>Đăng xuất. Đăng nhập tài khoản GIÁO VIÊN của bạn.</t>
         </is>
       </c>
       <c r="D25" s="58">
@@ -54470,7 +55544,7 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+          <t>Vào tab HỌC SINH.</t>
         </is>
       </c>
       <c r="D26" s="58">
@@ -54498,378 +55572,828 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="41" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab CHẤM BÀI.</t>
+        </is>
+      </c>
+      <c r="D27" s="58">
+        <f>COUNTIF('Người thử 1'!E31,"Một phần")+COUNTIF('Người thử 1'!E31,"Không đúng")+COUNTIF('Người thử 2'!E31,"Một phần")+COUNTIF('Người thử 2'!E31,"Không đúng")+COUNTIF('Người thử 3'!E31,"Một phần")+COUNTIF('Người thử 3'!E31,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E27" s="59">
+        <f>COUNTIF('Người thử 1'!G31,"Một phần")+COUNTIF('Người thử 1'!G31,"Không đúng")+COUNTIF('Người thử 2'!G31,"Một phần")+COUNTIF('Người thử 2'!G31,"Không đúng")+COUNTIF('Người thử 3'!G31,"Một phần")+COUNTIF('Người thử 3'!G31,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F27" s="60">
+        <f>COUNTIF('Người thử 1'!I31,"Một phần")+COUNTIF('Người thử 1'!I31,"Không đúng")+COUNTIF('Người thử 2'!I31,"Một phần")+COUNTIF('Người thử 2'!I31,"Không đúng")+COUNTIF('Người thử 3'!I31,"Một phần")+COUNTIF('Người thử 3'!I31,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G27" s="61">
+        <f>COUNTIF('Người thử 1'!K31,"Một phần")+COUNTIF('Người thử 1'!K31,"Không đúng")+COUNTIF('Người thử 2'!K31,"Một phần")+COUNTIF('Người thử 2'!K31,"Không đúng")+COUNTIF('Người thử 3'!K31,"Một phần")+COUNTIF('Người thử 3'!K31,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H27" s="62">
+        <f>COUNTIF('Người thử 1'!M31,"Một phần")+COUNTIF('Người thử 1'!M31,"Không đúng")+COUNTIF('Người thử 2'!M31,"Một phần")+COUNTIF('Người thử 2'!M31,"Không đúng")+COUNTIF('Người thử 3'!M31,"Một phần")+COUNTIF('Người thử 3'!M31,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I27" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O31,'Người thử 2'!O31,'Người thử 3'!O31),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Chấm MỘT bài 'Chưa đạt' (kèm lời nhắn cho em) và MỘT bài 'Đạt'.</t>
+        </is>
+      </c>
+      <c r="D28" s="58">
+        <f>COUNTIF('Người thử 1'!E32,"Một phần")+COUNTIF('Người thử 1'!E32,"Không đúng")+COUNTIF('Người thử 2'!E32,"Một phần")+COUNTIF('Người thử 2'!E32,"Không đúng")+COUNTIF('Người thử 3'!E32,"Một phần")+COUNTIF('Người thử 3'!E32,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E28" s="59">
+        <f>COUNTIF('Người thử 1'!G32,"Một phần")+COUNTIF('Người thử 1'!G32,"Không đúng")+COUNTIF('Người thử 2'!G32,"Một phần")+COUNTIF('Người thử 2'!G32,"Không đúng")+COUNTIF('Người thử 3'!G32,"Một phần")+COUNTIF('Người thử 3'!G32,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F28" s="60">
+        <f>COUNTIF('Người thử 1'!I32,"Một phần")+COUNTIF('Người thử 1'!I32,"Không đúng")+COUNTIF('Người thử 2'!I32,"Một phần")+COUNTIF('Người thử 2'!I32,"Không đúng")+COUNTIF('Người thử 3'!I32,"Một phần")+COUNTIF('Người thử 3'!I32,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G28" s="61">
+        <f>COUNTIF('Người thử 1'!K32,"Một phần")+COUNTIF('Người thử 1'!K32,"Không đúng")+COUNTIF('Người thử 2'!K32,"Một phần")+COUNTIF('Người thử 2'!K32,"Không đúng")+COUNTIF('Người thử 3'!K32,"Một phần")+COUNTIF('Người thử 3'!K32,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H28" s="62">
+        <f>COUNTIF('Người thử 1'!M32,"Một phần")+COUNTIF('Người thử 1'!M32,"Không đúng")+COUNTIF('Người thử 2'!M32,"Một phần")+COUNTIF('Người thử 2'!M32,"Không đúng")+COUNTIF('Người thử 3'!M32,"Một phần")+COUNTIF('Người thử 3'!M32,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I28" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O32,'Người thử 2'!O32,'Người thử 3'!O32),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="41" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Vào tab HỌC LIỆU.</t>
+        </is>
+      </c>
+      <c r="D29" s="58">
+        <f>COUNTIF('Người thử 1'!E33,"Một phần")+COUNTIF('Người thử 1'!E33,"Không đúng")+COUNTIF('Người thử 2'!E33,"Một phần")+COUNTIF('Người thử 2'!E33,"Không đúng")+COUNTIF('Người thử 3'!E33,"Một phần")+COUNTIF('Người thử 3'!E33,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E29" s="59">
+        <f>COUNTIF('Người thử 1'!G33,"Một phần")+COUNTIF('Người thử 1'!G33,"Không đúng")+COUNTIF('Người thử 2'!G33,"Một phần")+COUNTIF('Người thử 2'!G33,"Không đúng")+COUNTIF('Người thử 3'!G33,"Một phần")+COUNTIF('Người thử 3'!G33,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F29" s="60">
+        <f>COUNTIF('Người thử 1'!I33,"Một phần")+COUNTIF('Người thử 1'!I33,"Không đúng")+COUNTIF('Người thử 2'!I33,"Một phần")+COUNTIF('Người thử 2'!I33,"Không đúng")+COUNTIF('Người thử 3'!I33,"Một phần")+COUNTIF('Người thử 3'!I33,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G29" s="61">
+        <f>COUNTIF('Người thử 1'!K33,"Một phần")+COUNTIF('Người thử 1'!K33,"Không đúng")+COUNTIF('Người thử 2'!K33,"Một phần")+COUNTIF('Người thử 2'!K33,"Không đúng")+COUNTIF('Người thử 3'!K33,"Một phần")+COUNTIF('Người thử 3'!K33,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H29" s="62">
+        <f>COUNTIF('Người thử 1'!M33,"Một phần")+COUNTIF('Người thử 1'!M33,"Không đúng")+COUNTIF('Người thử 2'!M33,"Một phần")+COUNTIF('Người thử 2'!M33,"Không đúng")+COUNTIF('Người thử 3'!M33,"Một phần")+COUNTIF('Người thử 3'!M33,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I29" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O33,'Người thử 2'!O33,'Người thử 3'!O33),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="41" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Chọn bài 'Khái niệm mệnh đề logic'. Ở khung 'Thêm học liệu': đặt tên, để MỨC 1, chọn kiểu 'Phim ngắn', DÁN một link YouTube, bấm THÊM VÀO BÀI.</t>
+        </is>
+      </c>
+      <c r="D30" s="58">
+        <f>COUNTIF('Người thử 1'!E34,"Một phần")+COUNTIF('Người thử 1'!E34,"Không đúng")+COUNTIF('Người thử 2'!E34,"Một phần")+COUNTIF('Người thử 2'!E34,"Không đúng")+COUNTIF('Người thử 3'!E34,"Một phần")+COUNTIF('Người thử 3'!E34,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E30" s="59">
+        <f>COUNTIF('Người thử 1'!G34,"Một phần")+COUNTIF('Người thử 1'!G34,"Không đúng")+COUNTIF('Người thử 2'!G34,"Một phần")+COUNTIF('Người thử 2'!G34,"Không đúng")+COUNTIF('Người thử 3'!G34,"Một phần")+COUNTIF('Người thử 3'!G34,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F30" s="60">
+        <f>COUNTIF('Người thử 1'!I34,"Một phần")+COUNTIF('Người thử 1'!I34,"Không đúng")+COUNTIF('Người thử 2'!I34,"Một phần")+COUNTIF('Người thử 2'!I34,"Không đúng")+COUNTIF('Người thử 3'!I34,"Một phần")+COUNTIF('Người thử 3'!I34,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G30" s="61">
+        <f>COUNTIF('Người thử 1'!K34,"Một phần")+COUNTIF('Người thử 1'!K34,"Không đúng")+COUNTIF('Người thử 2'!K34,"Một phần")+COUNTIF('Người thử 2'!K34,"Không đúng")+COUNTIF('Người thử 3'!K34,"Một phần")+COUNTIF('Người thử 3'!K34,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H30" s="62">
+        <f>COUNTIF('Người thử 1'!M34,"Một phần")+COUNTIF('Người thử 1'!M34,"Không đúng")+COUNTIF('Người thử 2'!M34,"Một phần")+COUNTIF('Người thử 2'!M34,"Không đúng")+COUNTIF('Người thử 3'!M34,"Một phần")+COUNTIF('Người thử 3'!M34,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I30" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O34,'Người thử 2'!O34,'Người thử 3'!O34),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Thêm mục THỨ HAI cũng ở MỨC 1 nhưng TẢI TỆP LÊN (ảnh, PDF hoặc file Word bất kỳ).</t>
+        </is>
+      </c>
+      <c r="D31" s="58">
+        <f>COUNTIF('Người thử 1'!E35,"Một phần")+COUNTIF('Người thử 1'!E35,"Không đúng")+COUNTIF('Người thử 2'!E35,"Một phần")+COUNTIF('Người thử 2'!E35,"Không đúng")+COUNTIF('Người thử 3'!E35,"Một phần")+COUNTIF('Người thử 3'!E35,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E31" s="59">
+        <f>COUNTIF('Người thử 1'!G35,"Một phần")+COUNTIF('Người thử 1'!G35,"Không đúng")+COUNTIF('Người thử 2'!G35,"Một phần")+COUNTIF('Người thử 2'!G35,"Không đúng")+COUNTIF('Người thử 3'!G35,"Một phần")+COUNTIF('Người thử 3'!G35,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F31" s="60">
+        <f>COUNTIF('Người thử 1'!I35,"Một phần")+COUNTIF('Người thử 1'!I35,"Không đúng")+COUNTIF('Người thử 2'!I35,"Một phần")+COUNTIF('Người thử 2'!I35,"Không đúng")+COUNTIF('Người thử 3'!I35,"Một phần")+COUNTIF('Người thử 3'!I35,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G31" s="61">
+        <f>COUNTIF('Người thử 1'!K35,"Một phần")+COUNTIF('Người thử 1'!K35,"Không đúng")+COUNTIF('Người thử 2'!K35,"Một phần")+COUNTIF('Người thử 2'!K35,"Không đúng")+COUNTIF('Người thử 3'!K35,"Một phần")+COUNTIF('Người thử 3'!K35,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H31" s="62">
+        <f>COUNTIF('Người thử 1'!M35,"Một phần")+COUNTIF('Người thử 1'!M35,"Không đúng")+COUNTIF('Người thử 2'!M35,"Một phần")+COUNTIF('Người thử 2'!M35,"Không đúng")+COUNTIF('Người thử 3'!M35,"Một phần")+COUNTIF('Người thử 3'!M35,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I31" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O35,'Người thử 2'!O35,'Người thử 3'!O35),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Bấm nút CON MẮT ở một trong hai mục để tắt.</t>
+        </is>
+      </c>
+      <c r="D32" s="58">
+        <f>COUNTIF('Người thử 1'!E36,"Một phần")+COUNTIF('Người thử 1'!E36,"Không đúng")+COUNTIF('Người thử 2'!E36,"Một phần")+COUNTIF('Người thử 2'!E36,"Không đúng")+COUNTIF('Người thử 3'!E36,"Một phần")+COUNTIF('Người thử 3'!E36,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E32" s="59">
+        <f>COUNTIF('Người thử 1'!G36,"Một phần")+COUNTIF('Người thử 1'!G36,"Không đúng")+COUNTIF('Người thử 2'!G36,"Một phần")+COUNTIF('Người thử 2'!G36,"Không đúng")+COUNTIF('Người thử 3'!G36,"Một phần")+COUNTIF('Người thử 3'!G36,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F32" s="60">
+        <f>COUNTIF('Người thử 1'!I36,"Một phần")+COUNTIF('Người thử 1'!I36,"Không đúng")+COUNTIF('Người thử 2'!I36,"Một phần")+COUNTIF('Người thử 2'!I36,"Không đúng")+COUNTIF('Người thử 3'!I36,"Một phần")+COUNTIF('Người thử 3'!I36,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G32" s="61">
+        <f>COUNTIF('Người thử 1'!K36,"Một phần")+COUNTIF('Người thử 1'!K36,"Không đúng")+COUNTIF('Người thử 2'!K36,"Một phần")+COUNTIF('Người thử 2'!K36,"Không đúng")+COUNTIF('Người thử 3'!K36,"Một phần")+COUNTIF('Người thử 3'!K36,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H32" s="62">
+        <f>COUNTIF('Người thử 1'!M36,"Một phần")+COUNTIF('Người thử 1'!M36,"Không đúng")+COUNTIF('Người thử 2'!M36,"Một phần")+COUNTIF('Người thử 2'!M36,"Không đúng")+COUNTIF('Người thử 3'!M36,"Một phần")+COUNTIF('Người thử 3'!M36,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I32" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O36,'Người thử 2'!O36,'Người thử 3'!O36),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="41" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Thêm một mục nữa nhưng chọn MỨC 2.</t>
+        </is>
+      </c>
+      <c r="D33" s="58">
+        <f>COUNTIF('Người thử 1'!E37,"Một phần")+COUNTIF('Người thử 1'!E37,"Không đúng")+COUNTIF('Người thử 2'!E37,"Một phần")+COUNTIF('Người thử 2'!E37,"Không đúng")+COUNTIF('Người thử 3'!E37,"Một phần")+COUNTIF('Người thử 3'!E37,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E33" s="59">
+        <f>COUNTIF('Người thử 1'!G37,"Một phần")+COUNTIF('Người thử 1'!G37,"Không đúng")+COUNTIF('Người thử 2'!G37,"Một phần")+COUNTIF('Người thử 2'!G37,"Không đúng")+COUNTIF('Người thử 3'!G37,"Một phần")+COUNTIF('Người thử 3'!G37,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F33" s="60">
+        <f>COUNTIF('Người thử 1'!I37,"Một phần")+COUNTIF('Người thử 1'!I37,"Không đúng")+COUNTIF('Người thử 2'!I37,"Một phần")+COUNTIF('Người thử 2'!I37,"Không đúng")+COUNTIF('Người thử 3'!I37,"Một phần")+COUNTIF('Người thử 3'!I37,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G33" s="61">
+        <f>COUNTIF('Người thử 1'!K37,"Một phần")+COUNTIF('Người thử 1'!K37,"Không đúng")+COUNTIF('Người thử 2'!K37,"Một phần")+COUNTIF('Người thử 2'!K37,"Không đúng")+COUNTIF('Người thử 3'!K37,"Một phần")+COUNTIF('Người thử 3'!K37,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H33" s="62">
+        <f>COUNTIF('Người thử 1'!M37,"Một phần")+COUNTIF('Người thử 1'!M37,"Không đúng")+COUNTIF('Người thử 2'!M37,"Một phần")+COUNTIF('Người thử 2'!M37,"Không đúng")+COUNTIF('Người thử 3'!M37,"Một phần")+COUNTIF('Người thử 3'!M37,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I33" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O37,'Người thử 2'!O37,'Người thử 3'!O37),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="41" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Xem tab TỔNG QUAN và tab CHỦ ĐỀ.</t>
+        </is>
+      </c>
+      <c r="D34" s="58">
+        <f>COUNTIF('Người thử 1'!E38,"Một phần")+COUNTIF('Người thử 1'!E38,"Không đúng")+COUNTIF('Người thử 2'!E38,"Một phần")+COUNTIF('Người thử 2'!E38,"Không đúng")+COUNTIF('Người thử 3'!E38,"Một phần")+COUNTIF('Người thử 3'!E38,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E34" s="59">
+        <f>COUNTIF('Người thử 1'!G38,"Một phần")+COUNTIF('Người thử 1'!G38,"Không đúng")+COUNTIF('Người thử 2'!G38,"Một phần")+COUNTIF('Người thử 2'!G38,"Không đúng")+COUNTIF('Người thử 3'!G38,"Một phần")+COUNTIF('Người thử 3'!G38,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F34" s="60">
+        <f>COUNTIF('Người thử 1'!I38,"Một phần")+COUNTIF('Người thử 1'!I38,"Không đúng")+COUNTIF('Người thử 2'!I38,"Một phần")+COUNTIF('Người thử 2'!I38,"Không đúng")+COUNTIF('Người thử 3'!I38,"Một phần")+COUNTIF('Người thử 3'!I38,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G34" s="61">
+        <f>COUNTIF('Người thử 1'!K38,"Một phần")+COUNTIF('Người thử 1'!K38,"Không đúng")+COUNTIF('Người thử 2'!K38,"Một phần")+COUNTIF('Người thử 2'!K38,"Không đúng")+COUNTIF('Người thử 3'!K38,"Một phần")+COUNTIF('Người thử 3'!K38,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H34" s="62">
+        <f>COUNTIF('Người thử 1'!M38,"Một phần")+COUNTIF('Người thử 1'!M38,"Không đúng")+COUNTIF('Người thử 2'!M38,"Một phần")+COUNTIF('Người thử 2'!M38,"Không đúng")+COUNTIF('Người thử 3'!M38,"Một phần")+COUNTIF('Người thử 3'!M38,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I34" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O38,'Người thử 2'!O38,'Người thử 3'!O38),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Giáo Viên</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Đăng nhập lại tài khoản HỌC SINH của bạn, mở lộ trình.</t>
+        </is>
+      </c>
+      <c r="D35" s="58">
+        <f>COUNTIF('Người thử 1'!E39,"Một phần")+COUNTIF('Người thử 1'!E39,"Không đúng")+COUNTIF('Người thử 2'!E39,"Một phần")+COUNTIF('Người thử 2'!E39,"Không đúng")+COUNTIF('Người thử 3'!E39,"Một phần")+COUNTIF('Người thử 3'!E39,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E35" s="59">
+        <f>COUNTIF('Người thử 1'!G39,"Một phần")+COUNTIF('Người thử 1'!G39,"Không đúng")+COUNTIF('Người thử 2'!G39,"Một phần")+COUNTIF('Người thử 2'!G39,"Không đúng")+COUNTIF('Người thử 3'!G39,"Một phần")+COUNTIF('Người thử 3'!G39,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F35" s="60">
+        <f>COUNTIF('Người thử 1'!I39,"Một phần")+COUNTIF('Người thử 1'!I39,"Không đúng")+COUNTIF('Người thử 2'!I39,"Một phần")+COUNTIF('Người thử 2'!I39,"Không đúng")+COUNTIF('Người thử 3'!I39,"Một phần")+COUNTIF('Người thử 3'!I39,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G35" s="61">
+        <f>COUNTIF('Người thử 1'!K39,"Một phần")+COUNTIF('Người thử 1'!K39,"Không đúng")+COUNTIF('Người thử 2'!K39,"Một phần")+COUNTIF('Người thử 2'!K39,"Không đúng")+COUNTIF('Người thử 3'!K39,"Một phần")+COUNTIF('Người thử 3'!K39,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H35" s="62">
+        <f>COUNTIF('Người thử 1'!M39,"Một phần")+COUNTIF('Người thử 1'!M39,"Không đúng")+COUNTIF('Người thử 2'!M39,"Một phần")+COUNTIF('Người thử 2'!M39,"Không đúng")+COUNTIF('Người thử 3'!M39,"Một phần")+COUNTIF('Người thử 3'!M39,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I35" s="57">
+        <f>IFERROR(ROUND(AVERAGE('Người thử 1'!O39,'Người thử 2'!O39,'Người thử 3'!O39),1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>KỊCH BẢN PHỐI HỢP</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
-      <c r="I28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="41" t="n">
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>KB1 · Ba em cùng nộp bài</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="58">
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E29" s="59">
+      <c r="E38" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F29" s="60">
+      <c r="F38" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G29" s="61">
+      <c r="G38" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H29" s="62">
+      <c r="H38" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O5,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O5,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="41" t="n">
+      <c r="I38" s="21" t="n"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>KB2 · Chấm chéo, trả bài</t>
         </is>
       </c>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="58">
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E30" s="59">
+      <c r="E39" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F30" s="60">
+      <c r="F39" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G30" s="61">
+      <c r="G39" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H30" s="62">
+      <c r="H39" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O6,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O6,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I30" s="21" t="n"/>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="41" t="n">
+      <c r="I39" s="21" t="n"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="41" t="n">
         <v>3</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>KB3 · Nộp lại sau khi bị trả</t>
         </is>
       </c>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="58">
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E31" s="59">
+      <c r="E40" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F31" s="60">
+      <c r="F40" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G31" s="61">
+      <c r="G40" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H31" s="62">
+      <c r="H40" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O7,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O7,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I31" s="21" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="41" t="n">
+      <c r="I40" s="21" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>KB4 · Hai giáo viên cùng chấm</t>
         </is>
       </c>
-      <c r="C32" s="21" t="n"/>
-      <c r="D32" s="58">
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E32" s="59">
+      <c r="E41" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F32" s="60">
+      <c r="F41" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G32" s="61">
+      <c r="G41" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H32" s="62">
+      <c r="H41" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O8,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O8,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="41" t="n">
+      <c r="I41" s="21" t="n"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>KB5 · Phụ huynh không được thấy con nhà khác</t>
         </is>
       </c>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="58">
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E33" s="59">
+      <c r="E42" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F33" s="60">
+      <c r="F42" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G33" s="61">
+      <c r="G42" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H33" s="62">
+      <c r="H42" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O9,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O9,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="41" t="n">
+      <c r="I42" s="21" t="n"/>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>KB6 · Bảng xếp hạng có đủ ba em</t>
         </is>
       </c>
-      <c r="C34" s="21" t="n"/>
-      <c r="D34" s="58">
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E34" s="59">
+      <c r="E43" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F34" s="60">
+      <c r="F43" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G34" s="61">
+      <c r="G43" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H34" s="62">
+      <c r="H43" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O10,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O10,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="41" t="n">
+      <c r="I43" s="21" t="n"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>KB7 · Cùng một bài, tiến độ riêng</t>
         </is>
       </c>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="58">
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E35" s="59">
+      <c r="E44" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F35" s="60">
+      <c r="F44" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G35" s="61">
+      <c r="G44" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H35" s="62">
+      <c r="H44" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O11,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O11,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I35" s="21" t="n"/>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="41" t="n">
+      <c r="I44" s="21" t="n"/>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>KB8 · Giáo viên bộ môn vs chủ nhiệm</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="58">
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="58">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="E36" s="59">
+      <c r="E45" s="59">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="F36" s="60">
+      <c r="F45" s="60">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="G36" s="61">
+      <c r="G45" s="61">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="H36" s="62">
+      <c r="H45" s="62">
         <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O12,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O12,"Không đúng")</f>
         <v/>
       </c>
-      <c r="I36" s="21" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="I45" s="21" t="n"/>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="41" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>KB9 · Thầy cô đăng, cả lớp cùng thấy</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="58">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G13,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G13,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E46" s="59">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I13,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I13,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F46" s="60">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K13,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K13,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G46" s="61">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M13,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M13,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H46" s="62">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O13,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O13,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I46" s="21" t="n"/>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>KB10 · Mỗi em một tiến trình kho báu</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="58">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G14,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G14,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E47" s="59">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I14,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I14,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F47" s="60">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K14,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K14,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G47" s="61">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M14,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M14,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H47" s="62">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O14,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O14,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I47" s="21" t="n"/>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>KB11 · Tắt con mắt là học sinh hết thấy</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="58">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!G15,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!G15,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="E48" s="59">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!I15,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!I15,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="F48" s="60">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!K15,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!K15,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="G48" s="61">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!M15,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!M15,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="H48" s="62">
+        <f>COUNTIF('KỊCH BẢN PHỐI HỢP'!O15,"Một phần")+COUNTIF('KỊCH BẢN PHỐI HỢP'!O15,"Không đúng")</f>
+        <v/>
+      </c>
+      <c r="I48" s="21" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>ĐÃ XONG CHƯA? (ba điều kiện dừng)</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>Còn lỗi CHẶN HẲN chưa xử lý</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="53">
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="53">
         <f>COUNTIFS('SỔ LỖI'!$F$7:$F$206,"Chặn hẳn",'SỔ LỖI'!$G$7:$G$206,"&lt;&gt;Đã xong")</f>
         <v/>
       </c>
-      <c r="E39" s="63" t="inlineStr">
+      <c r="E51" s="63" t="inlineStr">
         <is>
           <t>phải = 0</t>
         </is>
       </c>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Dòng sổ lỗi chưa đóng</t>
         </is>
       </c>
-      <c r="B40" s="21" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="53">
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="53">
         <f>COUNTIF('SỔ LỖI'!$G$7:$G$206,"Mới")+COUNTIF('SỔ LỖI'!$G$7:$G$206,"Đang sửa")+COUNTIF('SỔ LỖI'!$G$7:$G$206,"Đã sửa - chờ kiểm")</f>
         <v/>
       </c>
-      <c r="E40" s="63" t="inlineStr">
+      <c r="E52" s="63" t="inlineStr">
         <is>
           <t>phải = 0</t>
         </is>
       </c>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="21" t="n"/>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Số ô 'chưa ổn' của đợt gần nhất</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n"/>
-      <c r="C41" s="21" t="n"/>
-      <c r="D41" s="53">
-        <f>SUM(H4:H26)</f>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="53">
+        <f>SUM(H4:H35)</f>
         <v/>
       </c>
-      <c r="E41" s="63" t="inlineStr">
+      <c r="E53" s="63" t="inlineStr">
         <is>
           <t>càng gần 0 càng tốt</t>
         </is>
       </c>
-      <c r="F41" s="21" t="n"/>
-      <c r="G41" s="21" t="n"/>
-      <c r="H41" s="21" t="n"/>
-      <c r="I41" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="n"/>
+      <c r="H53" s="21" t="n"/>
+      <c r="I53" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="E40:I40"/>
+  <mergeCells count="21">
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="E52:I52"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="E53:I53"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B48:C48"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="E51:I51"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B41:C41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
